--- a/Gott Bike/INDICADORES DIÁRIOS.xlsx
+++ b/Gott Bike/INDICADORES DIÁRIOS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8d3dd0af008984df/Consultorias/GOTT BIKE/Compartilhado GOTT Bike/Indicadores e Métricas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8d3dd0af008984df/Consultorias/GitHub/Cotta-Consultoria/Gott Bike/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2213" documentId="8_{49B7964F-2481-4178-A148-E82770C67CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BF8F591-8C42-47EF-AFA1-72F1A96CA7B3}"/>
+  <xr:revisionPtr revIDLastSave="2218" documentId="8_{49B7964F-2481-4178-A148-E82770C67CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88117421-4F24-45C9-BE07-16D8E53B5170}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AF016D11-4BBA-49FD-9799-541824B780DA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{AF016D11-4BBA-49FD-9799-541824B780DA}"/>
   </bookViews>
   <sheets>
     <sheet name="Faturamento" sheetId="4" r:id="rId1"/>
@@ -763,7 +763,7 @@
     <numFmt numFmtId="164" formatCode="ddd\ dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1092,7 +1092,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1244,16 +1244,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1272,8 +1268,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -1438,13 +1432,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color theme="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color theme="1"/>
         </left>
@@ -1479,6 +1466,13 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1504,10 +1498,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <numFmt numFmtId="164" formatCode="ddd\ dd/mm/yyyy"/>
     </dxf>
     <dxf>
       <font>
@@ -1568,13 +1562,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color theme="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color theme="1"/>
         </left>
@@ -1609,6 +1596,13 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1634,10 +1628,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="ddd\ dd/mm/yyyy"/>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <font>
@@ -1689,14 +1683,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4D968E04-06EF-4CC7-9C6F-A57B1CBB5F4B}" name="Tabela1" displayName="Tabela1" ref="B3:E107" totalsRowShown="0" headerRowDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4D968E04-06EF-4CC7-9C6F-A57B1CBB5F4B}" name="Tabela1" displayName="Tabela1" ref="B3:E107" totalsRowShown="0" headerRowDxfId="21">
   <autoFilter ref="B3:E107" xr:uid="{4D968E04-06EF-4CC7-9C6F-A57B1CBB5F4B}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:E89">
     <sortCondition ref="B3:B89"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{BB065966-614D-4168-B93D-A210BB1E0C8D}" name="Data" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{0E418006-DCE5-4F97-93B4-A899D67631E7}" name="Qtde" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{BB065966-614D-4168-B93D-A210BB1E0C8D}" name="Data" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{0E418006-DCE5-4F97-93B4-A899D67631E7}" name="Qtde" dataDxfId="19"/>
     <tableColumn id="3" xr3:uid="{5E9349A6-F048-4999-B707-3D89C965382E}" name="Plataforma"/>
     <tableColumn id="4" xr3:uid="{11AA1DC1-1AE5-4E49-B53D-967E3111E872}" name="(R$) Valor" dataCellStyle="Moeda"/>
   </tableColumns>
@@ -1705,22 +1699,22 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0EF1F2A8-F80A-407B-8B7B-0BFBFEDF6A0D}" name="Tabela8" displayName="Tabela8" ref="G2:G10" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26" headerRowBorderDxfId="24" tableBorderDxfId="25" totalsRowBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0EF1F2A8-F80A-407B-8B7B-0BFBFEDF6A0D}" name="Tabela8" displayName="Tabela8" ref="G2:G10" totalsRowShown="0" headerRowDxfId="18" dataDxfId="16" headerRowBorderDxfId="17" tableBorderDxfId="15" totalsRowBorderDxfId="14">
   <autoFilter ref="G2:G10" xr:uid="{0EF1F2A8-F80A-407B-8B7B-0BFBFEDF6A0D}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{047DC460-557A-40DB-8C81-95DF946F5AD7}" name="PLATAFORMAS" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{047DC460-557A-40DB-8C81-95DF946F5AD7}" name="PLATAFORMAS" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6EB69137-5DEF-4DEE-A295-1FA4C5115578}" name="Tabela135" displayName="Tabela135" ref="B3:F53" totalsRowShown="0" headerRowDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6EB69137-5DEF-4DEE-A295-1FA4C5115578}" name="Tabela135" displayName="Tabela135" ref="B3:F53" totalsRowShown="0" headerRowDxfId="30">
   <autoFilter ref="B3:F53" xr:uid="{6EB69137-5DEF-4DEE-A295-1FA4C5115578}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{F39CB7F4-E762-4BDF-B2C6-8749DB68D027}" name="Data"/>
-    <tableColumn id="2" xr3:uid="{E9E42632-7C2F-4C97-BCA4-C914BCBA10DC}" name="Banco" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{5B08F7C6-B877-42F6-98D4-8D56834BE254}" name="Plataforma" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{E9E42632-7C2F-4C97-BCA4-C914BCBA10DC}" name="Banco" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{5B08F7C6-B877-42F6-98D4-8D56834BE254}" name="Plataforma" dataDxfId="28"/>
     <tableColumn id="6" xr3:uid="{F7822F46-F359-40F0-8736-0420E5F8BEF4}" name="Descrição"/>
     <tableColumn id="4" xr3:uid="{D0BDF5C5-4A71-4AC2-A4FF-BA03AF90DFCB}" name="(R$) Valor" dataCellStyle="Moeda"/>
   </tableColumns>
@@ -1729,10 +1723,10 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{67A3570C-9B27-40AF-9CD6-28857E5EBB30}" name="Tabela810" displayName="Tabela810" ref="L2:L14" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17" headerRowBorderDxfId="15" tableBorderDxfId="16" totalsRowBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{67A3570C-9B27-40AF-9CD6-28857E5EBB30}" name="Tabela810" displayName="Tabela810" ref="L2:L14" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
   <autoFilter ref="L2:L14" xr:uid="{67A3570C-9B27-40AF-9CD6-28857E5EBB30}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{9127BBB1-B684-40F8-8735-E6EFF2611541}" name="PLATAFORMAS" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{9127BBB1-B684-40F8-8735-E6EFF2611541}" name="PLATAFORMAS" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2106,23 +2100,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{152610B4-81C2-44F7-A8DF-A454E1B8F2ED}">
   <dimension ref="B1:L105"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.5703125" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="2.7109375" customWidth="1"/>
-    <col min="7" max="7" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="2.7109375" customWidth="1"/>
-    <col min="9" max="9" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.85546875" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.5546875" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="2.6640625" customWidth="1"/>
+    <col min="7" max="7" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.6640625" customWidth="1"/>
+    <col min="9" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.88671875" customWidth="1"/>
     <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C1" s="60">
         <f>SUBTOTAL(9,Tabela1[Qtde])</f>
         <v>1533</v>
@@ -2132,7 +2126,7 @@
         <v>1150759.95</v>
       </c>
     </row>
-    <row r="2" spans="2:12">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B2" s="69" t="s">
         <v>0</v>
       </c>
@@ -2155,7 +2149,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="2:12" s="2" customFormat="1">
+    <row r="3" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
@@ -2186,7 +2180,7 @@
         <v>705.9876993865031</v>
       </c>
     </row>
-    <row r="4" spans="2:12">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" s="4">
         <v>46113</v>
       </c>
@@ -2203,7 +2197,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:12">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="4">
         <v>46113</v>
       </c>
@@ -2220,7 +2214,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="2:12">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="4">
         <v>46113</v>
       </c>
@@ -2237,7 +2231,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="2:12">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="4">
         <v>46113</v>
       </c>
@@ -2254,7 +2248,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="2:12">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="4">
         <v>46113</v>
       </c>
@@ -2271,7 +2265,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="2:12">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
         <v>46114</v>
       </c>
@@ -2288,7 +2282,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="2:12">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
         <v>46114</v>
       </c>
@@ -2305,7 +2299,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="2:12">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
         <v>46114</v>
       </c>
@@ -2319,7 +2313,7 @@
         <v>9293.6299999999992</v>
       </c>
     </row>
-    <row r="12" spans="2:12">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
         <v>46114</v>
       </c>
@@ -2333,7 +2327,7 @@
         <v>28799.62</v>
       </c>
     </row>
-    <row r="13" spans="2:12">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="4">
         <v>46115</v>
       </c>
@@ -2347,7 +2341,7 @@
         <v>15133.97</v>
       </c>
     </row>
-    <row r="14" spans="2:12">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="4">
         <v>46115</v>
       </c>
@@ -2361,7 +2355,7 @@
         <v>6839.16</v>
       </c>
     </row>
-    <row r="15" spans="2:12">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
         <v>46115</v>
       </c>
@@ -2375,7 +2369,7 @@
         <v>1410.4</v>
       </c>
     </row>
-    <row r="16" spans="2:12">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="4">
         <v>46115</v>
       </c>
@@ -2389,7 +2383,7 @@
         <v>2377.9</v>
       </c>
     </row>
-    <row r="17" spans="2:5">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="4">
         <v>46116</v>
       </c>
@@ -2403,7 +2397,7 @@
         <v>590.22</v>
       </c>
     </row>
-    <row r="18" spans="2:5">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="4">
         <v>46116</v>
       </c>
@@ -2417,7 +2411,7 @@
         <v>6866.8</v>
       </c>
     </row>
-    <row r="19" spans="2:5">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
         <v>46116</v>
       </c>
@@ -2431,7 +2425,7 @@
         <v>32745.85</v>
       </c>
     </row>
-    <row r="20" spans="2:5">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
         <v>46116</v>
       </c>
@@ -2445,7 +2439,7 @@
         <v>899.38</v>
       </c>
     </row>
-    <row r="21" spans="2:5">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="4">
         <v>46116</v>
       </c>
@@ -2459,7 +2453,7 @@
         <v>753.9</v>
       </c>
     </row>
-    <row r="22" spans="2:5">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="4">
         <v>46117</v>
       </c>
@@ -2473,7 +2467,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="23" spans="2:5">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="4">
         <v>46117</v>
       </c>
@@ -2487,7 +2481,7 @@
         <v>8018.35</v>
       </c>
     </row>
-    <row r="24" spans="2:5">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="4">
         <v>46117</v>
       </c>
@@ -2501,7 +2495,7 @@
         <v>23954.81</v>
       </c>
     </row>
-    <row r="25" spans="2:5">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="4">
         <v>46117</v>
       </c>
@@ -2515,7 +2509,7 @@
         <v>2301.6999999999998</v>
       </c>
     </row>
-    <row r="26" spans="2:5">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
         <v>46118</v>
       </c>
@@ -2529,7 +2523,7 @@
         <v>951.74</v>
       </c>
     </row>
-    <row r="27" spans="2:5">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" s="4">
         <v>46118</v>
       </c>
@@ -2543,7 +2537,7 @@
         <v>10337.6</v>
       </c>
     </row>
-    <row r="28" spans="2:5">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" s="4">
         <v>46118</v>
       </c>
@@ -2557,7 +2551,7 @@
         <v>29270.240000000002</v>
       </c>
     </row>
-    <row r="29" spans="2:5">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" s="4">
         <v>46119</v>
       </c>
@@ -2571,7 +2565,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="30" spans="2:5">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30" s="4">
         <v>46119</v>
       </c>
@@ -2585,7 +2579,7 @@
         <v>773.9</v>
       </c>
     </row>
-    <row r="31" spans="2:5">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
         <v>46119</v>
       </c>
@@ -2599,7 +2593,7 @@
         <v>13085.68</v>
       </c>
     </row>
-    <row r="32" spans="2:5">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
         <v>46119</v>
       </c>
@@ -2613,7 +2607,7 @@
         <v>47337.96</v>
       </c>
     </row>
-    <row r="33" spans="2:5">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33" s="4">
         <v>46119</v>
       </c>
@@ -2627,7 +2621,7 @@
         <v>663.5</v>
       </c>
     </row>
-    <row r="34" spans="2:5">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
         <v>46119</v>
       </c>
@@ -2641,7 +2635,7 @@
         <v>6828.1</v>
       </c>
     </row>
-    <row r="35" spans="2:5">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35" s="4">
         <v>46120</v>
       </c>
@@ -2655,7 +2649,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="36" spans="2:5">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36" s="4">
         <v>46120</v>
       </c>
@@ -2669,7 +2663,7 @@
         <v>8784.39</v>
       </c>
     </row>
-    <row r="37" spans="2:5">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B37" s="4">
         <v>46120</v>
       </c>
@@ -2683,7 +2677,7 @@
         <v>45046.9</v>
       </c>
     </row>
-    <row r="38" spans="2:5">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B38" s="4">
         <v>46120</v>
       </c>
@@ -2697,7 +2691,7 @@
         <v>5117.6000000000004</v>
       </c>
     </row>
-    <row r="39" spans="2:5">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B39" s="4">
         <v>46121</v>
       </c>
@@ -2711,7 +2705,7 @@
         <v>893.9</v>
       </c>
     </row>
-    <row r="40" spans="2:5">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B40" s="4">
         <v>46121</v>
       </c>
@@ -2725,7 +2719,7 @@
         <v>2922.54</v>
       </c>
     </row>
-    <row r="41" spans="2:5">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
         <v>46121</v>
       </c>
@@ -2739,7 +2733,7 @@
         <v>45523.38</v>
       </c>
     </row>
-    <row r="42" spans="2:5">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B42" s="4">
         <v>46121</v>
       </c>
@@ -2753,7 +2747,7 @@
         <v>4429.8999999999996</v>
       </c>
     </row>
-    <row r="43" spans="2:5">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B43" s="4">
         <v>46122</v>
       </c>
@@ -2767,7 +2761,7 @@
         <v>1591.8</v>
       </c>
     </row>
-    <row r="44" spans="2:5">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
         <v>46122</v>
       </c>
@@ -2781,7 +2775,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="45" spans="2:5">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B45" s="4">
         <v>46122</v>
       </c>
@@ -2795,7 +2789,7 @@
         <v>2264.6999999999998</v>
       </c>
     </row>
-    <row r="46" spans="2:5">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B46" s="4">
         <v>46122</v>
       </c>
@@ -2809,7 +2803,7 @@
         <v>53207.86</v>
       </c>
     </row>
-    <row r="47" spans="2:5">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
         <v>46123</v>
       </c>
@@ -2823,7 +2817,7 @@
         <v>3279.6</v>
       </c>
     </row>
-    <row r="48" spans="2:5">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B48" s="4">
         <v>46123</v>
       </c>
@@ -2837,7 +2831,7 @@
         <v>1767.8</v>
       </c>
     </row>
-    <row r="49" spans="2:5">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B49" s="4">
         <v>46123</v>
       </c>
@@ -2851,7 +2845,7 @@
         <v>753.9</v>
       </c>
     </row>
-    <row r="50" spans="2:5">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B50" s="4">
         <v>46123</v>
       </c>
@@ -2865,7 +2859,7 @@
         <v>55008.160000000003</v>
       </c>
     </row>
-    <row r="51" spans="2:5">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B51" s="4">
         <v>46124</v>
       </c>
@@ -2879,7 +2873,7 @@
         <v>2166.7800000000002</v>
       </c>
     </row>
-    <row r="52" spans="2:5">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B52" s="4">
         <v>46124</v>
       </c>
@@ -2893,7 +2887,7 @@
         <v>4149.7</v>
       </c>
     </row>
-    <row r="53" spans="2:5">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B53" s="4">
         <v>46124</v>
       </c>
@@ -2907,7 +2901,7 @@
         <v>43064.74</v>
       </c>
     </row>
-    <row r="54" spans="2:5">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B54" s="4">
         <v>46125</v>
       </c>
@@ -2921,7 +2915,7 @@
         <v>5023.46</v>
       </c>
     </row>
-    <row r="55" spans="2:5">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B55" s="4">
         <v>46125</v>
       </c>
@@ -2935,7 +2929,7 @@
         <v>48180.23</v>
       </c>
     </row>
-    <row r="56" spans="2:5">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B56" s="4">
         <v>46125</v>
       </c>
@@ -2949,7 +2943,7 @@
         <v>2529.8000000000002</v>
       </c>
     </row>
-    <row r="57" spans="2:5">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B57" s="4">
         <v>46126</v>
       </c>
@@ -2963,7 +2957,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="58" spans="2:5">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B58" s="4">
         <v>46126</v>
       </c>
@@ -2977,7 +2971,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="59" spans="2:5">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B59" s="4">
         <v>46126</v>
       </c>
@@ -2991,7 +2985,7 @@
         <v>5707</v>
       </c>
     </row>
-    <row r="60" spans="2:5">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B60" s="4">
         <v>46126</v>
       </c>
@@ -3005,7 +2999,7 @@
         <v>24605</v>
       </c>
     </row>
-    <row r="61" spans="2:5">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B61" s="4">
         <v>46126</v>
       </c>
@@ -3019,7 +3013,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="62" spans="2:5">
+    <row r="62" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B62" s="4">
         <v>46127</v>
       </c>
@@ -3033,7 +3027,7 @@
         <v>2388.38</v>
       </c>
     </row>
-    <row r="63" spans="2:5">
+    <row r="63" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B63" s="4">
         <v>46127</v>
       </c>
@@ -3047,7 +3041,7 @@
         <v>49270.34</v>
       </c>
     </row>
-    <row r="64" spans="2:5">
+    <row r="64" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B64" s="4">
         <v>46127</v>
       </c>
@@ -3061,7 +3055,7 @@
         <v>923.49</v>
       </c>
     </row>
-    <row r="65" spans="2:5">
+    <row r="65" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B65" s="4">
         <v>46127</v>
       </c>
@@ -3075,7 +3069,7 @@
         <v>3091.9</v>
       </c>
     </row>
-    <row r="66" spans="2:5">
+    <row r="66" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B66" s="4">
         <v>46127</v>
       </c>
@@ -3089,7 +3083,7 @@
         <v>2037.9</v>
       </c>
     </row>
-    <row r="67" spans="2:5">
+    <row r="67" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B67" s="4">
         <v>46128</v>
       </c>
@@ -3103,7 +3097,7 @@
         <v>1727.8</v>
       </c>
     </row>
-    <row r="68" spans="2:5">
+    <row r="68" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B68" s="4">
         <v>46128</v>
       </c>
@@ -3117,7 +3111,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="69" spans="2:5">
+    <row r="69" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B69" s="4">
         <v>46128</v>
       </c>
@@ -3131,7 +3125,7 @@
         <v>4734.04</v>
       </c>
     </row>
-    <row r="70" spans="2:5">
+    <row r="70" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B70" s="4">
         <v>46128</v>
       </c>
@@ -3145,7 +3139,7 @@
         <v>42282.67</v>
       </c>
     </row>
-    <row r="71" spans="2:5">
+    <row r="71" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B71" s="4">
         <v>46129</v>
       </c>
@@ -3159,7 +3153,7 @@
         <v>880.2</v>
       </c>
     </row>
-    <row r="72" spans="2:5">
+    <row r="72" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B72" s="4">
         <v>46129</v>
       </c>
@@ -3173,7 +3167,7 @@
         <v>2240.2600000000002</v>
       </c>
     </row>
-    <row r="73" spans="2:5">
+    <row r="73" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B73" s="4">
         <v>46129</v>
       </c>
@@ -3187,7 +3181,7 @@
         <v>37764</v>
       </c>
     </row>
-    <row r="74" spans="2:5">
+    <row r="74" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B74" s="4">
         <v>46129</v>
       </c>
@@ -3201,7 +3195,7 @@
         <v>713.9</v>
       </c>
     </row>
-    <row r="75" spans="2:5">
+    <row r="75" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B75" s="4">
         <v>46130</v>
       </c>
@@ -3215,7 +3209,7 @@
         <v>5175.68</v>
       </c>
     </row>
-    <row r="76" spans="2:5">
+    <row r="76" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B76" s="4">
         <v>46130</v>
       </c>
@@ -3229,7 +3223,7 @@
         <v>29981.46</v>
       </c>
     </row>
-    <row r="77" spans="2:5">
+    <row r="77" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B77" s="4">
         <v>46130</v>
       </c>
@@ -3243,7 +3237,7 @@
         <v>623.9</v>
       </c>
     </row>
-    <row r="78" spans="2:5">
+    <row r="78" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B78" s="4">
         <v>46131</v>
       </c>
@@ -3257,7 +3251,7 @@
         <v>3275</v>
       </c>
     </row>
-    <row r="79" spans="2:5">
+    <row r="79" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B79" s="4">
         <v>46131</v>
       </c>
@@ -3271,7 +3265,7 @@
         <v>1486.72</v>
       </c>
     </row>
-    <row r="80" spans="2:5">
+    <row r="80" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B80" s="4">
         <v>46131</v>
       </c>
@@ -3285,7 +3279,7 @@
         <v>24359.4</v>
       </c>
     </row>
-    <row r="81" spans="2:5">
+    <row r="81" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B81" s="4">
         <v>46131</v>
       </c>
@@ -3299,7 +3293,7 @@
         <v>733.9</v>
       </c>
     </row>
-    <row r="82" spans="2:5">
+    <row r="82" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B82" s="4">
         <v>46132</v>
       </c>
@@ -3313,7 +3307,7 @@
         <v>4190.3599999999997</v>
       </c>
     </row>
-    <row r="83" spans="2:5">
+    <row r="83" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B83" s="4">
         <v>46132</v>
       </c>
@@ -3327,7 +3321,7 @@
         <v>37618.129999999997</v>
       </c>
     </row>
-    <row r="84" spans="2:5">
+    <row r="84" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B84" s="4">
         <v>46132</v>
       </c>
@@ -3341,7 +3335,7 @@
         <v>4079.5</v>
       </c>
     </row>
-    <row r="85" spans="2:5">
+    <row r="85" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B85" s="4">
         <v>46133</v>
       </c>
@@ -3355,7 +3349,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="86" spans="2:5">
+    <row r="86" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B86" s="4">
         <v>46133</v>
       </c>
@@ -3369,7 +3363,7 @@
         <v>743.85</v>
       </c>
     </row>
-    <row r="87" spans="2:5">
+    <row r="87" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B87" s="4">
         <v>46133</v>
       </c>
@@ -3383,7 +3377,7 @@
         <v>4336.0200000000004</v>
       </c>
     </row>
-    <row r="88" spans="2:5">
+    <row r="88" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B88" s="4">
         <v>46133</v>
       </c>
@@ -3397,7 +3391,7 @@
         <v>22422.71</v>
       </c>
     </row>
-    <row r="89" spans="2:5">
+    <row r="89" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B89" s="4">
         <v>46133</v>
       </c>
@@ -3411,7 +3405,7 @@
         <v>1876.1</v>
       </c>
     </row>
-    <row r="90" spans="2:5">
+    <row r="90" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B90" s="4">
         <v>46134</v>
       </c>
@@ -3425,7 +3419,7 @@
         <v>2106.98</v>
       </c>
     </row>
-    <row r="91" spans="2:5">
+    <row r="91" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B91" s="4">
         <v>46134</v>
       </c>
@@ -3439,7 +3433,7 @@
         <v>86913.33</v>
       </c>
     </row>
-    <row r="92" spans="2:5">
+    <row r="92" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B92" s="4">
         <v>46134</v>
       </c>
@@ -3453,7 +3447,7 @@
         <v>2801.7</v>
       </c>
     </row>
-    <row r="93" spans="2:5">
+    <row r="93" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B93" s="4">
         <v>46135</v>
       </c>
@@ -3467,7 +3461,7 @@
         <v>825.9</v>
       </c>
     </row>
-    <row r="94" spans="2:5">
+    <row r="94" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B94" s="4">
         <v>46135</v>
       </c>
@@ -3481,7 +3475,7 @@
         <v>27646.44</v>
       </c>
     </row>
-    <row r="95" spans="2:5">
+    <row r="95" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B95" s="4">
         <v>46135</v>
       </c>
@@ -3495,7 +3489,7 @@
         <v>4102.1000000000004</v>
       </c>
     </row>
-    <row r="96" spans="2:5">
+    <row r="96" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B96" s="4">
         <v>46136</v>
       </c>
@@ -3509,7 +3503,7 @@
         <v>1347.8</v>
       </c>
     </row>
-    <row r="97" spans="2:5">
+    <row r="97" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B97" s="4">
         <v>46136</v>
       </c>
@@ -3523,7 +3517,7 @@
         <v>739.9</v>
       </c>
     </row>
-    <row r="98" spans="2:5">
+    <row r="98" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B98" s="4">
         <v>46136</v>
       </c>
@@ -3537,7 +3531,7 @@
         <v>1595.88</v>
       </c>
     </row>
-    <row r="99" spans="2:5">
+    <row r="99" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B99" s="4">
         <v>46136</v>
       </c>
@@ -3551,7 +3545,7 @@
         <v>15251.65</v>
       </c>
     </row>
-    <row r="100" spans="2:5">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B100" s="4">
         <v>46137</v>
       </c>
@@ -3565,7 +3559,7 @@
         <v>539.12</v>
       </c>
     </row>
-    <row r="101" spans="2:5">
+    <row r="101" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B101" s="4">
         <v>46137</v>
       </c>
@@ -3579,7 +3573,7 @@
         <v>22818.080000000002</v>
       </c>
     </row>
-    <row r="102" spans="2:5">
+    <row r="102" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B102" s="4">
         <v>46137</v>
       </c>
@@ -3593,7 +3587,7 @@
         <v>2348</v>
       </c>
     </row>
-    <row r="103" spans="2:5">
+    <row r="103" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B103" s="4">
         <v>46138</v>
       </c>
@@ -3607,7 +3601,7 @@
         <v>2299.08</v>
       </c>
     </row>
-    <row r="104" spans="2:5">
+    <row r="104" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B104" s="4">
         <v>46138</v>
       </c>
@@ -3621,7 +3615,7 @@
         <v>25019.45</v>
       </c>
     </row>
-    <row r="105" spans="2:5">
+    <row r="105" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B105" s="4">
         <v>46138</v>
       </c>
@@ -3656,29 +3650,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D51AF1E-9915-47D4-8A4E-D08B404C994F}">
   <dimension ref="B1:L58"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="60.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.140625" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="60.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.109375" customWidth="1"/>
+    <col min="8" max="8" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="3.7109375" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.6640625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="14.45">
+    <row r="1" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="F1" s="12">
         <f>SUBTOTAL(9,Tabela135[(R$) Valor])</f>
         <v>814152.59</v>
       </c>
     </row>
-    <row r="2" spans="2:12" ht="14.45">
+    <row r="2" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B2" s="69" t="s">
         <v>19</v>
       </c>
@@ -3695,7 +3689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="14.45">
+    <row r="3" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
@@ -3724,7 +3718,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="14.45">
+    <row r="4" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B4" s="4">
         <v>46114</v>
       </c>
@@ -3740,7 +3734,7 @@
       <c r="F4" s="6">
         <v>20435</v>
       </c>
-      <c r="H4" s="75">
+      <c r="H4" s="67">
         <v>46030</v>
       </c>
       <c r="I4" s="20">
@@ -3753,7 +3747,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="14.45">
+    <row r="5" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B5" s="4">
         <v>46118</v>
       </c>
@@ -3769,7 +3763,7 @@
       <c r="F5" s="6">
         <v>13502</v>
       </c>
-      <c r="H5" s="76">
+      <c r="H5" s="68">
         <v>46042</v>
       </c>
       <c r="I5" s="17">
@@ -3782,7 +3776,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="14.45">
+    <row r="6" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B6" s="4">
         <v>46118</v>
       </c>
@@ -3798,7 +3792,7 @@
       <c r="F6" s="6">
         <v>82.59</v>
       </c>
-      <c r="H6" s="75">
+      <c r="H6" s="67">
         <v>46051</v>
       </c>
       <c r="I6" s="20">
@@ -3811,7 +3805,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="14.45">
+    <row r="7" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B7" s="4">
         <v>46118</v>
       </c>
@@ -3827,7 +3821,7 @@
       <c r="F7" s="6">
         <v>266.32</v>
       </c>
-      <c r="H7" s="76">
+      <c r="H7" s="68">
         <v>46087</v>
       </c>
       <c r="I7" s="17">
@@ -3840,7 +3834,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="14.45">
+    <row r="8" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B8" s="4">
         <v>46118</v>
       </c>
@@ -3856,7 +3850,7 @@
       <c r="F8" s="6">
         <v>0</v>
       </c>
-      <c r="H8" s="75">
+      <c r="H8" s="67">
         <v>46090</v>
       </c>
       <c r="I8" s="20">
@@ -3869,7 +3863,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="14.45">
+    <row r="9" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
         <v>46118</v>
       </c>
@@ -3885,7 +3879,7 @@
       <c r="F9" s="6">
         <v>46650</v>
       </c>
-      <c r="H9" s="76">
+      <c r="H9" s="68">
         <v>46119</v>
       </c>
       <c r="I9" s="17">
@@ -3898,7 +3892,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="14.45">
+    <row r="10" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
         <v>46119</v>
       </c>
@@ -3914,7 +3908,7 @@
       <c r="F10" s="6">
         <v>542.97</v>
       </c>
-      <c r="H10" s="75">
+      <c r="H10" s="67">
         <v>46122</v>
       </c>
       <c r="I10" s="20">
@@ -3927,7 +3921,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="14.45">
+    <row r="11" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
         <v>46119</v>
       </c>
@@ -3943,7 +3937,7 @@
       <c r="F11" s="6">
         <v>50000</v>
       </c>
-      <c r="H11" s="76">
+      <c r="H11" s="68">
         <v>46129</v>
       </c>
       <c r="I11" s="17">
@@ -3956,7 +3950,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="14.45">
+    <row r="12" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
         <v>46119</v>
       </c>
@@ -3969,7 +3963,7 @@
       <c r="F12" s="6">
         <v>3200</v>
       </c>
-      <c r="H12" s="75">
+      <c r="H12" s="67">
         <v>46132</v>
       </c>
       <c r="I12" s="41">
@@ -3982,7 +3976,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="14.45">
+    <row r="13" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B13" s="4">
         <v>46120</v>
       </c>
@@ -3998,7 +3992,7 @@
       <c r="F13" s="6">
         <v>350</v>
       </c>
-      <c r="H13" s="76">
+      <c r="H13" s="68">
         <v>46134</v>
       </c>
       <c r="I13" s="50">
@@ -4011,7 +4005,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="14.45">
+    <row r="14" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B14" s="4">
         <v>46120</v>
       </c>
@@ -4027,7 +4021,7 @@
       <c r="F14" s="6">
         <v>24769</v>
       </c>
-      <c r="H14" s="75">
+      <c r="H14" s="67">
         <v>46134</v>
       </c>
       <c r="I14" s="41">
@@ -4040,7 +4034,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="14.45">
+    <row r="15" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
         <v>46121</v>
       </c>
@@ -4056,7 +4050,7 @@
       <c r="F15" s="6">
         <v>469.86</v>
       </c>
-      <c r="H15" s="76">
+      <c r="H15" s="68">
         <v>46137</v>
       </c>
       <c r="I15" s="50">
@@ -4066,7 +4060,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="14.45">
+    <row r="16" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B16" s="4">
         <v>46121</v>
       </c>
@@ -4082,7 +4076,7 @@
       <c r="F16" s="6">
         <v>50000</v>
       </c>
-      <c r="H16" s="75">
+      <c r="H16" s="67">
         <v>46137</v>
       </c>
       <c r="I16" s="20">
@@ -4092,7 +4086,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="14.45">
+    <row r="17" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B17" s="4">
         <v>46122</v>
       </c>
@@ -4109,7 +4103,7 @@
         <v>2290.2800000000002</v>
       </c>
     </row>
-    <row r="18" spans="2:9" ht="14.45">
+    <row r="18" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B18" s="4">
         <v>46122</v>
       </c>
@@ -4126,7 +4120,7 @@
         <v>479.72</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="14.45">
+    <row r="19" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
         <v>46122</v>
       </c>
@@ -4150,7 +4144,7 @@
         <v>769827.59</v>
       </c>
     </row>
-    <row r="20" spans="2:9" ht="14.45">
+    <row r="20" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
         <v>46122</v>
       </c>
@@ -4174,7 +4168,7 @@
         <v>44325</v>
       </c>
     </row>
-    <row r="21" spans="2:9" ht="14.45">
+    <row r="21" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B21" s="4">
         <v>46122</v>
       </c>
@@ -4192,7 +4186,7 @@
         <v>814152.59</v>
       </c>
     </row>
-    <row r="22" spans="2:9" ht="14.45">
+    <row r="22" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B22" s="4">
         <v>46125</v>
       </c>
@@ -4209,7 +4203,7 @@
         <v>24850</v>
       </c>
     </row>
-    <row r="23" spans="2:9" ht="14.45">
+    <row r="23" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B23" s="4">
         <v>46125</v>
       </c>
@@ -4226,7 +4220,7 @@
         <v>256.14</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="14.45">
+    <row r="24" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B24" s="4">
         <v>46125</v>
       </c>
@@ -4243,7 +4237,7 @@
         <v>27884</v>
       </c>
     </row>
-    <row r="25" spans="2:9" ht="14.45">
+    <row r="25" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B25" s="4">
         <v>46126</v>
       </c>
@@ -4260,7 +4254,7 @@
         <v>707.92</v>
       </c>
     </row>
-    <row r="26" spans="2:9" ht="14.45">
+    <row r="26" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
         <v>46127</v>
       </c>
@@ -4277,7 +4271,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="27" spans="2:9" ht="14.45">
+    <row r="27" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B27" s="4">
         <v>46128</v>
       </c>
@@ -4294,7 +4288,7 @@
         <v>82039</v>
       </c>
     </row>
-    <row r="28" spans="2:9" ht="14.45">
+    <row r="28" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B28" s="4">
         <v>46128</v>
       </c>
@@ -4311,7 +4305,7 @@
         <v>30409</v>
       </c>
     </row>
-    <row r="29" spans="2:9" ht="14.45">
+    <row r="29" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B29" s="4">
         <v>46128</v>
       </c>
@@ -4328,7 +4322,7 @@
         <v>641.91999999999996</v>
       </c>
     </row>
-    <row r="30" spans="2:9" ht="15" customHeight="1">
+    <row r="30" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="4">
         <v>46129</v>
       </c>
@@ -4345,7 +4339,7 @@
         <v>42189</v>
       </c>
     </row>
-    <row r="31" spans="2:9" ht="15" customHeight="1">
+    <row r="31" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
         <v>46129</v>
       </c>
@@ -4359,7 +4353,7 @@
         <v>4300</v>
       </c>
     </row>
-    <row r="32" spans="2:9" ht="15" customHeight="1">
+    <row r="32" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
         <v>46132</v>
       </c>
@@ -4377,7 +4371,7 @@
       </c>
       <c r="G32" s="48"/>
     </row>
-    <row r="33" spans="2:7" ht="15" customHeight="1">
+    <row r="33" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="4">
         <v>46132</v>
       </c>
@@ -4395,7 +4389,7 @@
       </c>
       <c r="G33" s="48"/>
     </row>
-    <row r="34" spans="2:7" ht="15" customHeight="1">
+    <row r="34" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
         <v>46132</v>
       </c>
@@ -4412,7 +4406,7 @@
         <v>8083.68</v>
       </c>
     </row>
-    <row r="35" spans="2:7" ht="15" customHeight="1">
+    <row r="35" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="4">
         <v>46132</v>
       </c>
@@ -4429,7 +4423,7 @@
         <v>1312.2</v>
       </c>
     </row>
-    <row r="36" spans="2:7" ht="15" customHeight="1">
+    <row r="36" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="4">
         <v>46132</v>
       </c>
@@ -4446,7 +4440,7 @@
         <v>678.51</v>
       </c>
     </row>
-    <row r="37" spans="2:7" ht="15" customHeight="1">
+    <row r="37" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="4">
         <v>46132</v>
       </c>
@@ -4463,7 +4457,7 @@
         <v>616.95000000000005</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="15" customHeight="1">
+    <row r="38" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="4">
         <v>46132</v>
       </c>
@@ -4480,7 +4474,7 @@
         <v>553.13</v>
       </c>
     </row>
-    <row r="39" spans="2:7" ht="15" customHeight="1">
+    <row r="39" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="4">
         <v>46132</v>
       </c>
@@ -4498,7 +4492,7 @@
       </c>
       <c r="G39" s="49"/>
     </row>
-    <row r="40" spans="2:7" ht="15" customHeight="1">
+    <row r="40" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="4">
         <v>46132</v>
       </c>
@@ -4515,7 +4509,7 @@
         <v>31934</v>
       </c>
     </row>
-    <row r="41" spans="2:7" ht="15" customHeight="1">
+    <row r="41" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
         <v>46132</v>
       </c>
@@ -4529,7 +4523,7 @@
         <v>4825</v>
       </c>
     </row>
-    <row r="42" spans="2:7" ht="15" customHeight="1">
+    <row r="42" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="4">
         <v>46134</v>
       </c>
@@ -4546,7 +4540,7 @@
         <v>81158.12</v>
       </c>
     </row>
-    <row r="43" spans="2:7" ht="15" customHeight="1">
+    <row r="43" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="4">
         <v>46134</v>
       </c>
@@ -4563,7 +4557,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="44" spans="2:7" ht="15" customHeight="1">
+    <row r="44" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
         <v>46134</v>
       </c>
@@ -4580,7 +4574,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="45" spans="2:7" ht="15" customHeight="1">
+    <row r="45" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="4">
         <v>46134</v>
       </c>
@@ -4594,7 +4588,7 @@
         <v>22000</v>
       </c>
     </row>
-    <row r="46" spans="2:7" ht="15" customHeight="1">
+    <row r="46" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="4">
         <v>46135</v>
       </c>
@@ -4611,7 +4605,7 @@
         <v>4563</v>
       </c>
     </row>
-    <row r="47" spans="2:7" ht="15" customHeight="1">
+    <row r="47" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
         <v>46135</v>
       </c>
@@ -4628,7 +4622,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="48" spans="2:7" ht="15" customHeight="1">
+    <row r="48" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="4">
         <v>46135</v>
       </c>
@@ -4645,7 +4639,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="49" spans="2:6" ht="15" customHeight="1">
+    <row r="49" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="4">
         <v>46136</v>
       </c>
@@ -4662,7 +4656,7 @@
         <v>23554</v>
       </c>
     </row>
-    <row r="50" spans="2:6" ht="15" customHeight="1">
+    <row r="50" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="4">
         <v>46136</v>
       </c>
@@ -4679,21 +4673,21 @@
         <v>16908</v>
       </c>
     </row>
-    <row r="51" spans="2:6" ht="15" customHeight="1">
+    <row r="51" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4">
         <v>46137</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D51" s="65" t="s">
+      <c r="D51" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F51" s="6">
         <v>10000</v>
       </c>
     </row>
-    <row r="52" spans="2:6" ht="15" customHeight="1">
+    <row r="52" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="4">
         <v>46139</v>
       </c>
@@ -4708,52 +4702,52 @@
         <v>250</v>
       </c>
     </row>
-    <row r="53" spans="2:6" ht="15" customHeight="1">
+    <row r="53" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="4">
         <v>46139</v>
       </c>
-      <c r="C53" s="66" t="s">
+      <c r="C53" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="D53" s="65" t="s">
+      <c r="D53" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F53" s="67">
+      <c r="F53" s="66">
         <v>7770</v>
       </c>
     </row>
-    <row r="54" spans="2:6" ht="15" customHeight="1">
+    <row r="54" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="21"/>
       <c r="C54" s="22"/>
       <c r="D54" s="22"/>
       <c r="E54" s="21"/>
       <c r="F54" s="64"/>
     </row>
-    <row r="55" spans="2:6" ht="15" customHeight="1">
+    <row r="55" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="15"/>
       <c r="C55" s="23"/>
       <c r="D55" s="23"/>
       <c r="E55" s="15"/>
       <c r="F55" s="62"/>
     </row>
-    <row r="56" spans="2:6" ht="15" customHeight="1">
+    <row r="56" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="21"/>
       <c r="C56" s="22"/>
       <c r="D56" s="22"/>
       <c r="E56" s="21"/>
       <c r="F56" s="64"/>
     </row>
-    <row r="57" spans="2:6" ht="15" customHeight="1">
+    <row r="57" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="15"/>
       <c r="C57" s="23"/>
       <c r="D57" s="23"/>
       <c r="E57" s="15"/>
       <c r="F57" s="62"/>
     </row>
-    <row r="58" spans="2:6" ht="15" customHeight="1">
+    <row r="58" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="21"/>
       <c r="C58" s="22"/>
       <c r="D58" s="22"/>
@@ -4781,20 +4775,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9163483-898B-48DF-A920-0A4DCD53730D}">
   <dimension ref="B1:H198"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.5703125" style="43" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="2.7109375" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.5546875" style="43" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" customWidth="1"/>
     <col min="8" max="8" width="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="2.7109375" customWidth="1"/>
+    <col min="9" max="9" width="2.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="14.45">
+    <row r="1" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="D1" s="57">
         <f>SUM(E1:F1)</f>
         <v>664406.19999999972</v>
@@ -4808,7 +4802,7 @@
         <v>623306.19999999972</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1">
+    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="69" t="s">
         <v>52</v>
       </c>
@@ -4823,7 +4817,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="14.45">
+    <row r="3" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
@@ -4843,7 +4837,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="14.45">
+    <row r="4" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B4" s="4">
         <v>46113</v>
       </c>
@@ -4860,7 +4854,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="14.45">
+    <row r="5" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B5" s="4">
         <v>46113</v>
       </c>
@@ -4877,7 +4871,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="14.45">
+    <row r="6" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B6" s="4">
         <v>46113</v>
       </c>
@@ -4894,7 +4888,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="14.45">
+    <row r="7" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B7" s="4">
         <v>46113</v>
       </c>
@@ -4911,7 +4905,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="14.45">
+    <row r="8" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B8" s="4">
         <v>46113</v>
       </c>
@@ -4928,7 +4922,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="14.45">
+    <row r="9" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
         <v>46113</v>
       </c>
@@ -4945,7 +4939,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="14.45">
+    <row r="10" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
         <v>46113</v>
       </c>
@@ -4965,7 +4959,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="14.45">
+    <row r="11" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
         <v>46113</v>
       </c>
@@ -4982,7 +4976,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="2:8" ht="14.45">
+    <row r="12" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
         <v>46114</v>
       </c>
@@ -4999,7 +4993,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="14.45">
+    <row r="13" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B13" s="4">
         <v>46114</v>
       </c>
@@ -5016,7 +5010,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="2:8" ht="14.45">
+    <row r="14" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B14" s="4">
         <v>46114</v>
       </c>
@@ -5033,7 +5027,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="14.45">
+    <row r="15" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
         <v>46114</v>
       </c>
@@ -5050,7 +5044,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="14.45">
+    <row r="16" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B16" s="4">
         <v>46114</v>
       </c>
@@ -5067,7 +5061,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="14.45">
+    <row r="17" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B17" s="4">
         <v>46114</v>
       </c>
@@ -5084,7 +5078,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="14.45">
+    <row r="18" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B18" s="4">
         <v>46114</v>
       </c>
@@ -5101,7 +5095,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="14.45">
+    <row r="19" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
         <v>46118</v>
       </c>
@@ -5118,7 +5112,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="14.45">
+    <row r="20" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
         <v>46118</v>
       </c>
@@ -5135,7 +5129,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="14.45">
+    <row r="21" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B21" s="4">
         <v>46118</v>
       </c>
@@ -5152,7 +5146,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="14.45">
+    <row r="22" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B22" s="4">
         <v>46118</v>
       </c>
@@ -5169,7 +5163,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="23" spans="2:8" ht="14.45">
+    <row r="23" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B23" s="4">
         <v>46118</v>
       </c>
@@ -5186,7 +5180,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="14.45">
+    <row r="24" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B24" s="4">
         <v>46118</v>
       </c>
@@ -5203,7 +5197,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="25" spans="2:8" ht="14.45">
+    <row r="25" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B25" s="4">
         <v>46118</v>
       </c>
@@ -5220,7 +5214,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="14.45">
+    <row r="26" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
         <v>46118</v>
       </c>
@@ -5237,7 +5231,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="14.45">
+    <row r="27" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B27" s="4">
         <v>46118</v>
       </c>
@@ -5254,7 +5248,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="14.45">
+    <row r="28" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B28" s="4">
         <v>46118</v>
       </c>
@@ -5271,7 +5265,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="29" spans="2:8" ht="14.45">
+    <row r="29" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B29" s="4">
         <v>46118</v>
       </c>
@@ -5288,7 +5282,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="14.45">
+    <row r="30" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B30" s="4">
         <v>46118</v>
       </c>
@@ -5305,7 +5299,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="2:8" ht="14.45">
+    <row r="31" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
         <v>46118</v>
       </c>
@@ -5322,7 +5316,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="14.45">
+    <row r="32" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
         <v>46118</v>
       </c>
@@ -5339,7 +5333,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="14.45">
+    <row r="33" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B33" s="4">
         <v>46118</v>
       </c>
@@ -5356,7 +5350,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="34" spans="2:8" ht="14.45">
+    <row r="34" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
         <v>46118</v>
       </c>
@@ -5373,7 +5367,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="14.45">
+    <row r="35" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B35" s="4">
         <v>46118</v>
       </c>
@@ -5390,7 +5384,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="14.45">
+    <row r="36" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B36" s="4">
         <v>46119</v>
       </c>
@@ -5407,7 +5401,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="37" spans="2:8" ht="14.45">
+    <row r="37" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B37" s="4">
         <v>46119</v>
       </c>
@@ -5424,7 +5418,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="38" spans="2:8" ht="14.45">
+    <row r="38" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B38" s="4">
         <v>46119</v>
       </c>
@@ -5441,7 +5435,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="39" spans="2:8" ht="14.45">
+    <row r="39" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B39" s="4">
         <v>46119</v>
       </c>
@@ -5458,7 +5452,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="14.45">
+    <row r="40" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B40" s="4">
         <v>46119</v>
       </c>
@@ -5475,7 +5469,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="14.45">
+    <row r="41" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
         <v>46119</v>
       </c>
@@ -5492,7 +5486,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="14.45">
+    <row r="42" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B42" s="4">
         <v>46119</v>
       </c>
@@ -5509,7 +5503,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="43" spans="2:8" ht="14.45">
+    <row r="43" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B43" s="4">
         <v>46119</v>
       </c>
@@ -5529,7 +5523,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="14.45">
+    <row r="44" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
         <v>46119</v>
       </c>
@@ -5546,7 +5540,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="45" spans="2:8" ht="14.45">
+    <row r="45" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B45" s="4">
         <v>46119</v>
       </c>
@@ -5563,7 +5557,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="14.45">
+    <row r="46" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B46" s="4">
         <v>46120</v>
       </c>
@@ -5580,7 +5574,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="47" spans="2:8" ht="14.45">
+    <row r="47" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
         <v>46120</v>
       </c>
@@ -5597,7 +5591,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="48" spans="2:8" ht="14.45">
+    <row r="48" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B48" s="4">
         <v>46120</v>
       </c>
@@ -5614,7 +5608,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="49" spans="2:8" ht="14.45">
+    <row r="49" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B49" s="4">
         <v>46120</v>
       </c>
@@ -5631,7 +5625,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="50" spans="2:8" ht="14.45">
+    <row r="50" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B50" s="4">
         <v>46120</v>
       </c>
@@ -5648,7 +5642,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="51" spans="2:8" ht="14.45">
+    <row r="51" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B51" s="4">
         <v>46120</v>
       </c>
@@ -5665,7 +5659,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="52" spans="2:8" ht="14.45">
+    <row r="52" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B52" s="4">
         <v>46120</v>
       </c>
@@ -5682,7 +5676,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="53" spans="2:8" ht="14.45">
+    <row r="53" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B53" s="4">
         <v>46120</v>
       </c>
@@ -5699,7 +5693,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="54" spans="2:8" ht="14.45">
+    <row r="54" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B54" s="4">
         <v>46120</v>
       </c>
@@ -5716,7 +5710,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="55" spans="2:8" ht="14.45">
+    <row r="55" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B55" s="4">
         <v>46120</v>
       </c>
@@ -5733,7 +5727,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="56" spans="2:8" ht="14.45">
+    <row r="56" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B56" s="4">
         <v>46120</v>
       </c>
@@ -5750,7 +5744,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="57" spans="2:8" ht="14.45">
+    <row r="57" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B57" s="4">
         <v>46120</v>
       </c>
@@ -5767,7 +5761,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="58" spans="2:8" ht="14.45">
+    <row r="58" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B58" s="14">
         <v>46121</v>
       </c>
@@ -5784,7 +5778,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="59" spans="2:8" ht="14.45">
+    <row r="59" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B59" s="14">
         <v>46121</v>
       </c>
@@ -5801,7 +5795,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="60" spans="2:8" ht="14.45">
+    <row r="60" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B60" s="14">
         <v>46121</v>
       </c>
@@ -5818,7 +5812,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="61" spans="2:8" ht="14.45">
+    <row r="61" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B61" s="14">
         <v>46121</v>
       </c>
@@ -5835,7 +5829,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="62" spans="2:8" ht="14.45">
+    <row r="62" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B62" s="14">
         <v>46121</v>
       </c>
@@ -5852,7 +5846,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="63" spans="2:8" ht="14.45">
+    <row r="63" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B63" s="14">
         <v>46121</v>
       </c>
@@ -5869,7 +5863,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="14.45">
+    <row r="64" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B64" s="4">
         <v>46122</v>
       </c>
@@ -5886,7 +5880,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="65" spans="2:8" ht="14.45">
+    <row r="65" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B65" s="4">
         <v>46122</v>
       </c>
@@ -5903,7 +5897,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="66" spans="2:8" ht="14.45">
+    <row r="66" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B66" s="4">
         <v>46122</v>
       </c>
@@ -5920,7 +5914,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="67" spans="2:8" ht="14.45">
+    <row r="67" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B67" s="4">
         <v>46122</v>
       </c>
@@ -5937,7 +5931,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="68" spans="2:8" ht="14.45">
+    <row r="68" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B68" s="4">
         <v>46122</v>
       </c>
@@ -5954,7 +5948,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="69" spans="2:8" ht="14.45">
+    <row r="69" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B69" s="4">
         <v>46122</v>
       </c>
@@ -5971,7 +5965,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="70" spans="2:8" ht="14.45">
+    <row r="70" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B70" s="4">
         <v>46122</v>
       </c>
@@ -5988,7 +5982,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="71" spans="2:8" ht="14.45">
+    <row r="71" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B71" s="4">
         <v>46122</v>
       </c>
@@ -6005,7 +5999,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="72" spans="2:8" ht="14.45">
+    <row r="72" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B72" s="4">
         <v>46122</v>
       </c>
@@ -6022,7 +6016,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="73" spans="2:8" ht="14.45">
+    <row r="73" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B73" s="4">
         <v>46122</v>
       </c>
@@ -6039,7 +6033,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="74" spans="2:8" ht="14.45">
+    <row r="74" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B74" s="4">
         <v>46122</v>
       </c>
@@ -6056,7 +6050,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="75" spans="2:8" ht="14.45">
+    <row r="75" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B75" s="4">
         <v>46122</v>
       </c>
@@ -6073,7 +6067,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="76" spans="2:8" ht="14.45">
+    <row r="76" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B76" s="4">
         <v>46122</v>
       </c>
@@ -6090,7 +6084,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="77" spans="2:8" ht="14.45">
+    <row r="77" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B77" s="4">
         <v>46122</v>
       </c>
@@ -6107,7 +6101,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="78" spans="2:8" ht="14.45">
+    <row r="78" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B78" s="4">
         <v>46125</v>
       </c>
@@ -6124,7 +6118,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="79" spans="2:8" ht="14.45">
+    <row r="79" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B79" s="4">
         <v>46125</v>
       </c>
@@ -6141,7 +6135,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="80" spans="2:8" ht="14.45">
+    <row r="80" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B80" s="4">
         <v>46126</v>
       </c>
@@ -6158,7 +6152,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="81" spans="2:8" ht="14.45">
+    <row r="81" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B81" s="4">
         <v>46126</v>
       </c>
@@ -6175,7 +6169,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="82" spans="2:8" ht="14.45">
+    <row r="82" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B82" s="4">
         <v>46126</v>
       </c>
@@ -6190,7 +6184,7 @@
       </c>
       <c r="H82" s="1"/>
     </row>
-    <row r="83" spans="2:8" ht="14.45">
+    <row r="83" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B83" s="4">
         <v>46126</v>
       </c>
@@ -6205,7 +6199,7 @@
       </c>
       <c r="H83" s="1"/>
     </row>
-    <row r="84" spans="2:8" ht="14.45">
+    <row r="84" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B84" s="4">
         <v>46126</v>
       </c>
@@ -6220,7 +6214,7 @@
       </c>
       <c r="H84" s="1"/>
     </row>
-    <row r="85" spans="2:8" ht="14.45">
+    <row r="85" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B85" s="4">
         <v>46126</v>
       </c>
@@ -6235,7 +6229,7 @@
       </c>
       <c r="H85" s="1"/>
     </row>
-    <row r="86" spans="2:8" ht="14.45">
+    <row r="86" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B86" s="4">
         <v>46126</v>
       </c>
@@ -6250,7 +6244,7 @@
       </c>
       <c r="H86" s="1"/>
     </row>
-    <row r="87" spans="2:8" ht="14.45">
+    <row r="87" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B87" s="4">
         <v>46126</v>
       </c>
@@ -6265,7 +6259,7 @@
       </c>
       <c r="H87" s="1"/>
     </row>
-    <row r="88" spans="2:8" ht="14.45">
+    <row r="88" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B88" s="4">
         <v>46126</v>
       </c>
@@ -6280,7 +6274,7 @@
       </c>
       <c r="H88" s="1"/>
     </row>
-    <row r="89" spans="2:8" ht="14.45">
+    <row r="89" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B89" s="4">
         <v>46126</v>
       </c>
@@ -6294,7 +6288,7 @@
         <v>3030.85</v>
       </c>
     </row>
-    <row r="90" spans="2:8" ht="14.45">
+    <row r="90" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B90" s="4">
         <v>46126</v>
       </c>
@@ -6308,7 +6302,7 @@
         <v>2445.6999999999998</v>
       </c>
     </row>
-    <row r="91" spans="2:8" ht="14.45">
+    <row r="91" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B91" s="4">
         <v>46126</v>
       </c>
@@ -6322,7 +6316,7 @@
         <v>1260.79</v>
       </c>
     </row>
-    <row r="92" spans="2:8" ht="14.45">
+    <row r="92" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B92" s="4">
         <v>46126</v>
       </c>
@@ -6336,7 +6330,7 @@
         <v>2504.25</v>
       </c>
     </row>
-    <row r="93" spans="2:8" ht="14.45">
+    <row r="93" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B93" s="4">
         <v>46126</v>
       </c>
@@ -6350,7 +6344,7 @@
         <v>4470</v>
       </c>
     </row>
-    <row r="94" spans="2:8" ht="14.45">
+    <row r="94" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B94" s="4">
         <v>46126</v>
       </c>
@@ -6364,7 +6358,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="95" spans="2:8" ht="14.45">
+    <row r="95" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B95" s="4">
         <v>46126</v>
       </c>
@@ -6378,7 +6372,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="96" spans="2:8" ht="14.45">
+    <row r="96" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B96" s="4">
         <v>46126</v>
       </c>
@@ -6392,7 +6386,7 @@
         <v>145.99</v>
       </c>
     </row>
-    <row r="97" spans="2:6" ht="14.45">
+    <row r="97" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B97" s="4">
         <v>46126</v>
       </c>
@@ -6406,7 +6400,7 @@
         <v>621.67999999999995</v>
       </c>
     </row>
-    <row r="98" spans="2:6" ht="14.45">
+    <row r="98" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B98" s="4">
         <v>46127</v>
       </c>
@@ -6420,7 +6414,7 @@
         <v>222.23</v>
       </c>
     </row>
-    <row r="99" spans="2:6" ht="14.45">
+    <row r="99" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B99" s="4">
         <v>46127</v>
       </c>
@@ -6434,7 +6428,7 @@
         <v>1320.66</v>
       </c>
     </row>
-    <row r="100" spans="2:6" ht="14.45">
+    <row r="100" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B100" s="4">
         <v>46127</v>
       </c>
@@ -6448,7 +6442,7 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="14.45">
+    <row r="101" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B101" s="4">
         <v>46127</v>
       </c>
@@ -6462,7 +6456,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="102" spans="2:6" ht="14.45">
+    <row r="102" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B102" s="4">
         <v>46128</v>
       </c>
@@ -6476,7 +6470,7 @@
         <v>3806.08</v>
       </c>
     </row>
-    <row r="103" spans="2:6" ht="14.45">
+    <row r="103" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B103" s="4">
         <v>46128</v>
       </c>
@@ -6490,7 +6484,7 @@
         <v>2454.98</v>
       </c>
     </row>
-    <row r="104" spans="2:6" ht="14.45">
+    <row r="104" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B104" s="4">
         <v>46128</v>
       </c>
@@ -6504,7 +6498,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="105" spans="2:6" ht="14.45">
+    <row r="105" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B105" s="4">
         <v>46128</v>
       </c>
@@ -6518,7 +6512,7 @@
         <v>2809.99</v>
       </c>
     </row>
-    <row r="106" spans="2:6" ht="14.45">
+    <row r="106" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B106" s="4">
         <v>46128</v>
       </c>
@@ -6532,7 +6526,7 @@
         <v>152.93</v>
       </c>
     </row>
-    <row r="107" spans="2:6" ht="14.45">
+    <row r="107" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B107" s="4">
         <v>46128</v>
       </c>
@@ -6546,7 +6540,7 @@
         <v>3664.04</v>
       </c>
     </row>
-    <row r="108" spans="2:6" ht="14.45">
+    <row r="108" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B108" s="4">
         <v>46128</v>
       </c>
@@ -6560,7 +6554,7 @@
         <v>896.61</v>
       </c>
     </row>
-    <row r="109" spans="2:6" ht="14.45">
+    <row r="109" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B109" s="4">
         <v>46128</v>
       </c>
@@ -6574,7 +6568,7 @@
         <v>536.58000000000004</v>
       </c>
     </row>
-    <row r="110" spans="2:6" ht="14.45">
+    <row r="110" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B110" s="4">
         <v>46128</v>
       </c>
@@ -6588,7 +6582,7 @@
         <v>4498.9399999999996</v>
       </c>
     </row>
-    <row r="111" spans="2:6" ht="14.45">
+    <row r="111" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B111" s="4">
         <v>46128</v>
       </c>
@@ -6602,7 +6596,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="112" spans="2:6" ht="14.45">
+    <row r="112" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B112" s="4">
         <v>46128</v>
       </c>
@@ -6616,7 +6610,7 @@
         <v>91.17</v>
       </c>
     </row>
-    <row r="113" spans="2:6" ht="14.45">
+    <row r="113" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B113" s="4">
         <v>46128</v>
       </c>
@@ -6630,7 +6624,7 @@
         <v>13953.27</v>
       </c>
     </row>
-    <row r="114" spans="2:6" ht="14.45">
+    <row r="114" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B114" s="4">
         <v>46128</v>
       </c>
@@ -6644,7 +6638,7 @@
         <v>130.5</v>
       </c>
     </row>
-    <row r="115" spans="2:6" ht="14.45">
+    <row r="115" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B115" s="4">
         <v>46128</v>
       </c>
@@ -6658,7 +6652,7 @@
         <v>5916.4</v>
       </c>
     </row>
-    <row r="116" spans="2:6" ht="14.45">
+    <row r="116" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B116" s="4">
         <v>46128</v>
       </c>
@@ -6672,7 +6666,7 @@
         <v>13391.92</v>
       </c>
     </row>
-    <row r="117" spans="2:6" ht="14.45">
+    <row r="117" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B117" s="4">
         <v>46128</v>
       </c>
@@ -6686,7 +6680,7 @@
         <v>826.63</v>
       </c>
     </row>
-    <row r="118" spans="2:6" ht="14.45">
+    <row r="118" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B118" s="4">
         <v>46128</v>
       </c>
@@ -6700,7 +6694,7 @@
         <v>91.8</v>
       </c>
     </row>
-    <row r="119" spans="2:6" ht="14.45">
+    <row r="119" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B119" s="4">
         <v>46128</v>
       </c>
@@ -6714,7 +6708,7 @@
         <v>359.29</v>
       </c>
     </row>
-    <row r="120" spans="2:6" ht="14.45">
+    <row r="120" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B120" s="4">
         <v>46128</v>
       </c>
@@ -6728,7 +6722,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="121" spans="2:6" ht="14.45">
+    <row r="121" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B121" s="4">
         <v>46129</v>
       </c>
@@ -6745,7 +6739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="2:6" ht="15" customHeight="1">
+    <row r="122" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B122" s="4">
         <v>46129</v>
       </c>
@@ -6759,7 +6753,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="123" spans="2:6" ht="15" customHeight="1">
+    <row r="123" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B123" s="4">
         <v>46129</v>
       </c>
@@ -6773,7 +6767,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="124" spans="2:6" ht="15" customHeight="1">
+    <row r="124" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B124" s="4">
         <v>46129</v>
       </c>
@@ -6787,7 +6781,7 @@
         <v>92.14</v>
       </c>
     </row>
-    <row r="125" spans="2:6" ht="15" customHeight="1">
+    <row r="125" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B125" s="4">
         <v>46129</v>
       </c>
@@ -6801,7 +6795,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="126" spans="2:6" ht="15" customHeight="1">
+    <row r="126" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B126" s="4">
         <v>46129</v>
       </c>
@@ -6815,7 +6809,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="127" spans="2:6" ht="15" customHeight="1">
+    <row r="127" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B127" s="4">
         <v>46129</v>
       </c>
@@ -6829,7 +6823,7 @@
         <v>106.66</v>
       </c>
     </row>
-    <row r="128" spans="2:6" ht="15" customHeight="1">
+    <row r="128" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B128" s="4">
         <v>46129</v>
       </c>
@@ -6843,7 +6837,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="129" spans="2:6" ht="15" customHeight="1">
+    <row r="129" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B129" s="4">
         <v>46129</v>
       </c>
@@ -6857,7 +6851,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="130" spans="2:6" ht="15" customHeight="1">
+    <row r="130" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B130" s="4">
         <v>46132</v>
       </c>
@@ -6874,7 +6868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="2:6" ht="15" customHeight="1">
+    <row r="131" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B131" s="4">
         <v>46132</v>
       </c>
@@ -6888,7 +6882,7 @@
         <v>434.3</v>
       </c>
     </row>
-    <row r="132" spans="2:6" ht="15" customHeight="1">
+    <row r="132" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B132" s="4">
         <v>46132</v>
       </c>
@@ -6903,7 +6897,7 @@
         <v>8227.7099999999991</v>
       </c>
     </row>
-    <row r="133" spans="2:6" ht="15" customHeight="1">
+    <row r="133" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B133" s="4">
         <v>46132</v>
       </c>
@@ -6917,7 +6911,7 @@
         <v>12428.85</v>
       </c>
     </row>
-    <row r="134" spans="2:6" ht="15" customHeight="1">
+    <row r="134" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B134" s="4">
         <v>46132</v>
       </c>
@@ -6932,7 +6926,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="135" spans="2:6" ht="15" customHeight="1">
+    <row r="135" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B135" s="4">
         <v>46132</v>
       </c>
@@ -6946,7 +6940,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="136" spans="2:6" ht="15" customHeight="1">
+    <row r="136" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B136" s="4">
         <v>46132</v>
       </c>
@@ -6961,7 +6955,7 @@
         <v>2689.59</v>
       </c>
     </row>
-    <row r="137" spans="2:6" ht="15" customHeight="1">
+    <row r="137" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B137" s="4">
         <v>46132</v>
       </c>
@@ -6975,7 +6969,7 @@
         <v>588.07000000000005</v>
       </c>
     </row>
-    <row r="138" spans="2:6" ht="15" customHeight="1">
+    <row r="138" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B138" s="4">
         <v>46132</v>
       </c>
@@ -6990,7 +6984,7 @@
         <v>915.59</v>
       </c>
     </row>
-    <row r="139" spans="2:6" ht="15" customHeight="1">
+    <row r="139" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B139" s="4">
         <v>46132</v>
       </c>
@@ -7004,7 +6998,7 @@
         <v>9757.1299999999992</v>
       </c>
     </row>
-    <row r="140" spans="2:6" ht="15" customHeight="1">
+    <row r="140" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B140" s="4">
         <v>46132</v>
       </c>
@@ -7019,7 +7013,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="141" spans="2:6" ht="15" customHeight="1">
+    <row r="141" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B141" s="4">
         <v>46132</v>
       </c>
@@ -7033,7 +7027,7 @@
         <v>97.34</v>
       </c>
     </row>
-    <row r="142" spans="2:6" ht="15" customHeight="1">
+    <row r="142" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B142" s="4">
         <v>46132</v>
       </c>
@@ -7048,7 +7042,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="143" spans="2:6" ht="15" customHeight="1">
+    <row r="143" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B143" s="4">
         <v>46132</v>
       </c>
@@ -7062,7 +7056,7 @@
         <v>1359.21</v>
       </c>
     </row>
-    <row r="144" spans="2:6" ht="15" customHeight="1">
+    <row r="144" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B144" s="4">
         <v>46132</v>
       </c>
@@ -7077,7 +7071,7 @@
         <v>7349.56</v>
       </c>
     </row>
-    <row r="145" spans="2:6" ht="15" customHeight="1">
+    <row r="145" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B145" s="4">
         <v>46132</v>
       </c>
@@ -7092,7 +7086,7 @@
         <v>3994</v>
       </c>
     </row>
-    <row r="146" spans="2:6" ht="15" customHeight="1">
+    <row r="146" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B146" s="4">
         <v>46132</v>
       </c>
@@ -7106,7 +7100,7 @@
         <v>6114.45</v>
       </c>
     </row>
-    <row r="147" spans="2:6" ht="15" customHeight="1">
+    <row r="147" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B147" s="4">
         <v>46132</v>
       </c>
@@ -7121,7 +7115,7 @@
         <v>534.5</v>
       </c>
     </row>
-    <row r="148" spans="2:6" ht="15" customHeight="1">
+    <row r="148" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B148" s="4">
         <v>46132</v>
       </c>
@@ -7136,7 +7130,7 @@
         <v>470.46</v>
       </c>
     </row>
-    <row r="149" spans="2:6" ht="15" customHeight="1">
+    <row r="149" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B149" s="4">
         <v>46132</v>
       </c>
@@ -7150,7 +7144,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="150" spans="2:6" ht="15" customHeight="1">
+    <row r="150" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B150" s="4">
         <v>46132</v>
       </c>
@@ -7165,7 +7159,7 @@
         <v>5906.64</v>
       </c>
     </row>
-    <row r="151" spans="2:6" ht="15" customHeight="1">
+    <row r="151" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B151" s="4">
         <v>46132</v>
       </c>
@@ -7180,7 +7174,7 @@
         <v>311.5</v>
       </c>
     </row>
-    <row r="152" spans="2:6" ht="15" customHeight="1">
+    <row r="152" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B152" s="4">
         <v>46132</v>
       </c>
@@ -7194,7 +7188,7 @@
         <v>1998.45</v>
       </c>
     </row>
-    <row r="153" spans="2:6" ht="15" customHeight="1">
+    <row r="153" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B153" s="4">
         <v>46132</v>
       </c>
@@ -7209,7 +7203,7 @@
         <v>2067.37</v>
       </c>
     </row>
-    <row r="154" spans="2:6" ht="15" customHeight="1">
+    <row r="154" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B154" s="4">
         <v>46134</v>
       </c>
@@ -7224,7 +7218,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="155" spans="2:6" ht="15" customHeight="1">
+    <row r="155" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B155" s="4">
         <v>46134</v>
       </c>
@@ -7238,7 +7232,7 @@
         <v>5115</v>
       </c>
     </row>
-    <row r="156" spans="2:6" ht="15" customHeight="1">
+    <row r="156" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B156" s="4">
         <v>46134</v>
       </c>
@@ -7253,7 +7247,7 @@
         <v>82.4</v>
       </c>
     </row>
-    <row r="157" spans="2:6" ht="15" customHeight="1">
+    <row r="157" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B157" s="4">
         <v>46134</v>
       </c>
@@ -7267,7 +7261,7 @@
         <v>2092</v>
       </c>
     </row>
-    <row r="158" spans="2:6" ht="15" customHeight="1">
+    <row r="158" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B158" s="4">
         <v>46134</v>
       </c>
@@ -7282,7 +7276,7 @@
         <v>2504.25</v>
       </c>
     </row>
-    <row r="159" spans="2:6" ht="15" customHeight="1">
+    <row r="159" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B159" s="4">
         <v>46134</v>
       </c>
@@ -7296,7 +7290,7 @@
         <v>3138.13</v>
       </c>
     </row>
-    <row r="160" spans="2:6" ht="15" customHeight="1">
+    <row r="160" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B160" s="4">
         <v>46134</v>
       </c>
@@ -7311,7 +7305,7 @@
         <v>6844.44</v>
       </c>
     </row>
-    <row r="161" spans="2:6" ht="15" customHeight="1">
+    <row r="161" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B161" s="4">
         <v>46134</v>
       </c>
@@ -7325,7 +7319,7 @@
         <v>11034.3</v>
       </c>
     </row>
-    <row r="162" spans="2:6" ht="15" customHeight="1">
+    <row r="162" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B162" s="4">
         <v>46134</v>
       </c>
@@ -7340,7 +7334,7 @@
         <v>45048</v>
       </c>
     </row>
-    <row r="163" spans="2:6" ht="15" customHeight="1">
+    <row r="163" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B163" s="4">
         <v>46134</v>
       </c>
@@ -7354,7 +7348,7 @@
         <v>30119.64</v>
       </c>
     </row>
-    <row r="164" spans="2:6" ht="15" customHeight="1">
+    <row r="164" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B164" s="4">
         <v>46134</v>
       </c>
@@ -7369,7 +7363,7 @@
         <v>2900</v>
       </c>
     </row>
-    <row r="165" spans="2:6" ht="15" customHeight="1">
+    <row r="165" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B165" s="4">
         <v>46134</v>
       </c>
@@ -7383,7 +7377,7 @@
         <v>899.5</v>
       </c>
     </row>
-    <row r="166" spans="2:6" ht="15" customHeight="1">
+    <row r="166" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B166" s="4">
         <v>46134</v>
       </c>
@@ -7398,7 +7392,7 @@
         <v>2278.8000000000002</v>
       </c>
     </row>
-    <row r="167" spans="2:6" ht="15" customHeight="1">
+    <row r="167" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B167" s="4">
         <v>46134</v>
       </c>
@@ -7412,7 +7406,7 @@
         <v>382.96</v>
       </c>
     </row>
-    <row r="168" spans="2:6" ht="15" customHeight="1">
+    <row r="168" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B168" s="4">
         <v>46135</v>
       </c>
@@ -7427,7 +7421,7 @@
         <v>2340</v>
       </c>
     </row>
-    <row r="169" spans="2:6" ht="15" customHeight="1">
+    <row r="169" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B169" s="4">
         <v>46135</v>
       </c>
@@ -7441,7 +7435,7 @@
         <v>83.72</v>
       </c>
     </row>
-    <row r="170" spans="2:6" ht="15" customHeight="1">
+    <row r="170" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B170" s="4">
         <v>46135</v>
       </c>
@@ -7456,7 +7450,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="171" spans="2:6" ht="15" customHeight="1">
+    <row r="171" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B171" s="4">
         <v>46135</v>
       </c>
@@ -7470,7 +7464,7 @@
         <v>2393.71</v>
       </c>
     </row>
-    <row r="172" spans="2:6" ht="15" customHeight="1">
+    <row r="172" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B172" s="4">
         <v>46135</v>
       </c>
@@ -7485,7 +7479,7 @@
         <v>2959.84</v>
       </c>
     </row>
-    <row r="173" spans="2:6" ht="15" customHeight="1">
+    <row r="173" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B173" s="4">
         <v>46135</v>
       </c>
@@ -7499,7 +7493,7 @@
         <v>8680.48</v>
       </c>
     </row>
-    <row r="174" spans="2:6" ht="15" customHeight="1">
+    <row r="174" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B174" s="4">
         <v>46135</v>
       </c>
@@ -7514,7 +7508,7 @@
         <v>15970.84</v>
       </c>
     </row>
-    <row r="175" spans="2:6" ht="15" customHeight="1">
+    <row r="175" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B175" s="4">
         <v>46135</v>
       </c>
@@ -7528,7 +7522,7 @@
         <v>104.52</v>
       </c>
     </row>
-    <row r="176" spans="2:6" ht="15" customHeight="1">
+    <row r="176" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B176" s="4">
         <v>46135</v>
       </c>
@@ -7543,7 +7537,7 @@
         <v>37.25</v>
       </c>
     </row>
-    <row r="177" spans="2:6" ht="15" customHeight="1">
+    <row r="177" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B177" s="4">
         <v>46136</v>
       </c>
@@ -7557,7 +7551,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="178" spans="2:6" ht="15" customHeight="1">
+    <row r="178" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B178" s="4">
         <v>46136</v>
       </c>
@@ -7572,7 +7566,7 @@
         <v>1914</v>
       </c>
     </row>
-    <row r="179" spans="2:6" ht="15" customHeight="1">
+    <row r="179" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B179" s="4">
         <v>46136</v>
       </c>
@@ -7586,7 +7580,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="180" spans="2:6" ht="15" customHeight="1">
+    <row r="180" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B180" s="4">
         <v>46136</v>
       </c>
@@ -7601,7 +7595,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="181" spans="2:6" ht="15" customHeight="1">
+    <row r="181" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B181" s="4">
         <v>46136</v>
       </c>
@@ -7611,12 +7605,12 @@
       <c r="D181" s="43" t="s">
         <v>168</v>
       </c>
-      <c r="E181" s="68"/>
+      <c r="E181" s="53"/>
       <c r="F181" s="6">
         <v>1019.45</v>
       </c>
     </row>
-    <row r="182" spans="2:6" ht="15" customHeight="1">
+    <row r="182" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B182" s="4">
         <v>46136</v>
       </c>
@@ -7626,12 +7620,12 @@
       <c r="D182" s="43" t="s">
         <v>210</v>
       </c>
-      <c r="E182" s="68"/>
+      <c r="E182" s="53"/>
       <c r="F182" s="6">
         <v>4000</v>
       </c>
     </row>
-    <row r="183" spans="2:6" ht="15" customHeight="1">
+    <row r="183" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B183" s="4">
         <v>46136</v>
       </c>
@@ -7641,12 +7635,12 @@
       <c r="D183" s="43" t="s">
         <v>205</v>
       </c>
-      <c r="E183" s="68"/>
+      <c r="E183" s="53"/>
       <c r="F183" s="6">
         <v>126.87</v>
       </c>
     </row>
-    <row r="184" spans="2:6" ht="15" customHeight="1">
+    <row r="184" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B184" s="4">
         <v>46136</v>
       </c>
@@ -7656,12 +7650,12 @@
       <c r="D184" s="43" t="s">
         <v>171</v>
       </c>
-      <c r="E184" s="68"/>
+      <c r="E184" s="53"/>
       <c r="F184" s="6">
         <v>145.99</v>
       </c>
     </row>
-    <row r="185" spans="2:6" ht="15" customHeight="1">
+    <row r="185" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B185" s="4">
         <v>46136</v>
       </c>
@@ -7671,12 +7665,12 @@
       <c r="D185" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="E185" s="68"/>
+      <c r="E185" s="53"/>
       <c r="F185" s="6">
         <v>458.33</v>
       </c>
     </row>
-    <row r="186" spans="2:6" ht="15" customHeight="1">
+    <row r="186" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B186" s="4">
         <v>46136</v>
       </c>
@@ -7686,12 +7680,12 @@
       <c r="D186" s="43" t="s">
         <v>213</v>
       </c>
-      <c r="E186" s="68"/>
+      <c r="E186" s="53"/>
       <c r="F186" s="6">
         <v>8982.7099999999991</v>
       </c>
     </row>
-    <row r="187" spans="2:6" ht="15" customHeight="1">
+    <row r="187" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B187" s="4">
         <v>46136</v>
       </c>
@@ -7701,12 +7695,12 @@
       <c r="D187" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="E187" s="68"/>
+      <c r="E187" s="53"/>
       <c r="F187" s="6">
         <v>438.72</v>
       </c>
     </row>
-    <row r="188" spans="2:6" ht="15" customHeight="1">
+    <row r="188" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B188" s="4">
         <v>46136</v>
       </c>
@@ -7716,12 +7710,12 @@
       <c r="D188" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="E188" s="68"/>
+      <c r="E188" s="53"/>
       <c r="F188" s="6">
         <v>826.34</v>
       </c>
     </row>
-    <row r="189" spans="2:6" ht="15" customHeight="1">
+    <row r="189" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B189" s="4">
         <v>46136</v>
       </c>
@@ -7731,12 +7725,12 @@
       <c r="D189" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="E189" s="68"/>
+      <c r="E189" s="53"/>
       <c r="F189" s="6">
         <v>2278.8000000000002</v>
       </c>
     </row>
-    <row r="190" spans="2:6" ht="15" customHeight="1">
+    <row r="190" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B190" s="4">
         <v>46136</v>
       </c>
@@ -7746,12 +7740,12 @@
       <c r="D190" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="E190" s="68"/>
+      <c r="E190" s="53"/>
       <c r="F190" s="6">
         <v>8219</v>
       </c>
     </row>
-    <row r="191" spans="2:6" ht="15" customHeight="1">
+    <row r="191" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B191" s="4">
         <v>46136</v>
       </c>
@@ -7761,12 +7755,12 @@
       <c r="D191" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="E191" s="68"/>
+      <c r="E191" s="53"/>
       <c r="F191" s="6">
         <v>1700</v>
       </c>
     </row>
-    <row r="192" spans="2:6" ht="15" customHeight="1">
+    <row r="192" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B192" s="4">
         <v>46136</v>
       </c>
@@ -7776,12 +7770,12 @@
       <c r="D192" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="E192" s="68"/>
+      <c r="E192" s="53"/>
       <c r="F192" s="6">
         <v>115.6</v>
       </c>
     </row>
-    <row r="193" spans="2:6" ht="15" customHeight="1">
+    <row r="193" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B193" s="4">
         <v>46136</v>
       </c>
@@ -7791,12 +7785,12 @@
       <c r="D193" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="E193" s="68"/>
+      <c r="E193" s="53"/>
       <c r="F193" s="6">
         <v>258.01</v>
       </c>
     </row>
-    <row r="194" spans="2:6" ht="15" customHeight="1">
+    <row r="194" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B194" s="4">
         <v>46136</v>
       </c>
@@ -7806,12 +7800,12 @@
       <c r="D194" s="43" t="s">
         <v>215</v>
       </c>
-      <c r="E194" s="68"/>
+      <c r="E194" s="53"/>
       <c r="F194" s="6">
         <v>1244.3</v>
       </c>
     </row>
-    <row r="195" spans="2:6" ht="15" customHeight="1">
+    <row r="195" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B195" s="4">
         <v>46136</v>
       </c>
@@ -7821,31 +7815,31 @@
       <c r="D195" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="E195" s="68"/>
+      <c r="E195" s="53"/>
       <c r="F195" s="6">
         <v>3941.28</v>
       </c>
     </row>
-    <row r="196" spans="2:6" ht="15" customHeight="1">
+    <row r="196" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B196" s="4">
         <v>46136</v>
       </c>
       <c r="D196" s="43"/>
-      <c r="E196" s="68"/>
-    </row>
-    <row r="197" spans="2:6" ht="15" customHeight="1">
+      <c r="E196" s="53"/>
+    </row>
+    <row r="197" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B197" s="4">
         <v>46136</v>
       </c>
       <c r="D197" s="43"/>
-      <c r="E197" s="68"/>
-    </row>
-    <row r="198" spans="2:6" ht="15" customHeight="1">
+      <c r="E197" s="53"/>
+    </row>
+    <row r="198" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B198" s="4">
         <v>46136</v>
       </c>
       <c r="D198" s="43"/>
-      <c r="E198" s="68"/>
+      <c r="E198" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7868,18 +7862,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{563D29B1-1023-471C-B57D-0AD257F1C41C}">
   <dimension ref="B1:F121"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="14.45"/>
-    <row r="2" spans="2:6" ht="15" customHeight="1">
+    <row r="1" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="73" t="s">
         <v>216</v>
       </c>
@@ -7888,7 +7882,7 @@
       <c r="E2" s="74"/>
       <c r="F2" s="74"/>
     </row>
-    <row r="3" spans="2:6" ht="14.45">
+    <row r="3" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B3" s="18" t="s">
         <v>23</v>
       </c>
@@ -7905,7 +7899,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="4" spans="2:6" ht="14.45">
+    <row r="4" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B4" s="19">
         <v>46116</v>
       </c>
@@ -7922,7 +7916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="14.45">
+    <row r="5" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B5" s="16">
         <v>46121</v>
       </c>
@@ -7939,7 +7933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="14.45">
+    <row r="6" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B6" s="19">
         <v>46123</v>
       </c>
@@ -7956,7 +7950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="14.45">
+    <row r="7" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B7" s="16">
         <v>46125</v>
       </c>
@@ -7973,7 +7967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="14.45">
+    <row r="8" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B8" s="29">
         <v>46133</v>
       </c>
@@ -7990,7 +7984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="14.45">
+    <row r="9" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B9" s="26">
         <v>46135</v>
       </c>
@@ -8007,7 +8001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="14.45">
+    <row r="10" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B10" s="31">
         <v>46137</v>
       </c>
@@ -8024,7 +8018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="14.45">
+    <row r="11" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B11" s="26">
         <v>46140</v>
       </c>
@@ -8041,7 +8035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="14.45">
+    <row r="12" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B12" s="39">
         <v>46140</v>
       </c>
@@ -8058,7 +8052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="14.45">
+    <row r="13" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B13" s="33">
         <v>46146</v>
       </c>
@@ -8075,7 +8069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="14.45">
+    <row r="14" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B14" s="36">
         <v>46153</v>
       </c>
@@ -8089,10 +8083,10 @@
         <v>219</v>
       </c>
       <c r="F14" s="44" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6" ht="14.45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B15" s="33">
         <v>46163</v>
       </c>
@@ -8106,10 +8100,10 @@
         <v>219</v>
       </c>
       <c r="F15" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" ht="14.45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B16" s="36">
         <v>46167</v>
       </c>
@@ -8123,10 +8117,10 @@
         <v>221</v>
       </c>
       <c r="F16" s="44" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" ht="14.45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B17" s="33">
         <v>46184</v>
       </c>
@@ -8140,10 +8134,10 @@
         <v>219</v>
       </c>
       <c r="F17" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" ht="14.45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B18" s="36">
         <v>46198</v>
       </c>
@@ -8157,112 +8151,112 @@
         <v>221</v>
       </c>
       <c r="F18" s="44" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" ht="14.45"/>
-    <row r="20" spans="2:6" ht="14.45"/>
-    <row r="21" spans="2:6" ht="14.45"/>
-    <row r="22" spans="2:6" ht="14.45"/>
-    <row r="23" spans="2:6" ht="14.45"/>
-    <row r="24" spans="2:6" ht="14.45"/>
-    <row r="25" spans="2:6" ht="14.45"/>
-    <row r="26" spans="2:6" ht="14.45"/>
-    <row r="27" spans="2:6" ht="14.45"/>
-    <row r="28" spans="2:6" ht="14.45"/>
-    <row r="29" spans="2:6" ht="14.45"/>
-    <row r="30" spans="2:6" ht="14.45"/>
-    <row r="31" spans="2:6" ht="14.45"/>
-    <row r="32" spans="2:6" ht="14.45"/>
-    <row r="33" ht="14.45"/>
-    <row r="34" ht="14.45"/>
-    <row r="35" ht="14.45"/>
-    <row r="36" ht="14.45"/>
-    <row r="37" ht="14.45"/>
-    <row r="38" ht="14.45"/>
-    <row r="39" ht="14.45"/>
-    <row r="40" ht="14.45"/>
-    <row r="41" ht="14.45"/>
-    <row r="42" ht="14.45"/>
-    <row r="43" ht="14.45"/>
-    <row r="44" ht="14.45"/>
-    <row r="45" ht="14.45"/>
-    <row r="46" ht="14.45"/>
-    <row r="47" ht="14.45"/>
-    <row r="48" ht="14.45"/>
-    <row r="49" ht="14.45"/>
-    <row r="50" ht="14.45"/>
-    <row r="51" ht="14.45"/>
-    <row r="52" ht="14.45"/>
-    <row r="53" ht="14.45"/>
-    <row r="54" ht="14.45"/>
-    <row r="55" ht="14.45"/>
-    <row r="56" ht="14.45"/>
-    <row r="57" ht="14.45"/>
-    <row r="58" ht="14.45"/>
-    <row r="59" ht="14.45"/>
-    <row r="60" ht="14.45"/>
-    <row r="61" ht="14.45"/>
-    <row r="62" ht="14.45"/>
-    <row r="63" ht="14.45"/>
-    <row r="64" ht="14.45"/>
-    <row r="65" ht="14.45"/>
-    <row r="66" ht="14.45"/>
-    <row r="67" ht="14.45"/>
-    <row r="68" ht="14.45"/>
-    <row r="69" ht="14.45"/>
-    <row r="70" ht="14.45"/>
-    <row r="71" ht="14.45"/>
-    <row r="72" ht="14.45"/>
-    <row r="73" ht="14.45"/>
-    <row r="74" ht="14.45"/>
-    <row r="75" ht="14.45"/>
-    <row r="76" ht="14.45"/>
-    <row r="77" ht="14.45"/>
-    <row r="78" ht="14.45"/>
-    <row r="79" ht="14.45"/>
-    <row r="80" ht="14.45"/>
-    <row r="81" ht="14.45"/>
-    <row r="82" ht="14.45"/>
-    <row r="83" ht="14.45"/>
-    <row r="84" ht="14.45"/>
-    <row r="85" ht="14.45"/>
-    <row r="86" ht="14.45"/>
-    <row r="87" ht="14.45"/>
-    <row r="88" ht="14.45"/>
-    <row r="89" ht="14.45"/>
-    <row r="90" ht="14.45"/>
-    <row r="91" ht="14.45"/>
-    <row r="92" ht="14.45"/>
-    <row r="93" ht="14.45"/>
-    <row r="94" ht="14.45"/>
-    <row r="95" ht="14.45"/>
-    <row r="96" ht="14.45"/>
-    <row r="97" ht="14.45"/>
-    <row r="98" ht="14.45"/>
-    <row r="99" ht="14.45"/>
-    <row r="100" ht="14.45"/>
-    <row r="101" ht="14.45"/>
-    <row r="102" ht="14.45"/>
-    <row r="103" ht="14.45"/>
-    <row r="104" ht="14.45"/>
-    <row r="105" ht="14.45"/>
-    <row r="106" ht="14.45"/>
-    <row r="107" ht="14.45"/>
-    <row r="108" ht="14.45"/>
-    <row r="109" ht="14.45"/>
-    <row r="110" ht="14.45"/>
-    <row r="111" ht="14.45"/>
-    <row r="112" ht="14.45"/>
-    <row r="113" ht="14.45"/>
-    <row r="114" ht="14.45"/>
-    <row r="115" ht="14.45"/>
-    <row r="116" ht="14.45"/>
-    <row r="117" ht="14.45"/>
-    <row r="118" ht="14.45"/>
-    <row r="119" ht="14.45"/>
-    <row r="120" ht="14.45"/>
-    <row r="121" ht="14.45"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="34" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="35" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="36" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="38" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="39" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="40" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="41" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="42" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="43" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="44" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="45" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="46" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="47" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="48" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="49" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="50" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="51" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="52" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="53" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="54" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="55" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="56" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="57" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="58" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="59" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="60" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="61" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="62" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="63" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="64" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="65" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="66" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="67" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="68" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="69" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="70" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="71" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="72" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="73" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="74" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="75" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="76" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="77" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="78" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="79" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="80" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="81" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="82" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="83" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="84" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="85" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="86" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="87" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="88" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="89" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="90" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="91" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="92" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="93" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="94" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="95" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="96" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="97" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="98" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="99" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="100" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="101" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="102" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="103" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="104" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="105" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="106" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="107" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="108" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="109" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="110" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="111" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="112" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="113" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="114" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="115" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="116" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="117" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="118" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="119" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="120" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="121" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:F2"/>
@@ -8275,23 +8269,23 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E746537A-A23A-41AB-9161-94E002D525F0}">
   <dimension ref="B1:G45"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="2.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="2.6640625" customWidth="1"/>
     <col min="7" max="7" width="31" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7">
+    <row r="1" spans="2:7" x14ac:dyDescent="0.3">
       <c r="E1" s="12">
         <f>SUM(Tabela1356[(R$) Valor])</f>
         <v>670865.03999999992</v>
       </c>
     </row>
-    <row r="2" spans="2:7">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B2" s="69" t="s">
         <v>222</v>
       </c>
@@ -8302,7 +8296,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="2:7">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
@@ -8319,7 +8313,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="2:7">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" s="4">
         <v>46113</v>
       </c>
@@ -8336,7 +8330,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B5" s="4">
         <v>46113</v>
       </c>
@@ -8353,7 +8347,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="2:7">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B6" s="4">
         <v>46113</v>
       </c>
@@ -8370,7 +8364,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="7" spans="2:7">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B7" s="4">
         <v>46113</v>
       </c>
@@ -8387,7 +8381,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="8" spans="2:7">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B8" s="4">
         <v>46113</v>
       </c>
@@ -8404,7 +8398,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="9" spans="2:7">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
         <v>46113</v>
       </c>
@@ -8421,7 +8415,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="2:7">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B10" s="59">
         <v>46113</v>
       </c>
@@ -8438,7 +8432,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="11" spans="2:7">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
         <v>46113</v>
       </c>
@@ -8455,7 +8449,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="12" spans="2:7">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
         <v>46113</v>
       </c>
@@ -8472,7 +8466,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="13" spans="2:7">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B13" s="4">
         <v>46114</v>
       </c>
@@ -8489,7 +8483,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="14" spans="2:7">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B14" s="4">
         <v>46114</v>
       </c>
@@ -8506,7 +8500,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="15" spans="2:7">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
         <v>46118</v>
       </c>
@@ -8523,7 +8517,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="16" spans="2:7">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B16" s="4">
         <v>46118</v>
       </c>
@@ -8540,7 +8534,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="2:7">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17" s="4">
         <v>46118</v>
       </c>
@@ -8557,7 +8551,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="18" spans="2:7">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" s="4">
         <v>46118</v>
       </c>
@@ -8574,7 +8568,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="2:7">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
         <v>46118</v>
       </c>
@@ -8591,7 +8585,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="20" spans="2:7">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
         <v>46119</v>
       </c>
@@ -8608,7 +8602,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="2:7">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" s="4">
         <v>46121</v>
       </c>
@@ -8625,7 +8619,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="22" spans="2:7">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B22" s="4">
         <v>46121</v>
       </c>
@@ -8642,7 +8636,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B23" s="4">
         <v>46121</v>
       </c>
@@ -8659,7 +8653,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="24" spans="2:7">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B24" s="4">
         <v>46121</v>
       </c>
@@ -8674,7 +8668,7 @@
       </c>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="2:7">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B25" s="4">
         <v>46126</v>
       </c>
@@ -8689,7 +8683,7 @@
       </c>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="2:7">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
         <v>46126</v>
       </c>
@@ -8704,7 +8698,7 @@
       </c>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="2:7">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B27" s="4">
         <v>46126</v>
       </c>
@@ -8719,7 +8713,7 @@
       </c>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="2:7">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B28" s="4">
         <v>46126</v>
       </c>
@@ -8733,7 +8727,7 @@
         <v>99715.1</v>
       </c>
     </row>
-    <row r="29" spans="2:7">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B29" s="4">
         <v>46126</v>
       </c>
@@ -8747,7 +8741,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="30" spans="2:7">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B30" s="4">
         <v>46126</v>
       </c>
@@ -8761,7 +8755,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="31" spans="2:7">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
         <v>46126</v>
       </c>
@@ -8775,7 +8769,7 @@
         <v>13020.4</v>
       </c>
     </row>
-    <row r="32" spans="2:7">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
         <v>46126</v>
       </c>
@@ -8789,7 +8783,7 @@
         <v>8974.75</v>
       </c>
     </row>
-    <row r="33" spans="2:5">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33" s="4">
         <v>46126</v>
       </c>
@@ -8803,7 +8797,7 @@
         <v>534.5</v>
       </c>
     </row>
-    <row r="34" spans="2:5">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
         <v>46126</v>
       </c>
@@ -8817,7 +8811,7 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="35" spans="2:5">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35" s="4">
         <v>46126</v>
       </c>
@@ -8831,7 +8825,7 @@
         <v>4390</v>
       </c>
     </row>
-    <row r="36" spans="2:5">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36" s="4">
         <v>46127</v>
       </c>
@@ -8845,7 +8839,7 @@
         <v>8024</v>
       </c>
     </row>
-    <row r="37" spans="2:5">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B37" s="4">
         <v>46127</v>
       </c>
@@ -8859,7 +8853,7 @@
         <v>20357.04</v>
       </c>
     </row>
-    <row r="38" spans="2:5">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B38" s="4">
         <v>46128</v>
       </c>
@@ -8873,7 +8867,7 @@
         <v>3300.7</v>
       </c>
     </row>
-    <row r="39" spans="2:5">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B39" s="4">
         <v>46129</v>
       </c>
@@ -8887,7 +8881,7 @@
         <v>4763.3999999999996</v>
       </c>
     </row>
-    <row r="40" spans="2:5">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B40" s="4">
         <v>46134</v>
       </c>
@@ -8901,7 +8895,7 @@
         <v>11765</v>
       </c>
     </row>
-    <row r="41" spans="2:5">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
         <v>46134</v>
       </c>
@@ -8915,7 +8909,7 @@
         <v>1958.46</v>
       </c>
     </row>
-    <row r="42" spans="2:5">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B42" s="4">
         <v>46134</v>
       </c>
@@ -8929,7 +8923,7 @@
         <v>1522.95</v>
       </c>
     </row>
-    <row r="43" spans="2:5">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B43" s="4">
         <v>46134</v>
       </c>
@@ -8943,7 +8937,7 @@
         <v>41442.46</v>
       </c>
     </row>
-    <row r="44" spans="2:5">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
         <v>46134</v>
       </c>
@@ -8957,7 +8951,7 @@
         <v>57885.279999999999</v>
       </c>
     </row>
-    <row r="45" spans="2:5">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B45" s="4">
         <v>46134</v>
       </c>

--- a/Gott Bike/INDICADORES DIÁRIOS.xlsx
+++ b/Gott Bike/INDICADORES DIÁRIOS.xlsx
@@ -1250,6 +1250,12 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1260,12 +1266,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1498,10 +1498,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="ddd\ dd/mm/yyyy"/>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <font>
@@ -1628,10 +1628,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <numFmt numFmtId="164" formatCode="ddd\ dd/mm/yyyy"/>
     </dxf>
     <dxf>
       <font>
@@ -1683,14 +1683,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4D968E04-06EF-4CC7-9C6F-A57B1CBB5F4B}" name="Tabela1" displayName="Tabela1" ref="B3:E107" totalsRowShown="0" headerRowDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4D968E04-06EF-4CC7-9C6F-A57B1CBB5F4B}" name="Tabela1" displayName="Tabela1" ref="B3:E107" totalsRowShown="0" headerRowDxfId="30">
   <autoFilter ref="B3:E107" xr:uid="{4D968E04-06EF-4CC7-9C6F-A57B1CBB5F4B}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:E89">
     <sortCondition ref="B3:B89"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{BB065966-614D-4168-B93D-A210BB1E0C8D}" name="Data" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{0E418006-DCE5-4F97-93B4-A899D67631E7}" name="Qtde" dataDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{BB065966-614D-4168-B93D-A210BB1E0C8D}" name="Data" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{0E418006-DCE5-4F97-93B4-A899D67631E7}" name="Qtde" dataDxfId="28"/>
     <tableColumn id="3" xr3:uid="{5E9349A6-F048-4999-B707-3D89C965382E}" name="Plataforma"/>
     <tableColumn id="4" xr3:uid="{11AA1DC1-1AE5-4E49-B53D-967E3111E872}" name="(R$) Valor" dataCellStyle="Moeda"/>
   </tableColumns>
@@ -1699,22 +1699,22 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0EF1F2A8-F80A-407B-8B7B-0BFBFEDF6A0D}" name="Tabela8" displayName="Tabela8" ref="G2:G10" totalsRowShown="0" headerRowDxfId="18" dataDxfId="16" headerRowBorderDxfId="17" tableBorderDxfId="15" totalsRowBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0EF1F2A8-F80A-407B-8B7B-0BFBFEDF6A0D}" name="Tabela8" displayName="Tabela8" ref="G2:G10" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
   <autoFilter ref="G2:G10" xr:uid="{0EF1F2A8-F80A-407B-8B7B-0BFBFEDF6A0D}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{047DC460-557A-40DB-8C81-95DF946F5AD7}" name="PLATAFORMAS" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{047DC460-557A-40DB-8C81-95DF946F5AD7}" name="PLATAFORMAS" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6EB69137-5DEF-4DEE-A295-1FA4C5115578}" name="Tabela135" displayName="Tabela135" ref="B3:F53" totalsRowShown="0" headerRowDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6EB69137-5DEF-4DEE-A295-1FA4C5115578}" name="Tabela135" displayName="Tabela135" ref="B3:F53" totalsRowShown="0" headerRowDxfId="21">
   <autoFilter ref="B3:F53" xr:uid="{6EB69137-5DEF-4DEE-A295-1FA4C5115578}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{F39CB7F4-E762-4BDF-B2C6-8749DB68D027}" name="Data"/>
-    <tableColumn id="2" xr3:uid="{E9E42632-7C2F-4C97-BCA4-C914BCBA10DC}" name="Banco" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{5B08F7C6-B877-42F6-98D4-8D56834BE254}" name="Plataforma" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{E9E42632-7C2F-4C97-BCA4-C914BCBA10DC}" name="Banco" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{5B08F7C6-B877-42F6-98D4-8D56834BE254}" name="Plataforma" dataDxfId="19"/>
     <tableColumn id="6" xr3:uid="{F7822F46-F359-40F0-8736-0420E5F8BEF4}" name="Descrição"/>
     <tableColumn id="4" xr3:uid="{D0BDF5C5-4A71-4AC2-A4FF-BA03AF90DFCB}" name="(R$) Valor" dataCellStyle="Moeda"/>
   </tableColumns>
@@ -1723,10 +1723,10 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{67A3570C-9B27-40AF-9CD6-28857E5EBB30}" name="Tabela810" displayName="Tabela810" ref="L2:L14" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{67A3570C-9B27-40AF-9CD6-28857E5EBB30}" name="Tabela810" displayName="Tabela810" ref="L2:L14" totalsRowShown="0" headerRowDxfId="18" dataDxfId="16" headerRowBorderDxfId="17" tableBorderDxfId="15" totalsRowBorderDxfId="14">
   <autoFilter ref="L2:L14" xr:uid="{67A3570C-9B27-40AF-9CD6-28857E5EBB30}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{9127BBB1-B684-40F8-8735-E6EFF2611541}" name="PLATAFORMAS" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{9127BBB1-B684-40F8-8735-E6EFF2611541}" name="PLATAFORMAS" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2127,12 +2127,12 @@
       </c>
     </row>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
       <c r="G2" s="10" t="s">
         <v>1</v>
       </c>
@@ -3673,18 +3673,18 @@
       </c>
     </row>
     <row r="2" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="H2" s="70" t="s">
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="H2" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="71"/>
-      <c r="J2" s="72"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="74"/>
       <c r="L2" s="10" t="s">
         <v>1</v>
       </c>
@@ -4803,13 +4803,13 @@
       </c>
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
       <c r="G2" t="s">
         <v>53</v>
       </c>
@@ -7874,13 +7874,13 @@
   <sheetData>
     <row r="1" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="73" t="s">
+      <c r="B2" s="69" t="s">
         <v>216</v>
       </c>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
     </row>
     <row r="3" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B3" s="18" t="s">
@@ -8286,12 +8286,12 @@
       </c>
     </row>
     <row r="2" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="71" t="s">
         <v>222</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
       <c r="G2" s="7" t="s">
         <v>54</v>
       </c>

--- a/Gott Bike/INDICADORES DIÁRIOS.xlsx
+++ b/Gott Bike/INDICADORES DIÁRIOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8d3dd0af008984df/Consultorias/GitHub/Cotta-Consultoria/Gott Bike/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2218" documentId="8_{49B7964F-2481-4178-A148-E82770C67CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88117421-4F24-45C9-BE07-16D8E53B5170}"/>
+  <xr:revisionPtr revIDLastSave="2223" documentId="8_{49B7964F-2481-4178-A148-E82770C67CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BFE415B-0709-4FFD-8D9B-5187CFAA970E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{AF016D11-4BBA-49FD-9799-541824B780DA}"/>
   </bookViews>
@@ -8083,7 +8083,7 @@
         <v>219</v>
       </c>
       <c r="F14" s="44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -8100,7 +8100,7 @@
         <v>219</v>
       </c>
       <c r="F15" s="45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -8117,7 +8117,7 @@
         <v>221</v>
       </c>
       <c r="F16" s="44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -8134,7 +8134,7 @@
         <v>219</v>
       </c>
       <c r="F17" s="45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -8151,7 +8151,7 @@
         <v>221</v>
       </c>
       <c r="F18" s="44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>

--- a/Gott Bike/INDICADORES DIÁRIOS.xlsx
+++ b/Gott Bike/INDICADORES DIÁRIOS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8d3dd0af008984df/Consultorias/GitHub/Cotta-Consultoria/Gott Bike/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Cotta-Consultoria\Gott Bike\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2223" documentId="8_{49B7964F-2481-4178-A148-E82770C67CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BFE415B-0709-4FFD-8D9B-5187CFAA970E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36BEC140-0C6D-46C1-8977-15C978460621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{AF016D11-4BBA-49FD-9799-541824B780DA}"/>
   </bookViews>
@@ -8134,7 +8134,7 @@
         <v>219</v>
       </c>
       <c r="F17" s="45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -8151,7 +8151,7 @@
         <v>221</v>
       </c>
       <c r="F18" s="44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>

--- a/Gott Bike/INDICADORES DIÁRIOS.xlsx
+++ b/Gott Bike/INDICADORES DIÁRIOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Cotta-Consultoria\Gott Bike\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36BEC140-0C6D-46C1-8977-15C978460621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3353C88F-9FF9-4B52-9BCF-7B20BDB3455D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{AF016D11-4BBA-49FD-9799-541824B780DA}"/>
   </bookViews>
@@ -8134,7 +8134,7 @@
         <v>219</v>
       </c>
       <c r="F17" s="45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -8151,7 +8151,7 @@
         <v>221</v>
       </c>
       <c r="F18" s="44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>

--- a/Gott Bike/INDICADORES DIÁRIOS.xlsx
+++ b/Gott Bike/INDICADORES DIÁRIOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Cotta-Consultoria\Gott Bike\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3353C88F-9FF9-4B52-9BCF-7B20BDB3455D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C587A653-E1FD-45BD-9C94-E24EE2281A6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{AF016D11-4BBA-49FD-9799-541824B780DA}"/>
   </bookViews>
@@ -8100,7 +8100,7 @@
         <v>219</v>
       </c>
       <c r="F15" s="45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -8117,7 +8117,7 @@
         <v>221</v>
       </c>
       <c r="F16" s="44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -8134,7 +8134,7 @@
         <v>219</v>
       </c>
       <c r="F17" s="45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -8151,7 +8151,7 @@
         <v>221</v>
       </c>
       <c r="F18" s="44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>

--- a/Gott Bike/INDICADORES DIÁRIOS.xlsx
+++ b/Gott Bike/INDICADORES DIÁRIOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Cotta-Consultoria\Gott Bike\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C587A653-E1FD-45BD-9C94-E24EE2281A6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F359322E-76BE-4A1E-9443-55560EB3BAC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{AF016D11-4BBA-49FD-9799-541824B780DA}"/>
   </bookViews>
@@ -8100,7 +8100,7 @@
         <v>219</v>
       </c>
       <c r="F15" s="45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -8117,7 +8117,7 @@
         <v>221</v>
       </c>
       <c r="F16" s="44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -8134,7 +8134,7 @@
         <v>219</v>
       </c>
       <c r="F17" s="45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -8151,7 +8151,7 @@
         <v>221</v>
       </c>
       <c r="F18" s="44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>

--- a/Gott Bike/INDICADORES DIÁRIOS.xlsx
+++ b/Gott Bike/INDICADORES DIÁRIOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Cotta-Consultoria\Gott Bike\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F359322E-76BE-4A1E-9443-55560EB3BAC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB66080E-7783-4512-9D60-AD6CB7A12877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{AF016D11-4BBA-49FD-9799-541824B780DA}"/>
   </bookViews>
@@ -8083,7 +8083,7 @@
         <v>219</v>
       </c>
       <c r="F14" s="44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -8100,7 +8100,7 @@
         <v>219</v>
       </c>
       <c r="F15" s="45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -8117,7 +8117,7 @@
         <v>221</v>
       </c>
       <c r="F16" s="44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -8134,7 +8134,7 @@
         <v>219</v>
       </c>
       <c r="F17" s="45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -8151,7 +8151,7 @@
         <v>221</v>
       </c>
       <c r="F18" s="44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>

--- a/Gott Bike/INDICADORES DIÁRIOS.xlsx
+++ b/Gott Bike/INDICADORES DIÁRIOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Cotta-Consultoria\Gott Bike\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB66080E-7783-4512-9D60-AD6CB7A12877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4692460E-69E7-4153-8231-6C221397C811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{AF016D11-4BBA-49FD-9799-541824B780DA}"/>
   </bookViews>
@@ -8083,7 +8083,7 @@
         <v>219</v>
       </c>
       <c r="F14" s="44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -8100,7 +8100,7 @@
         <v>219</v>
       </c>
       <c r="F15" s="45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -8117,7 +8117,7 @@
         <v>221</v>
       </c>
       <c r="F16" s="44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -8134,7 +8134,7 @@
         <v>219</v>
       </c>
       <c r="F17" s="45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -8151,7 +8151,7 @@
         <v>221</v>
       </c>
       <c r="F18" s="44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>

--- a/Gott Bike/INDICADORES DIÁRIOS.xlsx
+++ b/Gott Bike/INDICADORES DIÁRIOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Cotta-Consultoria\Gott Bike\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4692460E-69E7-4153-8231-6C221397C811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37A601CF-8D1D-4B86-AF28-2470D9DF57F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{AF016D11-4BBA-49FD-9799-541824B780DA}"/>
   </bookViews>
@@ -8151,7 +8151,7 @@
         <v>221</v>
       </c>
       <c r="F18" s="44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>

--- a/Gott Bike/INDICADORES DIÁRIOS.xlsx
+++ b/Gott Bike/INDICADORES DIÁRIOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Cotta-Consultoria\Gott Bike\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37A601CF-8D1D-4B86-AF28-2470D9DF57F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C9FE9D5-7084-4C44-B2D1-8D588F09FA15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{AF016D11-4BBA-49FD-9799-541824B780DA}"/>
   </bookViews>
@@ -8151,7 +8151,7 @@
         <v>221</v>
       </c>
       <c r="F18" s="44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>

--- a/Gott Bike/INDICADORES DIÁRIOS.xlsx
+++ b/Gott Bike/INDICADORES DIÁRIOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Cotta-Consultoria\Gott Bike\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C9FE9D5-7084-4C44-B2D1-8D588F09FA15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19AC8815-D3A0-4A4A-B3DF-6D44D77240BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{AF016D11-4BBA-49FD-9799-541824B780DA}"/>
   </bookViews>
@@ -8134,7 +8134,7 @@
         <v>219</v>
       </c>
       <c r="F17" s="45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -8151,7 +8151,7 @@
         <v>221</v>
       </c>
       <c r="F18" s="44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>

--- a/Gott Bike/INDICADORES DIÁRIOS.xlsx
+++ b/Gott Bike/INDICADORES DIÁRIOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Cotta-Consultoria\Gott Bike\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19AC8815-D3A0-4A4A-B3DF-6D44D77240BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B38F157-78DC-474A-ACED-F3FC85EF6927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{AF016D11-4BBA-49FD-9799-541824B780DA}"/>
   </bookViews>
@@ -8134,7 +8134,7 @@
         <v>219</v>
       </c>
       <c r="F17" s="45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -8151,7 +8151,7 @@
         <v>221</v>
       </c>
       <c r="F18" s="44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>

--- a/Gott Bike/INDICADORES DIÁRIOS.xlsx
+++ b/Gott Bike/INDICADORES DIÁRIOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Cotta-Consultoria\Gott Bike\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B38F157-78DC-474A-ACED-F3FC85EF6927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88554CAE-F22D-40DA-A9A4-1680D70FF9B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{AF016D11-4BBA-49FD-9799-541824B780DA}"/>
   </bookViews>
@@ -8117,7 +8117,7 @@
         <v>221</v>
       </c>
       <c r="F16" s="44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -8134,7 +8134,7 @@
         <v>219</v>
       </c>
       <c r="F17" s="45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -8151,7 +8151,7 @@
         <v>221</v>
       </c>
       <c r="F18" s="44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>

--- a/Gott Bike/INDICADORES DIÁRIOS.xlsx
+++ b/Gott Bike/INDICADORES DIÁRIOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Cotta-Consultoria\Gott Bike\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88554CAE-F22D-40DA-A9A4-1680D70FF9B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F39E742-1C8C-48C2-B5E8-85A171EFFB12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{AF016D11-4BBA-49FD-9799-541824B780DA}"/>
   </bookViews>
@@ -8117,7 +8117,7 @@
         <v>221</v>
       </c>
       <c r="F16" s="44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -8134,7 +8134,7 @@
         <v>219</v>
       </c>
       <c r="F17" s="45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -8151,7 +8151,7 @@
         <v>221</v>
       </c>
       <c r="F18" s="44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>

--- a/Gott Bike/INDICADORES DIÁRIOS.xlsx
+++ b/Gott Bike/INDICADORES DIÁRIOS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Cotta-Consultoria\Gott Bike\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8d3dd0af008984df/Consultorias/GitHub/Cotta-Consultoria/Gott Bike/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F39E742-1C8C-48C2-B5E8-85A171EFFB12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2217" documentId="8_{49B7964F-2481-4178-A148-E82770C67CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B87598F5-490E-4D01-9BBE-4AA987064A59}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{AF016D11-4BBA-49FD-9799-541824B780DA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AF016D11-4BBA-49FD-9799-541824B780DA}"/>
   </bookViews>
   <sheets>
     <sheet name="Faturamento" sheetId="4" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="236">
   <si>
     <t>CONTROLE DE FATURAMENTO</t>
   </si>
@@ -1250,12 +1250,6 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1266,6 +1260,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1498,10 +1498,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <numFmt numFmtId="164" formatCode="ddd\ dd/mm/yyyy"/>
     </dxf>
     <dxf>
       <font>
@@ -1628,10 +1628,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="ddd\ dd/mm/yyyy"/>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <font>
@@ -1683,14 +1683,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4D968E04-06EF-4CC7-9C6F-A57B1CBB5F4B}" name="Tabela1" displayName="Tabela1" ref="B3:E107" totalsRowShown="0" headerRowDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4D968E04-06EF-4CC7-9C6F-A57B1CBB5F4B}" name="Tabela1" displayName="Tabela1" ref="B3:E107" totalsRowShown="0" headerRowDxfId="21">
   <autoFilter ref="B3:E107" xr:uid="{4D968E04-06EF-4CC7-9C6F-A57B1CBB5F4B}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:E89">
     <sortCondition ref="B3:B89"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{BB065966-614D-4168-B93D-A210BB1E0C8D}" name="Data" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{0E418006-DCE5-4F97-93B4-A899D67631E7}" name="Qtde" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{BB065966-614D-4168-B93D-A210BB1E0C8D}" name="Data" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{0E418006-DCE5-4F97-93B4-A899D67631E7}" name="Qtde" dataDxfId="19"/>
     <tableColumn id="3" xr3:uid="{5E9349A6-F048-4999-B707-3D89C965382E}" name="Plataforma"/>
     <tableColumn id="4" xr3:uid="{11AA1DC1-1AE5-4E49-B53D-967E3111E872}" name="(R$) Valor" dataCellStyle="Moeda"/>
   </tableColumns>
@@ -1699,22 +1699,22 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0EF1F2A8-F80A-407B-8B7B-0BFBFEDF6A0D}" name="Tabela8" displayName="Tabela8" ref="G2:G10" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0EF1F2A8-F80A-407B-8B7B-0BFBFEDF6A0D}" name="Tabela8" displayName="Tabela8" ref="G2:G10" totalsRowShown="0" headerRowDxfId="18" dataDxfId="16" headerRowBorderDxfId="17" tableBorderDxfId="15" totalsRowBorderDxfId="14">
   <autoFilter ref="G2:G10" xr:uid="{0EF1F2A8-F80A-407B-8B7B-0BFBFEDF6A0D}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{047DC460-557A-40DB-8C81-95DF946F5AD7}" name="PLATAFORMAS" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{047DC460-557A-40DB-8C81-95DF946F5AD7}" name="PLATAFORMAS" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6EB69137-5DEF-4DEE-A295-1FA4C5115578}" name="Tabela135" displayName="Tabela135" ref="B3:F53" totalsRowShown="0" headerRowDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6EB69137-5DEF-4DEE-A295-1FA4C5115578}" name="Tabela135" displayName="Tabela135" ref="B3:F53" totalsRowShown="0" headerRowDxfId="30">
   <autoFilter ref="B3:F53" xr:uid="{6EB69137-5DEF-4DEE-A295-1FA4C5115578}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{F39CB7F4-E762-4BDF-B2C6-8749DB68D027}" name="Data"/>
-    <tableColumn id="2" xr3:uid="{E9E42632-7C2F-4C97-BCA4-C914BCBA10DC}" name="Banco" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{5B08F7C6-B877-42F6-98D4-8D56834BE254}" name="Plataforma" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{E9E42632-7C2F-4C97-BCA4-C914BCBA10DC}" name="Banco" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{5B08F7C6-B877-42F6-98D4-8D56834BE254}" name="Plataforma" dataDxfId="28"/>
     <tableColumn id="6" xr3:uid="{F7822F46-F359-40F0-8736-0420E5F8BEF4}" name="Descrição"/>
     <tableColumn id="4" xr3:uid="{D0BDF5C5-4A71-4AC2-A4FF-BA03AF90DFCB}" name="(R$) Valor" dataCellStyle="Moeda"/>
   </tableColumns>
@@ -1723,10 +1723,10 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{67A3570C-9B27-40AF-9CD6-28857E5EBB30}" name="Tabela810" displayName="Tabela810" ref="L2:L14" totalsRowShown="0" headerRowDxfId="18" dataDxfId="16" headerRowBorderDxfId="17" tableBorderDxfId="15" totalsRowBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{67A3570C-9B27-40AF-9CD6-28857E5EBB30}" name="Tabela810" displayName="Tabela810" ref="L2:L14" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
   <autoFilter ref="L2:L14" xr:uid="{67A3570C-9B27-40AF-9CD6-28857E5EBB30}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{9127BBB1-B684-40F8-8735-E6EFF2611541}" name="PLATAFORMAS" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{9127BBB1-B684-40F8-8735-E6EFF2611541}" name="PLATAFORMAS" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2099,7 +2099,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{152610B4-81C2-44F7-A8DF-A454E1B8F2ED}">
-  <dimension ref="B1:L105"/>
+  <dimension ref="B1:L106"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -2119,20 +2119,20 @@
     <row r="1" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C1" s="60">
         <f>SUBTOTAL(9,Tabela1[Qtde])</f>
-        <v>1533</v>
+        <v>1543</v>
       </c>
       <c r="E1" s="12">
         <f>SUBTOTAL(9,Tabela1[(R$) Valor])</f>
-        <v>1150759.95</v>
+        <v>1250759.95</v>
       </c>
     </row>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="71" t="s">
+      <c r="B2" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
       <c r="G2" s="10" t="s">
         <v>1</v>
       </c>
@@ -2170,14 +2170,14 @@
       </c>
       <c r="J3" s="55">
         <f>E1</f>
-        <v>1150759.95</v>
+        <v>1250759.95</v>
       </c>
       <c r="K3" s="61">
         <v>1630</v>
       </c>
       <c r="L3" s="55">
         <f>IFERROR(J3/K3,0)</f>
-        <v>705.9876993865031</v>
+        <v>767.33739263803682</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
@@ -3627,13 +3627,27 @@
       </c>
       <c r="E105" s="6">
         <v>743.9</v>
+      </c>
+    </row>
+    <row r="106" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B106" s="4">
+        <v>46136</v>
+      </c>
+      <c r="C106" s="1">
+        <v>10</v>
+      </c>
+      <c r="D106" t="s">
+        <v>16</v>
+      </c>
+      <c r="E106" s="6">
+        <v>100000</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:E2"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D107" xr:uid="{A625BF53-AEF2-4343-98C8-03A2E1A9920C}">
       <formula1>$G$3:$G$10</formula1>
     </dataValidation>
@@ -3673,18 +3687,18 @@
       </c>
     </row>
     <row r="2" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B2" s="71" t="s">
+      <c r="B2" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="H2" s="72" t="s">
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="H2" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="73"/>
-      <c r="J2" s="74"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="72"/>
       <c r="L2" s="10" t="s">
         <v>1</v>
       </c>
@@ -4803,13 +4817,13 @@
       </c>
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="71" t="s">
+      <c r="B2" s="69" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
       <c r="G2" t="s">
         <v>53</v>
       </c>
@@ -7874,13 +7888,13 @@
   <sheetData>
     <row r="1" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="73" t="s">
         <v>216</v>
       </c>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
     </row>
     <row r="3" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B3" s="18" t="s">
@@ -8286,12 +8300,12 @@
       </c>
     </row>
     <row r="2" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B2" s="71" t="s">
+      <c r="B2" s="69" t="s">
         <v>222</v>
       </c>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
       <c r="G2" s="7" t="s">
         <v>54</v>
       </c>

--- a/Gott Bike/INDICADORES DIÁRIOS.xlsx
+++ b/Gott Bike/INDICADORES DIÁRIOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8d3dd0af008984df/Consultorias/GitHub/Cotta-Consultoria/Gott Bike/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2217" documentId="8_{49B7964F-2481-4178-A148-E82770C67CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B87598F5-490E-4D01-9BBE-4AA987064A59}"/>
+  <xr:revisionPtr revIDLastSave="2221" documentId="8_{49B7964F-2481-4178-A148-E82770C67CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D99A6A5-BFEA-4EC4-8D68-1387A81B3170}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AF016D11-4BBA-49FD-9799-541824B780DA}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="236">
   <si>
     <t>CONTROLE DE FATURAMENTO</t>
   </si>
@@ -1498,10 +1498,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="ddd\ dd/mm/yyyy"/>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <font>
@@ -1628,10 +1628,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <numFmt numFmtId="164" formatCode="ddd\ dd/mm/yyyy"/>
     </dxf>
     <dxf>
       <font>
@@ -1683,14 +1683,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4D968E04-06EF-4CC7-9C6F-A57B1CBB5F4B}" name="Tabela1" displayName="Tabela1" ref="B3:E107" totalsRowShown="0" headerRowDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4D968E04-06EF-4CC7-9C6F-A57B1CBB5F4B}" name="Tabela1" displayName="Tabela1" ref="B3:E107" totalsRowShown="0" headerRowDxfId="30">
   <autoFilter ref="B3:E107" xr:uid="{4D968E04-06EF-4CC7-9C6F-A57B1CBB5F4B}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:E89">
     <sortCondition ref="B3:B89"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{BB065966-614D-4168-B93D-A210BB1E0C8D}" name="Data" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{0E418006-DCE5-4F97-93B4-A899D67631E7}" name="Qtde" dataDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{BB065966-614D-4168-B93D-A210BB1E0C8D}" name="Data" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{0E418006-DCE5-4F97-93B4-A899D67631E7}" name="Qtde" dataDxfId="28"/>
     <tableColumn id="3" xr3:uid="{5E9349A6-F048-4999-B707-3D89C965382E}" name="Plataforma"/>
     <tableColumn id="4" xr3:uid="{11AA1DC1-1AE5-4E49-B53D-967E3111E872}" name="(R$) Valor" dataCellStyle="Moeda"/>
   </tableColumns>
@@ -1699,22 +1699,22 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0EF1F2A8-F80A-407B-8B7B-0BFBFEDF6A0D}" name="Tabela8" displayName="Tabela8" ref="G2:G10" totalsRowShown="0" headerRowDxfId="18" dataDxfId="16" headerRowBorderDxfId="17" tableBorderDxfId="15" totalsRowBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0EF1F2A8-F80A-407B-8B7B-0BFBFEDF6A0D}" name="Tabela8" displayName="Tabela8" ref="G2:G10" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
   <autoFilter ref="G2:G10" xr:uid="{0EF1F2A8-F80A-407B-8B7B-0BFBFEDF6A0D}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{047DC460-557A-40DB-8C81-95DF946F5AD7}" name="PLATAFORMAS" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{047DC460-557A-40DB-8C81-95DF946F5AD7}" name="PLATAFORMAS" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6EB69137-5DEF-4DEE-A295-1FA4C5115578}" name="Tabela135" displayName="Tabela135" ref="B3:F53" totalsRowShown="0" headerRowDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6EB69137-5DEF-4DEE-A295-1FA4C5115578}" name="Tabela135" displayName="Tabela135" ref="B3:F53" totalsRowShown="0" headerRowDxfId="21">
   <autoFilter ref="B3:F53" xr:uid="{6EB69137-5DEF-4DEE-A295-1FA4C5115578}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{F39CB7F4-E762-4BDF-B2C6-8749DB68D027}" name="Data"/>
-    <tableColumn id="2" xr3:uid="{E9E42632-7C2F-4C97-BCA4-C914BCBA10DC}" name="Banco" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{5B08F7C6-B877-42F6-98D4-8D56834BE254}" name="Plataforma" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{E9E42632-7C2F-4C97-BCA4-C914BCBA10DC}" name="Banco" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{5B08F7C6-B877-42F6-98D4-8D56834BE254}" name="Plataforma" dataDxfId="19"/>
     <tableColumn id="6" xr3:uid="{F7822F46-F359-40F0-8736-0420E5F8BEF4}" name="Descrição"/>
     <tableColumn id="4" xr3:uid="{D0BDF5C5-4A71-4AC2-A4FF-BA03AF90DFCB}" name="(R$) Valor" dataCellStyle="Moeda"/>
   </tableColumns>
@@ -1723,10 +1723,10 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{67A3570C-9B27-40AF-9CD6-28857E5EBB30}" name="Tabela810" displayName="Tabela810" ref="L2:L14" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{67A3570C-9B27-40AF-9CD6-28857E5EBB30}" name="Tabela810" displayName="Tabela810" ref="L2:L14" totalsRowShown="0" headerRowDxfId="18" dataDxfId="16" headerRowBorderDxfId="17" tableBorderDxfId="15" totalsRowBorderDxfId="14">
   <autoFilter ref="L2:L14" xr:uid="{67A3570C-9B27-40AF-9CD6-28857E5EBB30}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{9127BBB1-B684-40F8-8735-E6EFF2611541}" name="PLATAFORMAS" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{9127BBB1-B684-40F8-8735-E6EFF2611541}" name="PLATAFORMAS" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2099,7 +2099,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{152610B4-81C2-44F7-A8DF-A454E1B8F2ED}">
-  <dimension ref="B1:L106"/>
+  <dimension ref="B1:L105"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -2119,11 +2119,11 @@
     <row r="1" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C1" s="60">
         <f>SUBTOTAL(9,Tabela1[Qtde])</f>
-        <v>1543</v>
+        <v>1533</v>
       </c>
       <c r="E1" s="12">
         <f>SUBTOTAL(9,Tabela1[(R$) Valor])</f>
-        <v>1250759.95</v>
+        <v>1150759.95</v>
       </c>
     </row>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
@@ -2170,14 +2170,14 @@
       </c>
       <c r="J3" s="55">
         <f>E1</f>
-        <v>1250759.95</v>
+        <v>1150759.95</v>
       </c>
       <c r="K3" s="61">
         <v>1630</v>
       </c>
       <c r="L3" s="55">
         <f>IFERROR(J3/K3,0)</f>
-        <v>767.33739263803682</v>
+        <v>705.9876993865031</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
@@ -3627,20 +3627,6 @@
       </c>
       <c r="E105" s="6">
         <v>743.9</v>
-      </c>
-    </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B106" s="4">
-        <v>46136</v>
-      </c>
-      <c r="C106" s="1">
-        <v>10</v>
-      </c>
-      <c r="D106" t="s">
-        <v>16</v>
-      </c>
-      <c r="E106" s="6">
-        <v>100000</v>
       </c>
     </row>
   </sheetData>

--- a/Gott Bike/INDICADORES DIÁRIOS.xlsx
+++ b/Gott Bike/INDICADORES DIÁRIOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8d3dd0af008984df/Consultorias/GitHub/Cotta-Consultoria/Gott Bike/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2221" documentId="8_{49B7964F-2481-4178-A148-E82770C67CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D99A6A5-BFEA-4EC4-8D68-1387A81B3170}"/>
+  <xr:revisionPtr revIDLastSave="2225" documentId="8_{49B7964F-2481-4178-A148-E82770C67CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E54238C-74CC-464D-A232-70C2D86F8594}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AF016D11-4BBA-49FD-9799-541824B780DA}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="236">
   <si>
     <t>CONTROLE DE FATURAMENTO</t>
   </si>
@@ -2099,7 +2099,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{152610B4-81C2-44F7-A8DF-A454E1B8F2ED}">
-  <dimension ref="B1:L105"/>
+  <dimension ref="B1:L106"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -2119,11 +2119,11 @@
     <row r="1" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C1" s="60">
         <f>SUBTOTAL(9,Tabela1[Qtde])</f>
-        <v>1533</v>
+        <v>1633</v>
       </c>
       <c r="E1" s="12">
         <f>SUBTOTAL(9,Tabela1[(R$) Valor])</f>
-        <v>1150759.95</v>
+        <v>1550759.95</v>
       </c>
     </row>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
@@ -2170,14 +2170,14 @@
       </c>
       <c r="J3" s="55">
         <f>E1</f>
-        <v>1150759.95</v>
+        <v>1550759.95</v>
       </c>
       <c r="K3" s="61">
         <v>1630</v>
       </c>
       <c r="L3" s="55">
         <f>IFERROR(J3/K3,0)</f>
-        <v>705.9876993865031</v>
+        <v>951.38647239263798</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
@@ -3627,6 +3627,20 @@
       </c>
       <c r="E105" s="6">
         <v>743.9</v>
+      </c>
+    </row>
+    <row r="106" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B106" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C106" s="1">
+        <v>100</v>
+      </c>
+      <c r="D106" t="s">
+        <v>16</v>
+      </c>
+      <c r="E106" s="6">
+        <v>400000</v>
       </c>
     </row>
   </sheetData>

--- a/Gott Bike/INDICADORES DIÁRIOS.xlsx
+++ b/Gott Bike/INDICADORES DIÁRIOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8d3dd0af008984df/Consultorias/GitHub/Cotta-Consultoria/Gott Bike/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2225" documentId="8_{49B7964F-2481-4178-A148-E82770C67CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E54238C-74CC-464D-A232-70C2D86F8594}"/>
+  <xr:revisionPtr revIDLastSave="2229" documentId="8_{49B7964F-2481-4178-A148-E82770C67CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9910FA58-6564-4498-8B00-BFD177FF2FC0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AF016D11-4BBA-49FD-9799-541824B780DA}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="236">
   <si>
     <t>CONTROLE DE FATURAMENTO</t>
   </si>
@@ -2099,7 +2099,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{152610B4-81C2-44F7-A8DF-A454E1B8F2ED}">
-  <dimension ref="B1:L106"/>
+  <dimension ref="B1:L105"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -2119,11 +2119,11 @@
     <row r="1" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C1" s="60">
         <f>SUBTOTAL(9,Tabela1[Qtde])</f>
-        <v>1633</v>
+        <v>1533</v>
       </c>
       <c r="E1" s="12">
         <f>SUBTOTAL(9,Tabela1[(R$) Valor])</f>
-        <v>1550759.95</v>
+        <v>1150759.95</v>
       </c>
     </row>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
@@ -2170,14 +2170,14 @@
       </c>
       <c r="J3" s="55">
         <f>E1</f>
-        <v>1550759.95</v>
+        <v>1150759.95</v>
       </c>
       <c r="K3" s="61">
         <v>1630</v>
       </c>
       <c r="L3" s="55">
         <f>IFERROR(J3/K3,0)</f>
-        <v>951.38647239263798</v>
+        <v>705.9876993865031</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
@@ -3627,20 +3627,6 @@
       </c>
       <c r="E105" s="6">
         <v>743.9</v>
-      </c>
-    </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B106" s="4">
-        <v>46139</v>
-      </c>
-      <c r="C106" s="1">
-        <v>100</v>
-      </c>
-      <c r="D106" t="s">
-        <v>16</v>
-      </c>
-      <c r="E106" s="6">
-        <v>400000</v>
       </c>
     </row>
   </sheetData>

--- a/Gott Bike/INDICADORES DIÁRIOS.xlsx
+++ b/Gott Bike/INDICADORES DIÁRIOS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8d3dd0af008984df/Consultorias/GitHub/Cotta-Consultoria/Gott Bike/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8d3dd0af008984df/Consultorias/GOTT BIKE/Compartilhado GOTT Bike/Indicadores e Métricas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2229" documentId="8_{49B7964F-2481-4178-A148-E82770C67CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9910FA58-6564-4498-8B00-BFD177FF2FC0}"/>
+  <xr:revisionPtr revIDLastSave="2546" documentId="8_{49B7964F-2481-4178-A148-E82770C67CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8653D045-8291-406A-A84D-DF033781A297}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AF016D11-4BBA-49FD-9799-541824B780DA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{AF016D11-4BBA-49FD-9799-541824B780DA}"/>
   </bookViews>
   <sheets>
     <sheet name="Faturamento" sheetId="4" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="262">
   <si>
     <t>CONTROLE DE FATURAMENTO</t>
   </si>
@@ -105,6 +105,9 @@
     <t>REPASSE MERCADO PAGO</t>
   </si>
   <si>
+    <t>REPASSE AMAZON</t>
+  </si>
+  <si>
     <t>Banco</t>
   </si>
   <si>
@@ -129,6 +132,9 @@
     <t>SICREDI</t>
   </si>
   <si>
+    <t>BRADESCO</t>
+  </si>
+  <si>
     <t>GETNET CREDITO MASTER | GETNET | 0001-96</t>
   </si>
   <si>
@@ -136,9 +142,6 @@
   </si>
   <si>
     <t>LIBERACAO CREDITO R$ 227.063,97</t>
-  </si>
-  <si>
-    <t>BRADESCO</t>
   </si>
   <si>
     <t xml:space="preserve">RECEBIMENTO PIX 27415911000136 Bytedance Brasil </t>
@@ -200,6 +203,10 @@
     <t>RECEBIMENTO PIX 42580969896 MARCOS DOUGLAS NOGUE</t>
   </si>
   <si>
+    <t xml:space="preserve">
+RECEBIMENTO PIX 48697278000196 GOTT SAUDE COMERC</t>
+  </si>
+  <si>
     <t>CONTROLE DE SAÍDAS</t>
   </si>
   <si>
@@ -218,6 +225,9 @@
     <t>Transferência</t>
   </si>
   <si>
+    <t>Coluna1</t>
+  </si>
+  <si>
     <t>ADV. EVANDRO LUIZ DA SILVA</t>
   </si>
   <si>
@@ -692,6 +702,69 @@
     <t>ALVARÁ</t>
   </si>
   <si>
+    <t>PEDIDO TESTE</t>
+  </si>
+  <si>
+    <t>LANCHONETE PRIMAVERA</t>
+  </si>
+  <si>
+    <t>OFFICE</t>
+  </si>
+  <si>
+    <t>TARUGÃO</t>
+  </si>
+  <si>
+    <t>MONTAGEM DE BICICLETAS</t>
+  </si>
+  <si>
+    <t>HAVOK</t>
+  </si>
+  <si>
+    <t>CAIXAS DE PAPELÃO</t>
+  </si>
+  <si>
+    <t>MONTAGEM DE RODAS</t>
+  </si>
+  <si>
+    <t>UNICRED</t>
+  </si>
+  <si>
+    <t>FATURA</t>
+  </si>
+  <si>
+    <t>MATERIAIS DE ESCRITÓRIO</t>
+  </si>
+  <si>
+    <t>CEFAS</t>
+  </si>
+  <si>
+    <t>DESIGNER</t>
+  </si>
+  <si>
+    <t>CORA</t>
+  </si>
+  <si>
+    <t>IMPRESSORA E TONNER</t>
+  </si>
+  <si>
+    <t>LUMASA</t>
+  </si>
+  <si>
+    <t>EMBALAGEM</t>
+  </si>
+  <si>
+    <t>FMD- THOR E WENDY</t>
+  </si>
+  <si>
+    <t>SRA VOLPATO</t>
+  </si>
+  <si>
+    <t>ARAMARCAS</t>
+  </si>
+  <si>
+    <t>MARCAS</t>
+  </si>
+  <si>
     <t>CONTROLES CHEQUES</t>
   </si>
   <si>
@@ -719,9 +792,6 @@
     <t>REPOSIÇÃO SEMANAL</t>
   </si>
   <si>
-    <t>LUMASA</t>
-  </si>
-  <si>
     <t>REPOSIÇÃO MENSAL</t>
   </si>
   <si>
@@ -750,6 +820,15 @@
   </si>
   <si>
     <t>ARO 26 E MANOEL GOMES</t>
+  </si>
+  <si>
+    <t>BARRA FORTE</t>
+  </si>
+  <si>
+    <t>REPOSIÇÃO SEMANAL E LP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
   </si>
 </sst>
 </file>
@@ -763,7 +842,7 @@
     <numFmt numFmtId="164" formatCode="ddd\ dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -835,8 +914,30 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF232F3E"/>
+      <name val="Amazon Ember"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="2" tint="-9.9978637043366805E-2"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -873,8 +974,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="18">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -1085,6 +1192,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1092,7 +1212,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1211,8 +1331,6 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1239,17 +1357,77 @@
     <xf numFmtId="3" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="12" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1268,6 +1446,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="13" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -1432,6 +1611,13 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <bottom style="thin">
+          <color theme="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <left style="thin">
           <color theme="1"/>
         </left>
@@ -1464,13 +1650,6 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="1"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1562,6 +1741,13 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <bottom style="thin">
+          <color theme="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <left style="thin">
           <color theme="1"/>
         </left>
@@ -1594,13 +1780,6 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="1"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1683,8 +1862,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4D968E04-06EF-4CC7-9C6F-A57B1CBB5F4B}" name="Tabela1" displayName="Tabela1" ref="B3:E107" totalsRowShown="0" headerRowDxfId="30">
-  <autoFilter ref="B3:E107" xr:uid="{4D968E04-06EF-4CC7-9C6F-A57B1CBB5F4B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4D968E04-06EF-4CC7-9C6F-A57B1CBB5F4B}" name="Tabela1" displayName="Tabela1" ref="B3:E111" totalsRowShown="0" headerRowDxfId="30">
+  <autoFilter ref="B3:E111" xr:uid="{4D968E04-06EF-4CC7-9C6F-A57B1CBB5F4B}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:E89">
     <sortCondition ref="B3:B89"/>
   </sortState>
@@ -1699,7 +1878,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0EF1F2A8-F80A-407B-8B7B-0BFBFEDF6A0D}" name="Tabela8" displayName="Tabela8" ref="G2:G10" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0EF1F2A8-F80A-407B-8B7B-0BFBFEDF6A0D}" name="Tabela8" displayName="Tabela8" ref="G2:G10" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26" headerRowBorderDxfId="24" tableBorderDxfId="25" totalsRowBorderDxfId="23">
   <autoFilter ref="G2:G10" xr:uid="{0EF1F2A8-F80A-407B-8B7B-0BFBFEDF6A0D}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{047DC460-557A-40DB-8C81-95DF946F5AD7}" name="PLATAFORMAS" dataDxfId="22"/>
@@ -1709,8 +1888,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6EB69137-5DEF-4DEE-A295-1FA4C5115578}" name="Tabela135" displayName="Tabela135" ref="B3:F53" totalsRowShown="0" headerRowDxfId="21">
-  <autoFilter ref="B3:F53" xr:uid="{6EB69137-5DEF-4DEE-A295-1FA4C5115578}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6EB69137-5DEF-4DEE-A295-1FA4C5115578}" name="Tabela135" displayName="Tabela135" ref="B3:F65" totalsRowShown="0" headerRowDxfId="21">
+  <autoFilter ref="B3:F65" xr:uid="{6EB69137-5DEF-4DEE-A295-1FA4C5115578}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{F39CB7F4-E762-4BDF-B2C6-8749DB68D027}" name="Data"/>
     <tableColumn id="2" xr3:uid="{E9E42632-7C2F-4C97-BCA4-C914BCBA10DC}" name="Banco" dataDxfId="20"/>
@@ -1723,8 +1902,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{67A3570C-9B27-40AF-9CD6-28857E5EBB30}" name="Tabela810" displayName="Tabela810" ref="L2:L14" totalsRowShown="0" headerRowDxfId="18" dataDxfId="16" headerRowBorderDxfId="17" tableBorderDxfId="15" totalsRowBorderDxfId="14">
-  <autoFilter ref="L2:L14" xr:uid="{67A3570C-9B27-40AF-9CD6-28857E5EBB30}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{67A3570C-9B27-40AF-9CD6-28857E5EBB30}" name="Tabela810" displayName="Tabela810" ref="P2:P14" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17" headerRowBorderDxfId="15" tableBorderDxfId="16" totalsRowBorderDxfId="14">
+  <autoFilter ref="P2:P14" xr:uid="{67A3570C-9B27-40AF-9CD6-28857E5EBB30}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{9127BBB1-B684-40F8-8735-E6EFF2611541}" name="PLATAFORMAS" dataDxfId="13"/>
   </tableColumns>
@@ -1733,14 +1912,21 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C40E1681-2A06-40B2-9F0F-8A80EAD60188}" name="Tabela13" displayName="Tabela13" ref="B3:F198" totalsRowShown="0" headerRowDxfId="12">
-  <autoFilter ref="B3:F198" xr:uid="{C40E1681-2A06-40B2-9F0F-8A80EAD60188}"/>
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C40E1681-2A06-40B2-9F0F-8A80EAD60188}" name="Tabela13" displayName="Tabela13" ref="B3:G224" totalsRowShown="0" headerRowDxfId="12">
+  <autoFilter ref="B3:G224" xr:uid="{C40E1681-2A06-40B2-9F0F-8A80EAD60188}">
+    <filterColumn colId="0">
+      <filters>
+        <dateGroupItem year="2026" month="4" day="27" dateTimeGrouping="day"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{6CE0E58B-6690-45A4-8D8F-962F67B0773A}" name="Data" dataDxfId="11"/>
     <tableColumn id="3" xr3:uid="{9BD39337-5CC3-45E0-9CCF-8A1AF726B1E7}" name="Fornecedor" dataDxfId="10"/>
     <tableColumn id="6" xr3:uid="{83C7ADF5-BFC9-4593-8DC5-4C3E3C16ED71}" name="Classificação" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{75D7101C-1F6F-4866-AE9B-8E1020F00ABA}" name="Transferência" dataDxfId="8" dataCellStyle="Moeda"/>
     <tableColumn id="4" xr3:uid="{6D5478EE-2C1F-4D7A-AA31-67FDC70DDD6E}" name="(R$) Valor" dataCellStyle="Moeda"/>
+    <tableColumn id="5" xr3:uid="{49C1FEB7-BB7F-4941-A01E-990EEBF05392}" name="Coluna1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1760,8 +1946,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{1E04E65A-2485-4589-A796-1A66585BC718}" name="Tabela1356" displayName="Tabela1356" ref="B3:E50" totalsRowShown="0" headerRowDxfId="4">
-  <autoFilter ref="B3:E50" xr:uid="{1E04E65A-2485-4589-A796-1A66585BC718}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{1E04E65A-2485-4589-A796-1A66585BC718}" name="Tabela1356" displayName="Tabela1356" ref="B3:E52" totalsRowShown="0" headerRowDxfId="4">
+  <autoFilter ref="B3:E52" xr:uid="{1E04E65A-2485-4589-A796-1A66585BC718}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{3EF54C17-4CBA-4AE8-9B76-5B5C08E0C878}" name="Data"/>
     <tableColumn id="3" xr3:uid="{AE045E1D-0144-4129-B5E1-6BC6563C07B0}" name="Fornecedor" dataDxfId="3"/>
@@ -2099,57 +2285,57 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{152610B4-81C2-44F7-A8DF-A454E1B8F2ED}">
-  <dimension ref="B1:L105"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:L110"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="15.109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.5546875" customWidth="1"/>
-    <col min="5" max="5" width="15.88671875" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="2.6640625" customWidth="1"/>
-    <col min="7" max="7" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="2.6640625" customWidth="1"/>
-    <col min="9" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.88671875" customWidth="1"/>
+    <col min="1" max="1" width="2.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="29.5703125" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="2.7109375" customWidth="1"/>
+    <col min="7" max="7" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.7109375" customWidth="1"/>
+    <col min="9" max="9" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.85546875" customWidth="1"/>
     <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="C1" s="60">
+    <row r="1" spans="2:12">
+      <c r="C1" s="58">
         <f>SUBTOTAL(9,Tabela1[Qtde])</f>
-        <v>1533</v>
+        <v>1606</v>
       </c>
       <c r="E1" s="12">
         <f>SUBTOTAL(9,Tabela1[(R$) Valor])</f>
-        <v>1150759.95</v>
-      </c>
-    </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="69" t="s">
+        <v>1206212.9100000001</v>
+      </c>
+    </row>
+    <row r="2" spans="2:12">
+      <c r="B2" s="95" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
       <c r="G2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="54" t="s">
+      <c r="I2" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="54" t="s">
+      <c r="J2" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="54" t="s">
+      <c r="K2" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="54" t="s">
+      <c r="L2" s="52" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:12" s="2" customFormat="1">
       <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
@@ -2165,22 +2351,22 @@
       <c r="G3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="56" t="s">
+      <c r="I3" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="55">
+      <c r="J3" s="53">
         <f>E1</f>
-        <v>1150759.95</v>
-      </c>
-      <c r="K3" s="61">
-        <v>1630</v>
-      </c>
-      <c r="L3" s="55">
+        <v>1206212.9100000001</v>
+      </c>
+      <c r="K3" s="59">
+        <v>1704</v>
+      </c>
+      <c r="L3" s="53">
         <f>IFERROR(J3/K3,0)</f>
-        <v>705.9876993865031</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+        <v>707.87142605633812</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12">
       <c r="B4" s="4">
         <v>46113</v>
       </c>
@@ -2197,7 +2383,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12">
       <c r="B5" s="4">
         <v>46113</v>
       </c>
@@ -2214,7 +2400,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12">
       <c r="B6" s="4">
         <v>46113</v>
       </c>
@@ -2231,7 +2417,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12">
       <c r="B7" s="4">
         <v>46113</v>
       </c>
@@ -2248,7 +2434,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12">
       <c r="B8" s="4">
         <v>46113</v>
       </c>
@@ -2265,7 +2451,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12">
       <c r="B9" s="4">
         <v>46114</v>
       </c>
@@ -2282,7 +2468,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12">
       <c r="B10" s="4">
         <v>46114</v>
       </c>
@@ -2299,7 +2485,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12">
       <c r="B11" s="4">
         <v>46114</v>
       </c>
@@ -2313,7 +2499,7 @@
         <v>9293.6299999999992</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12">
       <c r="B12" s="4">
         <v>46114</v>
       </c>
@@ -2327,7 +2513,7 @@
         <v>28799.62</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12">
       <c r="B13" s="4">
         <v>46115</v>
       </c>
@@ -2341,7 +2527,7 @@
         <v>15133.97</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12">
       <c r="B14" s="4">
         <v>46115</v>
       </c>
@@ -2355,7 +2541,7 @@
         <v>6839.16</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12">
       <c r="B15" s="4">
         <v>46115</v>
       </c>
@@ -2369,7 +2555,7 @@
         <v>1410.4</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12">
       <c r="B16" s="4">
         <v>46115</v>
       </c>
@@ -2383,7 +2569,7 @@
         <v>2377.9</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5">
       <c r="B17" s="4">
         <v>46116</v>
       </c>
@@ -2397,7 +2583,7 @@
         <v>590.22</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5">
       <c r="B18" s="4">
         <v>46116</v>
       </c>
@@ -2411,7 +2597,7 @@
         <v>6866.8</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5">
       <c r="B19" s="4">
         <v>46116</v>
       </c>
@@ -2425,7 +2611,7 @@
         <v>32745.85</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5">
       <c r="B20" s="4">
         <v>46116</v>
       </c>
@@ -2439,7 +2625,7 @@
         <v>899.38</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5">
       <c r="B21" s="4">
         <v>46116</v>
       </c>
@@ -2453,7 +2639,7 @@
         <v>753.9</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5">
       <c r="B22" s="4">
         <v>46117</v>
       </c>
@@ -2467,7 +2653,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5">
       <c r="B23" s="4">
         <v>46117</v>
       </c>
@@ -2481,7 +2667,7 @@
         <v>8018.35</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5">
       <c r="B24" s="4">
         <v>46117</v>
       </c>
@@ -2495,7 +2681,7 @@
         <v>23954.81</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5">
       <c r="B25" s="4">
         <v>46117</v>
       </c>
@@ -2509,7 +2695,7 @@
         <v>2301.6999999999998</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:5">
       <c r="B26" s="4">
         <v>46118</v>
       </c>
@@ -2523,7 +2709,7 @@
         <v>951.74</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5">
       <c r="B27" s="4">
         <v>46118</v>
       </c>
@@ -2537,7 +2723,7 @@
         <v>10337.6</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:5">
       <c r="B28" s="4">
         <v>46118</v>
       </c>
@@ -2551,7 +2737,7 @@
         <v>29270.240000000002</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:5">
       <c r="B29" s="4">
         <v>46119</v>
       </c>
@@ -2565,7 +2751,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:5">
       <c r="B30" s="4">
         <v>46119</v>
       </c>
@@ -2579,7 +2765,7 @@
         <v>773.9</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:5">
       <c r="B31" s="4">
         <v>46119</v>
       </c>
@@ -2593,7 +2779,7 @@
         <v>13085.68</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:5">
       <c r="B32" s="4">
         <v>46119</v>
       </c>
@@ -2607,7 +2793,7 @@
         <v>47337.96</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:5">
       <c r="B33" s="4">
         <v>46119</v>
       </c>
@@ -2621,7 +2807,7 @@
         <v>663.5</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:5">
       <c r="B34" s="4">
         <v>46119</v>
       </c>
@@ -2635,7 +2821,7 @@
         <v>6828.1</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:5">
       <c r="B35" s="4">
         <v>46120</v>
       </c>
@@ -2649,7 +2835,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:5">
       <c r="B36" s="4">
         <v>46120</v>
       </c>
@@ -2663,7 +2849,7 @@
         <v>8784.39</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:5">
       <c r="B37" s="4">
         <v>46120</v>
       </c>
@@ -2677,7 +2863,7 @@
         <v>45046.9</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:5">
       <c r="B38" s="4">
         <v>46120</v>
       </c>
@@ -2691,7 +2877,7 @@
         <v>5117.6000000000004</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:5">
       <c r="B39" s="4">
         <v>46121</v>
       </c>
@@ -2705,7 +2891,7 @@
         <v>893.9</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:5">
       <c r="B40" s="4">
         <v>46121</v>
       </c>
@@ -2719,7 +2905,7 @@
         <v>2922.54</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:5">
       <c r="B41" s="4">
         <v>46121</v>
       </c>
@@ -2733,7 +2919,7 @@
         <v>45523.38</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:5">
       <c r="B42" s="4">
         <v>46121</v>
       </c>
@@ -2747,7 +2933,7 @@
         <v>4429.8999999999996</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:5">
       <c r="B43" s="4">
         <v>46122</v>
       </c>
@@ -2761,7 +2947,7 @@
         <v>1591.8</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:5">
       <c r="B44" s="4">
         <v>46122</v>
       </c>
@@ -2775,7 +2961,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:5">
       <c r="B45" s="4">
         <v>46122</v>
       </c>
@@ -2789,7 +2975,7 @@
         <v>2264.6999999999998</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:5">
       <c r="B46" s="4">
         <v>46122</v>
       </c>
@@ -2803,7 +2989,7 @@
         <v>53207.86</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:5">
       <c r="B47" s="4">
         <v>46123</v>
       </c>
@@ -2817,7 +3003,7 @@
         <v>3279.6</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:5">
       <c r="B48" s="4">
         <v>46123</v>
       </c>
@@ -2831,7 +3017,7 @@
         <v>1767.8</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:5">
       <c r="B49" s="4">
         <v>46123</v>
       </c>
@@ -2845,7 +3031,7 @@
         <v>753.9</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:5">
       <c r="B50" s="4">
         <v>46123</v>
       </c>
@@ -2859,7 +3045,7 @@
         <v>55008.160000000003</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:5">
       <c r="B51" s="4">
         <v>46124</v>
       </c>
@@ -2873,7 +3059,7 @@
         <v>2166.7800000000002</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:5">
       <c r="B52" s="4">
         <v>46124</v>
       </c>
@@ -2887,7 +3073,7 @@
         <v>4149.7</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:5">
       <c r="B53" s="4">
         <v>46124</v>
       </c>
@@ -2901,7 +3087,7 @@
         <v>43064.74</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:5">
       <c r="B54" s="4">
         <v>46125</v>
       </c>
@@ -2915,7 +3101,7 @@
         <v>5023.46</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:5">
       <c r="B55" s="4">
         <v>46125</v>
       </c>
@@ -2929,7 +3115,7 @@
         <v>48180.23</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:5">
       <c r="B56" s="4">
         <v>46125</v>
       </c>
@@ -2943,7 +3129,7 @@
         <v>2529.8000000000002</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:5">
       <c r="B57" s="4">
         <v>46126</v>
       </c>
@@ -2957,7 +3143,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:5">
       <c r="B58" s="4">
         <v>46126</v>
       </c>
@@ -2971,7 +3157,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:5">
       <c r="B59" s="4">
         <v>46126</v>
       </c>
@@ -2985,7 +3171,7 @@
         <v>5707</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:5">
       <c r="B60" s="4">
         <v>46126</v>
       </c>
@@ -2999,7 +3185,7 @@
         <v>24605</v>
       </c>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:5">
       <c r="B61" s="4">
         <v>46126</v>
       </c>
@@ -3013,7 +3199,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:5">
       <c r="B62" s="4">
         <v>46127</v>
       </c>
@@ -3027,7 +3213,7 @@
         <v>2388.38</v>
       </c>
     </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:5">
       <c r="B63" s="4">
         <v>46127</v>
       </c>
@@ -3041,7 +3227,7 @@
         <v>49270.34</v>
       </c>
     </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:5">
       <c r="B64" s="4">
         <v>46127</v>
       </c>
@@ -3055,7 +3241,7 @@
         <v>923.49</v>
       </c>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:5">
       <c r="B65" s="4">
         <v>46127</v>
       </c>
@@ -3069,7 +3255,7 @@
         <v>3091.9</v>
       </c>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:5">
       <c r="B66" s="4">
         <v>46127</v>
       </c>
@@ -3083,7 +3269,7 @@
         <v>2037.9</v>
       </c>
     </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:5">
       <c r="B67" s="4">
         <v>46128</v>
       </c>
@@ -3097,7 +3283,7 @@
         <v>1727.8</v>
       </c>
     </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:5">
       <c r="B68" s="4">
         <v>46128</v>
       </c>
@@ -3111,7 +3297,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:5">
       <c r="B69" s="4">
         <v>46128</v>
       </c>
@@ -3125,7 +3311,7 @@
         <v>4734.04</v>
       </c>
     </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:5">
       <c r="B70" s="4">
         <v>46128</v>
       </c>
@@ -3139,7 +3325,7 @@
         <v>42282.67</v>
       </c>
     </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:5">
       <c r="B71" s="4">
         <v>46129</v>
       </c>
@@ -3153,7 +3339,7 @@
         <v>880.2</v>
       </c>
     </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:5">
       <c r="B72" s="4">
         <v>46129</v>
       </c>
@@ -3167,7 +3353,7 @@
         <v>2240.2600000000002</v>
       </c>
     </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:5">
       <c r="B73" s="4">
         <v>46129</v>
       </c>
@@ -3181,7 +3367,7 @@
         <v>37764</v>
       </c>
     </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:5">
       <c r="B74" s="4">
         <v>46129</v>
       </c>
@@ -3195,7 +3381,7 @@
         <v>713.9</v>
       </c>
     </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:5">
       <c r="B75" s="4">
         <v>46130</v>
       </c>
@@ -3209,7 +3395,7 @@
         <v>5175.68</v>
       </c>
     </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:5">
       <c r="B76" s="4">
         <v>46130</v>
       </c>
@@ -3223,7 +3409,7 @@
         <v>29981.46</v>
       </c>
     </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:5">
       <c r="B77" s="4">
         <v>46130</v>
       </c>
@@ -3237,7 +3423,7 @@
         <v>623.9</v>
       </c>
     </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:5">
       <c r="B78" s="4">
         <v>46131</v>
       </c>
@@ -3251,7 +3437,7 @@
         <v>3275</v>
       </c>
     </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:5">
       <c r="B79" s="4">
         <v>46131</v>
       </c>
@@ -3265,7 +3451,7 @@
         <v>1486.72</v>
       </c>
     </row>
-    <row r="80" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:5">
       <c r="B80" s="4">
         <v>46131</v>
       </c>
@@ -3279,7 +3465,7 @@
         <v>24359.4</v>
       </c>
     </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:5">
       <c r="B81" s="4">
         <v>46131</v>
       </c>
@@ -3293,7 +3479,7 @@
         <v>733.9</v>
       </c>
     </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:5">
       <c r="B82" s="4">
         <v>46132</v>
       </c>
@@ -3307,7 +3493,7 @@
         <v>4190.3599999999997</v>
       </c>
     </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:5">
       <c r="B83" s="4">
         <v>46132</v>
       </c>
@@ -3321,7 +3507,7 @@
         <v>37618.129999999997</v>
       </c>
     </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:5">
       <c r="B84" s="4">
         <v>46132</v>
       </c>
@@ -3335,7 +3521,7 @@
         <v>4079.5</v>
       </c>
     </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:5">
       <c r="B85" s="4">
         <v>46133</v>
       </c>
@@ -3349,7 +3535,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:5">
       <c r="B86" s="4">
         <v>46133</v>
       </c>
@@ -3363,7 +3549,7 @@
         <v>743.85</v>
       </c>
     </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:5">
       <c r="B87" s="4">
         <v>46133</v>
       </c>
@@ -3377,7 +3563,7 @@
         <v>4336.0200000000004</v>
       </c>
     </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:5">
       <c r="B88" s="4">
         <v>46133</v>
       </c>
@@ -3391,7 +3577,7 @@
         <v>22422.71</v>
       </c>
     </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:5">
       <c r="B89" s="4">
         <v>46133</v>
       </c>
@@ -3405,7 +3591,7 @@
         <v>1876.1</v>
       </c>
     </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:5">
       <c r="B90" s="4">
         <v>46134</v>
       </c>
@@ -3419,7 +3605,7 @@
         <v>2106.98</v>
       </c>
     </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:5">
       <c r="B91" s="4">
         <v>46134</v>
       </c>
@@ -3433,7 +3619,7 @@
         <v>86913.33</v>
       </c>
     </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:5">
       <c r="B92" s="4">
         <v>46134</v>
       </c>
@@ -3447,7 +3633,7 @@
         <v>2801.7</v>
       </c>
     </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:5">
       <c r="B93" s="4">
         <v>46135</v>
       </c>
@@ -3461,7 +3647,7 @@
         <v>825.9</v>
       </c>
     </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:5">
       <c r="B94" s="4">
         <v>46135</v>
       </c>
@@ -3475,7 +3661,7 @@
         <v>27646.44</v>
       </c>
     </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:5">
       <c r="B95" s="4">
         <v>46135</v>
       </c>
@@ -3489,7 +3675,7 @@
         <v>4102.1000000000004</v>
       </c>
     </row>
-    <row r="96" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:5">
       <c r="B96" s="4">
         <v>46136</v>
       </c>
@@ -3503,7 +3689,7 @@
         <v>1347.8</v>
       </c>
     </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:5">
       <c r="B97" s="4">
         <v>46136</v>
       </c>
@@ -3517,7 +3703,7 @@
         <v>739.9</v>
       </c>
     </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:5">
       <c r="B98" s="4">
         <v>46136</v>
       </c>
@@ -3531,7 +3717,7 @@
         <v>1595.88</v>
       </c>
     </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:5">
       <c r="B99" s="4">
         <v>46136</v>
       </c>
@@ -3545,7 +3731,7 @@
         <v>15251.65</v>
       </c>
     </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:5">
       <c r="B100" s="4">
         <v>46137</v>
       </c>
@@ -3559,7 +3745,7 @@
         <v>539.12</v>
       </c>
     </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:5">
       <c r="B101" s="4">
         <v>46137</v>
       </c>
@@ -3573,7 +3759,7 @@
         <v>22818.080000000002</v>
       </c>
     </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:5">
       <c r="B102" s="4">
         <v>46137</v>
       </c>
@@ -3587,7 +3773,7 @@
         <v>2348</v>
       </c>
     </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:5">
       <c r="B103" s="4">
         <v>46138</v>
       </c>
@@ -3601,7 +3787,7 @@
         <v>2299.08</v>
       </c>
     </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:5">
       <c r="B104" s="4">
         <v>46138</v>
       </c>
@@ -3615,7 +3801,7 @@
         <v>25019.45</v>
       </c>
     </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:5">
       <c r="B105" s="4">
         <v>46138</v>
       </c>
@@ -3627,14 +3813,84 @@
       </c>
       <c r="E105" s="6">
         <v>743.9</v>
+      </c>
+    </row>
+    <row r="106" spans="2:5">
+      <c r="B106" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C106" s="1">
+        <v>1</v>
+      </c>
+      <c r="D106" t="s">
+        <v>10</v>
+      </c>
+      <c r="E106" s="6">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="107" spans="2:5">
+      <c r="B107" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C107" s="1">
+        <v>1</v>
+      </c>
+      <c r="D107" t="s">
+        <v>13</v>
+      </c>
+      <c r="E107" s="6">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="108" spans="2:5">
+      <c r="B108" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C108" s="1">
+        <v>65</v>
+      </c>
+      <c r="D108" t="s">
+        <v>14</v>
+      </c>
+      <c r="E108" s="6">
+        <v>49413.87</v>
+      </c>
+    </row>
+    <row r="109" spans="2:5">
+      <c r="B109" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C109" s="1">
+        <v>2</v>
+      </c>
+      <c r="D109" t="s">
+        <v>15</v>
+      </c>
+      <c r="E109" s="6">
+        <v>858.49</v>
+      </c>
+    </row>
+    <row r="110" spans="2:5">
+      <c r="B110" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C110" s="1">
+        <v>4</v>
+      </c>
+      <c r="D110" t="s">
+        <v>16</v>
+      </c>
+      <c r="E110" s="6">
+        <v>3095.6</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:E2"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D107" xr:uid="{A625BF53-AEF2-4343-98C8-03A2E1A9920C}">
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D111" xr:uid="{A625BF53-AEF2-4343-98C8-03A2E1A9920C}">
       <formula1>$G$3:$G$10</formula1>
     </dataValidation>
   </dataValidations>
@@ -3649,313 +3905,397 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D51AF1E-9915-47D4-8A4E-D08B404C994F}">
-  <dimension ref="B1:L58"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:P65"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="60.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.109375" customWidth="1"/>
-    <col min="8" max="8" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="60.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.140625" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="3.6640625" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.7109375" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.140625" customWidth="1"/>
+    <col min="16" max="16" width="18.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:16">
       <c r="F1" s="12">
         <f>SUBTOTAL(9,Tabela135[(R$) Valor])</f>
-        <v>814152.59</v>
-      </c>
-    </row>
-    <row r="2" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B2" s="69" t="s">
+        <v>852200.21</v>
+      </c>
+    </row>
+    <row r="2" spans="2:16">
+      <c r="B2" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="H2" s="70" t="s">
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="H2" s="96" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="71"/>
-      <c r="J2" s="72"/>
-      <c r="L2" s="10" t="s">
+      <c r="I2" s="97"/>
+      <c r="J2" s="98"/>
+      <c r="L2" s="96" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="97"/>
+      <c r="N2" s="98"/>
+      <c r="P2" s="10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:16">
       <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H3" s="18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I3" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="18" t="s">
+      <c r="M3" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="N3" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="P3" s="8" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:16">
       <c r="B4" s="4">
         <v>46114</v>
       </c>
       <c r="C4" s="47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" s="6">
         <v>20435</v>
       </c>
-      <c r="H4" s="67">
+      <c r="H4" s="65">
         <v>46030</v>
       </c>
-      <c r="I4" s="20">
+      <c r="I4" s="86">
         <v>1021.54</v>
       </c>
-      <c r="J4" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="L4" s="9" t="s">
+      <c r="J4" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="71">
+        <v>46118</v>
+      </c>
+      <c r="M4" s="86">
+        <v>655</v>
+      </c>
+      <c r="N4" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="P4" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:16">
       <c r="B5" s="4">
         <v>46118</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F5" s="6">
         <v>13502</v>
       </c>
-      <c r="H5" s="68">
+      <c r="H5" s="66">
         <v>46042</v>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="87">
         <v>26000</v>
       </c>
-      <c r="J5" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="L5" s="8" t="s">
+      <c r="J5" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" s="74">
+        <v>46129</v>
+      </c>
+      <c r="M5" s="93">
+        <v>2214.86</v>
+      </c>
+      <c r="N5" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="P5" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:16">
       <c r="B6" s="4">
         <v>46118</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F6" s="6">
         <v>82.59</v>
       </c>
-      <c r="H6" s="67">
+      <c r="H6" s="65">
         <v>46051</v>
       </c>
-      <c r="I6" s="20">
+      <c r="I6" s="86">
         <v>6559</v>
       </c>
-      <c r="J6" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="L6" s="9" t="s">
+      <c r="J6" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6" s="76">
+        <v>46129</v>
+      </c>
+      <c r="M6" s="86">
+        <v>490.83</v>
+      </c>
+      <c r="N6" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="P6" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:16">
       <c r="B7" s="4">
         <v>46118</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F7" s="6">
         <v>266.32</v>
       </c>
-      <c r="H7" s="68">
+      <c r="H7" s="66">
         <v>46087</v>
       </c>
-      <c r="I7" s="17">
+      <c r="I7" s="87">
         <v>14000</v>
       </c>
-      <c r="J7" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="L7" s="8" t="s">
+      <c r="J7" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="L7" s="74">
+        <v>46129</v>
+      </c>
+      <c r="M7" s="93">
+        <v>1330.36</v>
+      </c>
+      <c r="N7" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="P7" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:16">
       <c r="B8" s="4">
         <v>46118</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F8" s="6">
         <v>0</v>
       </c>
-      <c r="H8" s="67">
+      <c r="H8" s="65">
         <v>46090</v>
       </c>
-      <c r="I8" s="20">
+      <c r="I8" s="86">
         <v>24200</v>
       </c>
-      <c r="J8" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="L8" s="9" t="s">
+      <c r="J8" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="L8" s="71">
+        <v>46140</v>
+      </c>
+      <c r="M8" s="86">
+        <v>655.17999999999995</v>
+      </c>
+      <c r="N8" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="P8" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:16">
       <c r="B9" s="4">
         <v>46118</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F9" s="6">
         <v>46650</v>
       </c>
-      <c r="H9" s="68">
+      <c r="H9" s="66">
         <v>46119</v>
       </c>
-      <c r="I9" s="17">
+      <c r="I9" s="87">
         <v>3200</v>
       </c>
-      <c r="J9" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="L9" s="8" t="s">
+      <c r="J9" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="L9" s="74">
+        <v>46140</v>
+      </c>
+      <c r="M9" s="93">
+        <v>1767.85</v>
+      </c>
+      <c r="N9" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="P9" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:16">
       <c r="B10" s="4">
         <v>46119</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F10" s="6">
         <v>542.97</v>
       </c>
-      <c r="H10" s="67">
+      <c r="H10" s="65">
         <v>46122</v>
       </c>
-      <c r="I10" s="20">
+      <c r="I10" s="86">
         <v>2000</v>
       </c>
-      <c r="J10" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="L10" s="11" t="s">
+      <c r="J10" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="L10" s="71">
+        <v>46140</v>
+      </c>
+      <c r="M10" s="86">
+        <v>2854</v>
+      </c>
+      <c r="N10" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="P10" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:16">
       <c r="B11" s="4">
         <v>46119</v>
       </c>
       <c r="C11" s="47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F11" s="6">
         <v>50000</v>
       </c>
-      <c r="H11" s="68">
+      <c r="H11" s="66">
         <v>46129</v>
       </c>
-      <c r="I11" s="17">
+      <c r="I11" s="87">
         <v>4300</v>
       </c>
-      <c r="J11" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="J11" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="L11" s="72"/>
+      <c r="M11" s="93"/>
+      <c r="N11" s="23"/>
+      <c r="P11" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16">
       <c r="B12" s="4">
         <v>46119</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>13</v>
@@ -3963,388 +4303,445 @@
       <c r="F12" s="6">
         <v>3200</v>
       </c>
-      <c r="H12" s="67">
+      <c r="H12" s="65">
         <v>46132</v>
       </c>
-      <c r="I12" s="41">
+      <c r="I12" s="88">
         <v>4825</v>
       </c>
-      <c r="J12" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="L12" s="11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="J12" s="67" t="s">
+        <v>30</v>
+      </c>
+      <c r="L12" s="71"/>
+      <c r="M12" s="86"/>
+      <c r="N12" s="67"/>
+      <c r="P12" s="11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16">
       <c r="B13" s="4">
         <v>46120</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F13" s="6">
         <v>350</v>
       </c>
-      <c r="H13" s="68">
+      <c r="H13" s="66">
         <v>46134</v>
       </c>
-      <c r="I13" s="50">
+      <c r="I13" s="89">
         <v>10000</v>
       </c>
-      <c r="J13" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="J13" s="62" t="s">
+        <v>29</v>
+      </c>
+      <c r="L13" s="72"/>
+      <c r="M13" s="94"/>
+      <c r="N13" s="62"/>
+      <c r="P13" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16">
       <c r="B14" s="4">
         <v>46120</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F14" s="6">
         <v>24769</v>
       </c>
-      <c r="H14" s="67">
+      <c r="H14" s="65">
         <v>46134</v>
       </c>
-      <c r="I14" s="41">
+      <c r="I14" s="88">
         <v>22000</v>
       </c>
-      <c r="J14" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="L14" s="11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="J14" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="L14" s="71"/>
+      <c r="M14" s="86"/>
+      <c r="N14" s="22"/>
+      <c r="P14" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16">
       <c r="B15" s="4">
         <v>46121</v>
       </c>
       <c r="C15" s="47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F15" s="6">
         <v>469.86</v>
       </c>
-      <c r="H15" s="68">
+      <c r="H15" s="66">
         <v>46137</v>
       </c>
-      <c r="I15" s="50">
+      <c r="I15" s="89">
         <v>10000</v>
       </c>
-      <c r="J15" s="51" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="J15" s="62" t="s">
+        <v>30</v>
+      </c>
+      <c r="L15" s="72"/>
+      <c r="M15" s="93"/>
+      <c r="N15" s="62"/>
+    </row>
+    <row r="16" spans="2:16">
       <c r="B16" s="4">
         <v>46121</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F16" s="6">
         <v>50000</v>
       </c>
-      <c r="H16" s="67">
+      <c r="H16" s="70">
         <v>46137</v>
       </c>
-      <c r="I16" s="20">
+      <c r="I16" s="88">
         <v>7770</v>
       </c>
-      <c r="J16" s="21" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="J16" s="67" t="s">
+        <v>29</v>
+      </c>
+      <c r="L16" s="73"/>
+      <c r="M16" s="86"/>
+      <c r="N16" s="67"/>
+    </row>
+    <row r="17" spans="2:14">
       <c r="B17" s="4">
         <v>46122</v>
       </c>
       <c r="C17" s="47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F17" s="6">
         <v>2290.2800000000002</v>
       </c>
-    </row>
-    <row r="18" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="H17" s="70">
+        <v>46139</v>
+      </c>
+      <c r="I17" s="90">
+        <v>5200</v>
+      </c>
+      <c r="J17" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="L17" s="77"/>
+      <c r="M17" s="93"/>
+      <c r="N17" s="79"/>
+    </row>
+    <row r="18" spans="2:14">
       <c r="B18" s="4">
         <v>46122</v>
       </c>
       <c r="C18" s="47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F18" s="6">
         <v>479.72</v>
       </c>
-    </row>
-    <row r="19" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="H18" s="21"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="L18" s="21"/>
+      <c r="M18" s="86"/>
+      <c r="N18" s="22"/>
+    </row>
+    <row r="19" spans="2:14">
       <c r="B19" s="4">
         <v>46122</v>
       </c>
       <c r="C19" s="47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E19" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F19" s="6">
         <v>2690.03</v>
       </c>
-      <c r="H19" t="s">
-        <v>26</v>
-      </c>
-      <c r="I19" s="52">
-        <f>SUMIF(C:C,H19,F:F)</f>
-        <v>769827.59</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="H19" s="15"/>
+      <c r="I19" s="91"/>
+      <c r="J19" s="23"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="93"/>
+      <c r="N19" s="23"/>
+    </row>
+    <row r="20" spans="2:14">
       <c r="B20" s="4">
         <v>46122</v>
       </c>
       <c r="C20" s="47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F20" s="6">
         <v>2476.36</v>
       </c>
-      <c r="H20" t="s">
-        <v>36</v>
-      </c>
-      <c r="I20" s="52">
-        <f>SUMIF(C:C,H20,F:F)</f>
-        <v>44325</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="H20" s="21"/>
+      <c r="I20" s="92"/>
+      <c r="J20" s="22"/>
+      <c r="L20" s="21"/>
+      <c r="M20" s="86"/>
+      <c r="N20" s="22"/>
+    </row>
+    <row r="21" spans="2:14">
       <c r="B21" s="4">
         <v>46122</v>
       </c>
       <c r="C21" s="47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F21" s="6">
         <v>140</v>
       </c>
-      <c r="I21" s="52">
-        <f>I19+I20</f>
-        <v>814152.59</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="H21" s="15"/>
+      <c r="I21" s="91"/>
+      <c r="J21" s="23"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="93"/>
+      <c r="N21" s="23"/>
+    </row>
+    <row r="22" spans="2:14">
       <c r="B22" s="4">
         <v>46125</v>
       </c>
       <c r="C22" s="47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F22" s="6">
         <v>24850</v>
       </c>
-    </row>
-    <row r="23" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="H22" s="21"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="L22" s="21"/>
+      <c r="M22" s="86"/>
+      <c r="N22" s="22"/>
+    </row>
+    <row r="23" spans="2:14">
       <c r="B23" s="4">
         <v>46125</v>
       </c>
       <c r="C23" s="47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F23" s="6">
         <v>256.14</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:14">
       <c r="B24" s="4">
         <v>46125</v>
       </c>
       <c r="C24" s="47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F24" s="6">
         <v>27884</v>
       </c>
     </row>
-    <row r="25" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:14">
       <c r="B25" s="4">
         <v>46126</v>
       </c>
       <c r="C25" s="47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F25" s="6">
         <v>707.92</v>
       </c>
-    </row>
-    <row r="26" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="H25" t="s">
+        <v>27</v>
+      </c>
+      <c r="I25" s="50">
+        <f>SUMIF(C:C,H25,F:F)</f>
+        <v>797907.13</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14">
       <c r="B26" s="4">
         <v>46127</v>
       </c>
       <c r="C26" s="47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F26" s="6">
         <v>50000</v>
       </c>
-    </row>
-    <row r="27" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="H26" t="s">
+        <v>37</v>
+      </c>
+      <c r="I26" s="50">
+        <f>SUMIF(C:C,H26,F:F)</f>
+        <v>54293.08</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14">
       <c r="B27" s="4">
         <v>46128</v>
       </c>
       <c r="C27" s="47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F27" s="6">
         <v>82039</v>
       </c>
-    </row>
-    <row r="28" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="I27" s="50">
+        <f>I25+I26</f>
+        <v>852200.21</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14">
       <c r="B28" s="4">
         <v>46128</v>
       </c>
       <c r="C28" s="47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F28" s="6">
         <v>30409</v>
       </c>
     </row>
-    <row r="29" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:14">
       <c r="B29" s="4">
         <v>46128</v>
       </c>
       <c r="C29" s="47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E29" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F29" s="6">
         <v>641.91999999999996</v>
       </c>
     </row>
-    <row r="30" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:14" ht="15" customHeight="1">
       <c r="B30" s="4">
         <v>46129</v>
       </c>
       <c r="C30" s="47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F30" s="6">
         <v>42189</v>
       </c>
     </row>
-    <row r="31" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:14" ht="15" customHeight="1">
       <c r="B31" s="4">
         <v>46129</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>13</v>
@@ -4353,168 +4750,168 @@
         <v>4300</v>
       </c>
     </row>
-    <row r="32" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:14" ht="15" customHeight="1">
       <c r="B32" s="4">
         <v>46132</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E32" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F32" s="6">
         <v>5771.86</v>
       </c>
       <c r="G32" s="48"/>
     </row>
-    <row r="33" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:7" ht="15" customHeight="1">
       <c r="B33" s="4">
         <v>46132</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E33" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F33" s="6">
         <v>751.55</v>
       </c>
       <c r="G33" s="48"/>
     </row>
-    <row r="34" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:7" ht="15" customHeight="1">
       <c r="B34" s="4">
         <v>46132</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E34" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F34" s="6">
         <v>8083.68</v>
       </c>
     </row>
-    <row r="35" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:7" ht="15" customHeight="1">
       <c r="B35" s="4">
         <v>46132</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E35" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F35" s="6">
         <v>1312.2</v>
       </c>
     </row>
-    <row r="36" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:7" ht="15" customHeight="1">
       <c r="B36" s="4">
         <v>46132</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E36" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F36" s="6">
         <v>678.51</v>
       </c>
     </row>
-    <row r="37" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:7" ht="15" customHeight="1">
       <c r="B37" s="4">
         <v>46132</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E37" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F37" s="6">
         <v>616.95000000000005</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:7" ht="15" customHeight="1">
       <c r="B38" s="4">
         <v>46132</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E38" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F38" s="6">
         <v>553.13</v>
       </c>
     </row>
-    <row r="39" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:7" ht="15" customHeight="1">
       <c r="B39" s="4">
         <v>46132</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F39" s="6">
         <v>1451.48</v>
       </c>
       <c r="G39" s="49"/>
     </row>
-    <row r="40" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:7" ht="15" customHeight="1">
       <c r="B40" s="4">
         <v>46132</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E40" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F40" s="6">
         <v>31934</v>
       </c>
     </row>
-    <row r="41" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:7" ht="15" customHeight="1">
       <c r="B41" s="4">
         <v>46132</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>13</v>
@@ -4523,63 +4920,63 @@
         <v>4825</v>
       </c>
     </row>
-    <row r="42" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:7" ht="15" customHeight="1">
       <c r="B42" s="4">
         <v>46134</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E42" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F42" s="6">
         <v>81158.12</v>
       </c>
     </row>
-    <row r="43" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:7" ht="15" customHeight="1">
       <c r="B43" s="4">
         <v>46134</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E43" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F43" s="6">
         <v>10000</v>
       </c>
     </row>
-    <row r="44" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:7" ht="15" customHeight="1">
       <c r="B44" s="4">
         <v>46134</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E44" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F44" s="6">
         <v>50000</v>
       </c>
     </row>
-    <row r="45" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:7" ht="15" customHeight="1">
       <c r="B45" s="4">
         <v>46134</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>13</v>
@@ -4588,180 +4985,314 @@
         <v>22000</v>
       </c>
     </row>
-    <row r="46" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:7" ht="15" customHeight="1">
       <c r="B46" s="4">
         <v>46135</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E46" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F46" s="6">
         <v>4563</v>
       </c>
     </row>
-    <row r="47" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:7" ht="15" customHeight="1">
       <c r="B47" s="4">
         <v>46135</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E47" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F47" s="6">
         <v>350</v>
       </c>
     </row>
-    <row r="48" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:7" ht="15" customHeight="1">
       <c r="B48" s="4">
         <v>46135</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E48" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F48" s="6">
         <v>50000</v>
       </c>
     </row>
-    <row r="49" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:6" ht="15" customHeight="1">
       <c r="B49" s="4">
         <v>46136</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E49" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F49" s="6">
         <v>23554</v>
       </c>
     </row>
-    <row r="50" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:6" ht="15" customHeight="1">
       <c r="B50" s="4">
         <v>46136</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D50" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="D50" s="60" t="s">
         <v>14</v>
       </c>
       <c r="E50" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F50" s="6">
         <v>16908</v>
       </c>
     </row>
-    <row r="51" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:6" ht="15" customHeight="1">
       <c r="B51" s="4">
         <v>46137</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D51" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D51" s="61" t="s">
         <v>13</v>
       </c>
       <c r="F51" s="6">
         <v>10000</v>
       </c>
     </row>
-    <row r="52" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:6" ht="15" customHeight="1">
       <c r="B52" s="4">
         <v>46139</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D52" s="63"/>
+        <v>27</v>
+      </c>
+      <c r="D52" s="60"/>
       <c r="E52" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F52" s="6">
         <v>250</v>
       </c>
     </row>
-    <row r="53" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:6" ht="15" customHeight="1">
       <c r="B53" s="4">
         <v>46139</v>
       </c>
-      <c r="C53" s="65" t="s">
-        <v>26</v>
-      </c>
-      <c r="D53" s="1" t="s">
+      <c r="C53" s="62" t="s">
+        <v>27</v>
+      </c>
+      <c r="D53" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="E53" t="s">
+        <v>28</v>
+      </c>
+      <c r="F53" s="63">
+        <v>7770</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6" ht="15" customHeight="1">
+      <c r="B54" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C54" s="67" t="s">
+        <v>27</v>
+      </c>
+      <c r="D54" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="E54" t="s">
+        <v>44</v>
+      </c>
+      <c r="F54" s="68">
+        <v>1456.54</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6" ht="15" customHeight="1">
+      <c r="B55" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C55" s="62" t="s">
+        <v>27</v>
+      </c>
+      <c r="D55" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="F53" s="66">
-        <v>7770</v>
-      </c>
-    </row>
-    <row r="54" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="21"/>
-      <c r="C54" s="22"/>
-      <c r="D54" s="22"/>
-      <c r="E54" s="21"/>
-      <c r="F54" s="64"/>
-    </row>
-    <row r="55" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="15"/>
-      <c r="C55" s="23"/>
-      <c r="D55" s="23"/>
-      <c r="E55" s="15"/>
-      <c r="F55" s="62"/>
-    </row>
-    <row r="56" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="21"/>
-      <c r="C56" s="22"/>
-      <c r="D56" s="22"/>
-      <c r="E56" s="21"/>
-      <c r="F56" s="64"/>
-    </row>
-    <row r="57" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="15"/>
-      <c r="C57" s="23"/>
-      <c r="D57" s="23"/>
-      <c r="E57" s="15"/>
-      <c r="F57" s="62"/>
-    </row>
-    <row r="58" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="21"/>
-      <c r="C58" s="22"/>
-      <c r="D58" s="22"/>
-      <c r="E58" s="21"/>
-      <c r="F58" s="64"/>
+      <c r="E55" t="s">
+        <v>28</v>
+      </c>
+      <c r="F55" s="63">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6" ht="15" customHeight="1">
+      <c r="B56" s="4">
+        <v>46140</v>
+      </c>
+      <c r="C56" s="67" t="s">
+        <v>27</v>
+      </c>
+      <c r="D56" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="E56" t="s">
+        <v>53</v>
+      </c>
+      <c r="F56" s="68">
+        <v>21423</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6" ht="15" customHeight="1">
+      <c r="B57" s="74">
+        <v>46118</v>
+      </c>
+      <c r="C57" s="69" t="s">
+        <v>37</v>
+      </c>
+      <c r="D57" s="61" t="s">
+        <v>10</v>
+      </c>
+      <c r="E57" s="78"/>
+      <c r="F57" s="75">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6" ht="15" customHeight="1">
+      <c r="B58" s="74">
+        <v>46129</v>
+      </c>
+      <c r="C58" s="69" t="s">
+        <v>37</v>
+      </c>
+      <c r="D58" s="61" t="s">
+        <v>10</v>
+      </c>
+      <c r="E58" s="78"/>
+      <c r="F58" s="75">
+        <v>2214.86</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" ht="15" customHeight="1">
+      <c r="B59" s="74">
+        <v>46129</v>
+      </c>
+      <c r="C59" s="69" t="s">
+        <v>37</v>
+      </c>
+      <c r="D59" s="61" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59" s="78"/>
+      <c r="F59" s="75">
+        <v>490.83</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" ht="15" customHeight="1">
+      <c r="B60" s="72">
+        <v>46129</v>
+      </c>
+      <c r="C60" s="62" t="s">
+        <v>37</v>
+      </c>
+      <c r="D60" s="60" t="s">
+        <v>10</v>
+      </c>
+      <c r="F60" s="75">
+        <v>1330.36</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" ht="15" customHeight="1">
+      <c r="B61" s="74">
+        <v>46140</v>
+      </c>
+      <c r="C61" s="69" t="s">
+        <v>37</v>
+      </c>
+      <c r="D61" s="61" t="s">
+        <v>10</v>
+      </c>
+      <c r="E61" s="78"/>
+      <c r="F61" s="75">
+        <v>655.17999999999995</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6" ht="15" customHeight="1">
+      <c r="B62" s="72">
+        <v>46140</v>
+      </c>
+      <c r="C62" s="62" t="s">
+        <v>37</v>
+      </c>
+      <c r="D62" s="60" t="s">
+        <v>10</v>
+      </c>
+      <c r="F62" s="17">
+        <v>1767.85</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6" ht="15" customHeight="1">
+      <c r="B63" s="74">
+        <v>46140</v>
+      </c>
+      <c r="C63" s="69" t="s">
+        <v>37</v>
+      </c>
+      <c r="D63" s="61" t="s">
+        <v>10</v>
+      </c>
+      <c r="E63" s="78"/>
+      <c r="F63" s="75">
+        <v>2854</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6" ht="15" customHeight="1">
+      <c r="B64" s="80"/>
+      <c r="C64" s="81"/>
+      <c r="D64" s="82"/>
+      <c r="E64" s="80"/>
+      <c r="F64" s="83"/>
+    </row>
+    <row r="65" spans="2:6" ht="15" customHeight="1">
+      <c r="B65" s="84"/>
+      <c r="C65" s="69"/>
+      <c r="D65" s="69"/>
+      <c r="E65" s="84"/>
+      <c r="F65" s="85"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="H2:J2"/>
+    <mergeCell ref="L2:N2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D14 D16:D30 D33:D52" xr:uid="{D4BB0447-AF3D-4F86-9822-6839F011C631}">
-      <formula1>$L$3:$L$14</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D14 D16:D30 D33:D63" xr:uid="{D4BB0447-AF3D-4F86-9822-6839F011C631}">
+      <formula1>$P$3:$P$14</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -4774,180 +5305,187 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9163483-898B-48DF-A920-0A4DCD53730D}">
-  <dimension ref="B1:H198"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:H224"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.5546875" style="43" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.88671875" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" customWidth="1"/>
+    <col min="1" max="1" width="2.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.5703125" style="43" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.7109375" customWidth="1"/>
     <col min="8" max="8" width="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="2.6640625" customWidth="1"/>
+    <col min="9" max="9" width="2.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="D1" s="57">
+    <row r="1" spans="2:8">
+      <c r="D1" s="55">
         <f>SUM(E1:F1)</f>
-        <v>664406.19999999972</v>
-      </c>
-      <c r="E1" s="58">
+        <v>774125.41999999969</v>
+      </c>
+      <c r="E1" s="56">
         <f>SUBTOTAL(9,Tabela13[Transferência])</f>
         <v>41100</v>
       </c>
-      <c r="F1" s="58">
+      <c r="F1" s="56">
         <f>SUBTOTAL(9,Tabela13[(R$) Valor])</f>
-        <v>623306.19999999972</v>
-      </c>
-    </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="69" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
+        <v>733025.41999999969</v>
+      </c>
+      <c r="H1" s="101">
+        <f>993810.43-F1</f>
+        <v>260785.01000000036</v>
+      </c>
+    </row>
+    <row r="2" spans="2:8" ht="15" customHeight="1">
+      <c r="B2" s="95" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
       <c r="G2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8">
       <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>9</v>
       </c>
+      <c r="G3" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="H3" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="14.45">
       <c r="B4" s="4">
         <v>46113</v>
       </c>
       <c r="C4" s="43" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D4" s="43" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F4" s="6">
         <v>1440</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="14.45">
       <c r="B5" s="4">
         <v>46113</v>
       </c>
       <c r="C5" s="43" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D5" s="43" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F5" s="6">
         <v>153.66</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="14.45">
       <c r="B6" s="4">
         <v>46113</v>
       </c>
       <c r="C6" s="43" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D6" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F6" s="6">
         <v>2911.3</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="14.45">
       <c r="B7" s="4">
         <v>46113</v>
       </c>
       <c r="C7" s="43" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D7" s="43" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F7" s="6">
         <v>64.39</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="14.45">
       <c r="B8" s="4">
         <v>46113</v>
       </c>
       <c r="C8" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="43" t="s">
         <v>69</v>
-      </c>
-      <c r="D8" s="43" t="s">
-        <v>66</v>
       </c>
       <c r="F8" s="6">
         <v>930.1</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="14.45">
       <c r="B9" s="4">
         <v>46113</v>
       </c>
       <c r="C9" s="43" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" s="43" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F9" s="6">
         <v>102.92</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" ht="14.45">
       <c r="B10" s="4">
         <v>46113</v>
       </c>
       <c r="C10" s="43" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" s="43" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E10" s="6">
         <v>2100</v>
@@ -4956,562 +5494,562 @@
         <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" ht="14.45">
       <c r="B11" s="4">
         <v>46113</v>
       </c>
       <c r="C11" s="43" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" s="43" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F11" s="6">
         <v>140.53</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" ht="14.45">
       <c r="B12" s="4">
         <v>46114</v>
       </c>
       <c r="C12" s="43" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D12" s="43" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F12" s="6">
         <v>2039.26</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" ht="14.45">
       <c r="B13" s="4">
         <v>46114</v>
       </c>
       <c r="C13" s="43" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D13" s="43" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F13" s="6">
         <v>135</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" ht="14.45">
       <c r="B14" s="4">
         <v>46114</v>
       </c>
       <c r="C14" s="43" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D14" s="43" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F14" s="6">
         <v>1490</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" ht="14.45">
       <c r="B15" s="4">
         <v>46114</v>
       </c>
       <c r="C15" s="43" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D15" s="43" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F15" s="6">
         <v>176.6</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" ht="14.45">
       <c r="B16" s="4">
         <v>46114</v>
       </c>
       <c r="C16" s="43" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D16" s="43" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F16" s="6">
         <v>400</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="14.45">
       <c r="B17" s="4">
         <v>46114</v>
       </c>
       <c r="C17" s="43" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D17" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F17" s="6">
         <v>19184.13</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="14.45">
       <c r="B18" s="4">
         <v>46114</v>
       </c>
       <c r="C18" s="43" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D18" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F18" s="6">
         <v>2728.65</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" ht="14.45">
       <c r="B19" s="4">
         <v>46118</v>
       </c>
       <c r="C19" s="43" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D19" s="43" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F19" s="6">
         <v>2240</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" ht="14.45">
       <c r="B20" s="4">
         <v>46118</v>
       </c>
       <c r="C20" s="43" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" s="43" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F20" s="6">
         <v>8035.64</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" ht="14.45">
       <c r="B21" s="4">
         <v>46118</v>
       </c>
       <c r="C21" s="43" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D21" s="43" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F21" s="6">
         <v>360</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" ht="14.45">
       <c r="B22" s="4">
         <v>46118</v>
       </c>
       <c r="C22" s="43" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D22" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F22" s="6">
         <v>3935.66</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" ht="14.45">
       <c r="B23" s="4">
         <v>46118</v>
       </c>
       <c r="C23" s="43" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D23" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F23" s="6">
         <v>5789.1</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" ht="14.45">
       <c r="B24" s="4">
         <v>46118</v>
       </c>
       <c r="C24" s="43" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D24" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F24" s="6">
         <v>4377.1899999999996</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" ht="14.45">
       <c r="B25" s="4">
         <v>46118</v>
       </c>
       <c r="C25" s="43" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D25" s="43" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F25" s="6">
         <v>302.33999999999997</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" ht="14.45">
       <c r="B26" s="4">
         <v>46118</v>
       </c>
       <c r="C26" s="43" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D26" s="43" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F26" s="6">
         <v>299.95999999999998</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" ht="14.45">
       <c r="B27" s="4">
         <v>46118</v>
       </c>
       <c r="C27" s="43" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D27" s="43" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F27" s="6">
         <v>3906.98</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" ht="14.45">
       <c r="B28" s="4">
         <v>46118</v>
       </c>
       <c r="C28" s="43" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D28" s="43" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F28" s="6">
         <v>152</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" ht="14.45">
       <c r="B29" s="4">
         <v>46118</v>
       </c>
       <c r="C29" s="43" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D29" s="43" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F29" s="6">
         <v>405.65</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" ht="14.45">
       <c r="B30" s="4">
         <v>46118</v>
       </c>
       <c r="C30" s="43" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D30" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F30" s="6">
         <v>7415.63</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" ht="14.45">
       <c r="B31" s="4">
         <v>46118</v>
       </c>
       <c r="C31" s="43" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D31" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F31" s="6">
         <v>10284.719999999999</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" ht="14.45">
       <c r="B32" s="4">
         <v>46118</v>
       </c>
       <c r="C32" s="43" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D32" s="43" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F32" s="6">
         <v>1478.53</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="33" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" ht="14.45">
       <c r="B33" s="4">
         <v>46118</v>
       </c>
       <c r="C33" s="43" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D33" s="43" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F33" s="6">
         <v>2947.5</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" ht="14.45">
       <c r="B34" s="4">
         <v>46118</v>
       </c>
       <c r="C34" s="43" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D34" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F34" s="6">
         <v>50</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" ht="14.45">
       <c r="B35" s="4">
         <v>46118</v>
       </c>
       <c r="C35" s="43" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D35" s="43" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F35" s="6">
         <v>0</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" ht="14.45">
       <c r="B36" s="4">
         <v>46119</v>
       </c>
       <c r="C36" s="43" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D36" s="43" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F36" s="6">
         <v>15195.48</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" ht="14.45">
       <c r="B37" s="4">
         <v>46119</v>
       </c>
       <c r="C37" s="43" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D37" s="43" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F37" s="6">
         <v>209.91</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" ht="14.45">
       <c r="B38" s="4">
         <v>46119</v>
       </c>
       <c r="C38" s="43" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D38" s="43" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F38" s="6">
         <v>175.56</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" ht="14.45">
       <c r="B39" s="4">
         <v>46119</v>
       </c>
       <c r="C39" s="43" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D39" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F39" s="6">
         <v>11293.32</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="40" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" ht="14.45">
       <c r="B40" s="4">
         <v>46119</v>
       </c>
       <c r="C40" s="43" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D40" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F40" s="6">
         <v>1467.91</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="41" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" ht="14.45">
       <c r="B41" s="4">
         <v>46119</v>
       </c>
       <c r="C41" s="43" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D41" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F41" s="6">
         <v>2959.83</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="42" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" ht="14.45">
       <c r="B42" s="4">
         <v>46119</v>
       </c>
       <c r="C42" s="43" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D42" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F42" s="6">
         <v>901.91</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="43" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" ht="14.45">
       <c r="B43" s="4">
         <v>46119</v>
       </c>
       <c r="C43" s="43" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D43" s="43" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E43" s="6">
         <v>13000</v>
@@ -5520,1217 +6058,1217 @@
         <v>0</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="44" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" ht="14.45">
       <c r="B44" s="4">
         <v>46119</v>
       </c>
       <c r="C44" s="43" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D44" s="43" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F44" s="6">
         <v>4390</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="45" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" ht="14.45">
       <c r="B45" s="4">
         <v>46119</v>
       </c>
       <c r="C45" s="43" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D45" s="43" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F45" s="6">
         <v>247.89</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" ht="14.45">
       <c r="B46" s="4">
         <v>46120</v>
       </c>
       <c r="C46" s="43" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D46" s="43" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F46" s="6">
         <v>826.7</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" ht="14.45">
       <c r="B47" s="4">
         <v>46120</v>
       </c>
       <c r="C47" s="43" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D47" s="43" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F47" s="6">
         <v>80.73</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" ht="14.45">
       <c r="B48" s="4">
         <v>46120</v>
       </c>
       <c r="C48" s="43" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D48" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F48" s="6">
         <v>608.92999999999995</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" ht="14.45">
       <c r="B49" s="4">
         <v>46120</v>
       </c>
       <c r="C49" s="43" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D49" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F49" s="6">
         <v>1033.08</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="50" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" ht="14.45">
       <c r="B50" s="4">
         <v>46120</v>
       </c>
       <c r="C50" s="43" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D50" s="43" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F50" s="6">
         <v>2959.84</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="51" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" ht="14.45">
       <c r="B51" s="4">
         <v>46120</v>
       </c>
       <c r="C51" s="43" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D51" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F51" s="6">
         <v>868.28</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="52" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" ht="14.45">
       <c r="B52" s="4">
         <v>46120</v>
       </c>
       <c r="C52" s="43" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D52" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F52" s="6">
         <v>6984.26</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="53" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" ht="14.45">
       <c r="B53" s="4">
         <v>46120</v>
       </c>
       <c r="C53" s="43" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D53" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F53" s="6">
         <v>1874.61</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="54" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" ht="14.45">
       <c r="B54" s="4">
         <v>46120</v>
       </c>
       <c r="C54" s="43" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D54" s="43" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F54" s="6">
         <v>2000</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="55" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" ht="14.45">
       <c r="B55" s="4">
         <v>46120</v>
       </c>
       <c r="C55" s="43" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D55" s="43" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F55" s="6">
         <v>800</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="56" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" ht="14.45">
       <c r="B56" s="4">
         <v>46120</v>
       </c>
       <c r="C56" s="43" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D56" s="43" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F56" s="6">
         <v>903.07</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="57" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" ht="14.45">
       <c r="B57" s="4">
         <v>46120</v>
       </c>
       <c r="C57" s="43" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D57" s="43" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F57" s="6">
         <v>19567.97</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="58" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" ht="14.45">
       <c r="B58" s="14">
         <v>46121</v>
       </c>
       <c r="C58" s="43" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D58" s="43" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F58" s="6">
         <v>19.57</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="59" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" ht="14.45">
       <c r="B59" s="14">
         <v>46121</v>
       </c>
       <c r="C59" s="43" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D59" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F59" s="6">
         <v>1560.58</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="60" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" ht="14.45">
       <c r="B60" s="14">
         <v>46121</v>
       </c>
       <c r="C60" s="43" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D60" s="43" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F60" s="6">
         <v>239.9</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="61" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" ht="14.45">
       <c r="B61" s="14">
         <v>46121</v>
       </c>
       <c r="C61" s="43" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D61" s="43" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F61" s="6">
         <v>166.86</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="62" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" ht="14.45">
       <c r="B62" s="14">
         <v>46121</v>
       </c>
       <c r="C62" s="43" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D62" s="43" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F62" s="6">
         <v>10872.76</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="63" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" ht="14.45">
       <c r="B63" s="14">
         <v>46121</v>
       </c>
       <c r="C63" s="43" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D63" s="43" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F63" s="6">
         <v>1000</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="64" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" ht="14.45">
       <c r="B64" s="4">
         <v>46122</v>
       </c>
       <c r="C64" s="43" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D64" s="43" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F64" s="6">
         <v>170.61</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="65" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="65" spans="2:8" ht="14.45">
       <c r="B65" s="4">
         <v>46122</v>
       </c>
       <c r="C65" s="43" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D65" s="43" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F65" s="6">
         <v>705.21</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="66" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="66" spans="2:8" ht="14.45">
       <c r="B66" s="4">
         <v>46122</v>
       </c>
       <c r="C66" s="43" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D66" s="43" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F66" s="6">
         <v>53.76</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="67" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="67" spans="2:8" ht="14.45">
       <c r="B67" s="4">
         <v>46122</v>
       </c>
       <c r="C67" s="43" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D67" s="43" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F67" s="6">
         <v>5466.28</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="68" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="68" spans="2:8" ht="14.45">
       <c r="B68" s="4">
         <v>46122</v>
       </c>
       <c r="C68" s="43" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D68" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F68" s="6">
         <v>3496</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="69" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="69" spans="2:8" ht="14.45">
       <c r="B69" s="4">
         <v>46122</v>
       </c>
       <c r="C69" s="43" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D69" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F69" s="6">
         <v>144</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="70" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="70" spans="2:8" ht="14.45">
       <c r="B70" s="4">
         <v>46122</v>
       </c>
       <c r="C70" s="43" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D70" s="43" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F70" s="6">
         <v>123.62</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="71" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="71" spans="2:8" ht="14.45">
       <c r="B71" s="4">
         <v>46122</v>
       </c>
       <c r="C71" s="43" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D71" s="43" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F71" s="6">
         <v>3432.87</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="72" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="72" spans="2:8" ht="14.45">
       <c r="B72" s="4">
         <v>46122</v>
       </c>
       <c r="C72" s="43" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D72" s="43" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F72" s="6">
         <v>728.25</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="73" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="73" spans="2:8" ht="14.45">
       <c r="B73" s="4">
         <v>46122</v>
       </c>
       <c r="C73" s="43" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D73" s="43" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F73" s="6">
         <v>1200</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="74" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="74" spans="2:8" ht="14.45">
       <c r="B74" s="4">
         <v>46122</v>
       </c>
       <c r="C74" s="43" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D74" s="43" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F74" s="6">
         <v>400</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="75" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="75" spans="2:8" ht="14.45">
       <c r="B75" s="4">
         <v>46122</v>
       </c>
       <c r="C75" s="43" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D75" s="43" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F75" s="6">
         <v>720</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="76" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="76" spans="2:8" ht="14.45">
       <c r="B76" s="4">
         <v>46122</v>
       </c>
       <c r="C76" s="43" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D76" s="43" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F76" s="6">
         <v>440</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="77" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="77" spans="2:8" ht="14.45">
       <c r="B77" s="4">
         <v>46122</v>
       </c>
       <c r="C77" s="43" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D77" s="43" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F77" s="6">
         <v>3260.93</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="78" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="78" spans="2:8" ht="14.45">
       <c r="B78" s="4">
         <v>46125</v>
       </c>
       <c r="C78" s="43" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D78" s="43" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F78" s="6">
         <v>36108.1</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="79" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="79" spans="2:8" ht="14.45">
       <c r="B79" s="4">
         <v>46125</v>
       </c>
       <c r="C79" s="43" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D79" s="43" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F79" s="6">
         <v>9266.66</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="80" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="80" spans="2:8" ht="14.45">
       <c r="B80" s="4">
         <v>46126</v>
       </c>
       <c r="C80" s="43" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D80" s="43" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F80" s="6">
         <v>6.67</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" ht="14.45">
       <c r="B81" s="4">
         <v>46126</v>
       </c>
       <c r="C81" s="43" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D81" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F81" s="6">
         <v>9144.36</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="82" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="82" spans="2:8" ht="14.45">
       <c r="B82" s="4">
         <v>46126</v>
       </c>
       <c r="C82" s="43" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D82" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F82" s="6">
         <v>14541.68</v>
       </c>
       <c r="H82" s="1"/>
     </row>
-    <row r="83" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:8" ht="14.45">
       <c r="B83" s="4">
         <v>46126</v>
       </c>
       <c r="C83" s="43" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D83" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F83" s="6">
         <v>3407.79</v>
       </c>
       <c r="H83" s="1"/>
     </row>
-    <row r="84" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:8" ht="14.45">
       <c r="B84" s="4">
         <v>46126</v>
       </c>
       <c r="C84" s="43" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D84" s="43" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F84" s="6">
         <v>2380.69</v>
       </c>
       <c r="H84" s="1"/>
     </row>
-    <row r="85" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:8" ht="14.45">
       <c r="B85" s="4">
         <v>46126</v>
       </c>
       <c r="C85" s="43" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D85" s="43" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F85" s="6">
         <v>1089.33</v>
       </c>
       <c r="H85" s="1"/>
     </row>
-    <row r="86" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:8" ht="14.45">
       <c r="B86" s="4">
         <v>46126</v>
       </c>
       <c r="C86" s="43" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D86" s="43" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F86" s="6">
         <v>3525.83</v>
       </c>
       <c r="H86" s="1"/>
     </row>
-    <row r="87" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:8" ht="14.45">
       <c r="B87" s="4">
         <v>46126</v>
       </c>
       <c r="C87" s="43" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D87" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F87" s="6">
         <v>1801.21</v>
       </c>
       <c r="H87" s="1"/>
     </row>
-    <row r="88" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:8" ht="14.45">
       <c r="B88" s="4">
         <v>46126</v>
       </c>
       <c r="C88" s="43" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D88" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F88" s="6">
         <v>8778.98</v>
       </c>
       <c r="H88" s="1"/>
     </row>
-    <row r="89" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:8" ht="14.45">
       <c r="B89" s="4">
         <v>46126</v>
       </c>
       <c r="C89" s="43" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D89" s="43" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F89" s="6">
         <v>3030.85</v>
       </c>
     </row>
-    <row r="90" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:8" ht="14.45">
       <c r="B90" s="4">
         <v>46126</v>
       </c>
       <c r="C90" s="43" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D90" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F90" s="6">
         <v>2445.6999999999998</v>
       </c>
     </row>
-    <row r="91" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:8" ht="14.45">
       <c r="B91" s="4">
         <v>46126</v>
       </c>
       <c r="C91" s="43" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D91" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F91" s="6">
         <v>1260.79</v>
       </c>
     </row>
-    <row r="92" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:8" ht="14.45">
       <c r="B92" s="4">
         <v>46126</v>
       </c>
       <c r="C92" s="43" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D92" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F92" s="6">
         <v>2504.25</v>
       </c>
     </row>
-    <row r="93" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:8" ht="14.45">
       <c r="B93" s="4">
         <v>46126</v>
       </c>
       <c r="C93" s="43" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D93" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F93" s="6">
         <v>4470</v>
       </c>
     </row>
-    <row r="94" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:8" ht="14.45">
       <c r="B94" s="4">
         <v>46126</v>
       </c>
       <c r="C94" s="43" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D94" s="43" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F94" s="6">
         <v>1300</v>
       </c>
     </row>
-    <row r="95" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:8" ht="14.45">
       <c r="B95" s="4">
         <v>46126</v>
       </c>
       <c r="C95" s="43" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D95" s="43" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F95" s="6">
         <v>12</v>
       </c>
     </row>
-    <row r="96" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:8" ht="14.45">
       <c r="B96" s="4">
         <v>46126</v>
       </c>
       <c r="C96" s="43" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D96" s="43" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F96" s="6">
         <v>145.99</v>
       </c>
     </row>
-    <row r="97" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:6" ht="14.45">
       <c r="B97" s="4">
         <v>46126</v>
       </c>
       <c r="C97" s="43" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D97" s="43" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F97" s="6">
         <v>621.67999999999995</v>
       </c>
     </row>
-    <row r="98" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:6" ht="14.45">
       <c r="B98" s="4">
         <v>46127</v>
       </c>
       <c r="C98" s="43" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D98" s="43" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F98" s="6">
         <v>222.23</v>
       </c>
     </row>
-    <row r="99" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:6" ht="14.45">
       <c r="B99" s="4">
         <v>46127</v>
       </c>
       <c r="C99" s="43" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D99" s="43" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F99" s="6">
         <v>1320.66</v>
       </c>
     </row>
-    <row r="100" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:6" ht="14.45">
       <c r="B100" s="4">
         <v>46127</v>
       </c>
       <c r="C100" s="43" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D100" s="43" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F100" s="6">
         <v>1680</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:6" ht="14.45">
       <c r="B101" s="4">
         <v>46127</v>
       </c>
       <c r="C101" s="43" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D101" s="43" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F101" s="6">
         <v>150</v>
       </c>
     </row>
-    <row r="102" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:6" ht="14.45">
       <c r="B102" s="4">
         <v>46128</v>
       </c>
       <c r="C102" s="43" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D102" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F102" s="6">
         <v>3806.08</v>
       </c>
     </row>
-    <row r="103" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:6" ht="14.45">
       <c r="B103" s="4">
         <v>46128</v>
       </c>
       <c r="C103" s="43" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D103" s="43" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F103" s="6">
         <v>2454.98</v>
       </c>
     </row>
-    <row r="104" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:6" ht="14.45">
       <c r="B104" s="4">
         <v>46128</v>
       </c>
       <c r="C104" s="43" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D104" s="43" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F104" s="6">
         <v>38</v>
       </c>
     </row>
-    <row r="105" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:6" ht="14.45">
       <c r="B105" s="4">
         <v>46128</v>
       </c>
       <c r="C105" s="43" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D105" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F105" s="6">
         <v>2809.99</v>
       </c>
     </row>
-    <row r="106" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:6" ht="14.45">
       <c r="B106" s="4">
         <v>46128</v>
       </c>
       <c r="C106" s="43" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D106" s="43" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F106" s="6">
         <v>152.93</v>
       </c>
     </row>
-    <row r="107" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:6" ht="14.45">
       <c r="B107" s="4">
         <v>46128</v>
       </c>
       <c r="C107" s="43" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D107" s="43" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F107" s="6">
         <v>3664.04</v>
       </c>
     </row>
-    <row r="108" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:6" ht="14.45">
       <c r="B108" s="4">
         <v>46128</v>
       </c>
       <c r="C108" s="43" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D108" s="43" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F108" s="6">
         <v>896.61</v>
       </c>
     </row>
-    <row r="109" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:6" ht="14.45">
       <c r="B109" s="4">
         <v>46128</v>
       </c>
       <c r="C109" s="43" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D109" s="43" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F109" s="6">
         <v>536.58000000000004</v>
       </c>
     </row>
-    <row r="110" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:6" ht="14.45">
       <c r="B110" s="4">
         <v>46128</v>
       </c>
       <c r="C110" s="43" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D110" s="43" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F110" s="6">
         <v>4498.9399999999996</v>
       </c>
     </row>
-    <row r="111" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:6" ht="14.45">
       <c r="B111" s="4">
         <v>46128</v>
       </c>
       <c r="C111" s="43" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D111" s="43" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F111" s="6">
         <v>315</v>
       </c>
     </row>
-    <row r="112" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:6" ht="14.45">
       <c r="B112" s="4">
         <v>46128</v>
       </c>
       <c r="C112" s="43" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D112" s="43" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F112" s="6">
         <v>91.17</v>
       </c>
     </row>
-    <row r="113" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:6" ht="14.45">
       <c r="B113" s="4">
         <v>46128</v>
       </c>
       <c r="C113" s="43" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D113" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F113" s="6">
         <v>13953.27</v>
       </c>
     </row>
-    <row r="114" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:6" ht="14.45">
       <c r="B114" s="4">
         <v>46128</v>
       </c>
       <c r="C114" s="43" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D114" s="43" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F114" s="6">
         <v>130.5</v>
       </c>
     </row>
-    <row r="115" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:6" ht="14.45">
       <c r="B115" s="4">
         <v>46128</v>
       </c>
       <c r="C115" s="43" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D115" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F115" s="6">
         <v>5916.4</v>
       </c>
     </row>
-    <row r="116" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:6" ht="14.45">
       <c r="B116" s="4">
         <v>46128</v>
       </c>
       <c r="C116" s="43" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D116" s="43" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F116" s="6">
         <v>13391.92</v>
       </c>
     </row>
-    <row r="117" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:6" ht="14.45">
       <c r="B117" s="4">
         <v>46128</v>
       </c>
       <c r="C117" s="43" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D117" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F117" s="6">
         <v>826.63</v>
       </c>
     </row>
-    <row r="118" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:6" ht="14.45">
       <c r="B118" s="4">
         <v>46128</v>
       </c>
       <c r="C118" s="43" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D118" s="43" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F118" s="6">
         <v>91.8</v>
       </c>
     </row>
-    <row r="119" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:6" ht="14.45">
       <c r="B119" s="4">
         <v>46128</v>
       </c>
       <c r="C119" s="43" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D119" s="43" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F119" s="6">
         <v>359.29</v>
       </c>
     </row>
-    <row r="120" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:6" ht="14.45">
       <c r="B120" s="4">
         <v>46128</v>
       </c>
       <c r="C120" s="43" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D120" s="43" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F120" s="6">
         <v>7000</v>
       </c>
     </row>
-    <row r="121" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:6" ht="14.45">
       <c r="B121" s="4">
         <v>46129</v>
       </c>
       <c r="C121" s="43" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D121" s="43" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E121" s="6">
         <v>15000</v>
@@ -6739,127 +7277,127 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:6" ht="15" customHeight="1">
       <c r="B122" s="4">
         <v>46129</v>
       </c>
       <c r="C122" s="43" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D122" s="43" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F122" s="6">
         <v>600</v>
       </c>
     </row>
-    <row r="123" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:6" ht="15" customHeight="1">
       <c r="B123" s="4">
         <v>46129</v>
       </c>
       <c r="C123" s="43" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D123" s="43" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F123" s="6">
         <v>3500</v>
       </c>
     </row>
-    <row r="124" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:6" ht="15" customHeight="1">
       <c r="B124" s="4">
         <v>46129</v>
       </c>
       <c r="C124" s="43" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D124" s="43" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F124" s="6">
         <v>92.14</v>
       </c>
     </row>
-    <row r="125" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:6" ht="15" customHeight="1">
       <c r="B125" s="4">
         <v>46129</v>
       </c>
       <c r="C125" s="43" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D125" s="43" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F125" s="6">
         <v>606</v>
       </c>
     </row>
-    <row r="126" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:6" ht="15" customHeight="1">
       <c r="B126" s="4">
         <v>46129</v>
       </c>
       <c r="C126" s="43" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D126" s="43" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F126" s="6">
         <v>2000</v>
       </c>
     </row>
-    <row r="127" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:6" ht="15" customHeight="1">
       <c r="B127" s="4">
         <v>46129</v>
       </c>
       <c r="C127" s="43" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D127" s="43" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F127" s="6">
         <v>106.66</v>
       </c>
     </row>
-    <row r="128" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:6" ht="15" customHeight="1">
       <c r="B128" s="4">
         <v>46129</v>
       </c>
       <c r="C128" s="43" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D128" s="43" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F128" s="6">
         <v>225</v>
       </c>
     </row>
-    <row r="129" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:6" ht="15" customHeight="1">
       <c r="B129" s="4">
         <v>46129</v>
       </c>
       <c r="C129" s="43" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D129" s="43" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F129" s="6">
         <v>50</v>
       </c>
     </row>
-    <row r="130" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:6" ht="15" customHeight="1">
       <c r="B130" s="4">
         <v>46132</v>
       </c>
       <c r="C130" s="43" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D130" s="43" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E130" s="6">
         <v>11000</v>
@@ -6868,978 +7406,1372 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:6" ht="15" customHeight="1">
       <c r="B131" s="4">
         <v>46132</v>
       </c>
       <c r="C131" s="43" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D131" s="43" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F131" s="6">
         <v>434.3</v>
       </c>
     </row>
-    <row r="132" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:6" ht="15" customHeight="1">
       <c r="B132" s="4">
         <v>46132</v>
       </c>
       <c r="C132" s="43" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D132" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="E132" s="53"/>
+        <v>183</v>
+      </c>
+      <c r="E132" s="51"/>
       <c r="F132" s="6">
         <v>8227.7099999999991</v>
       </c>
     </row>
-    <row r="133" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:6" ht="15" customHeight="1">
       <c r="B133" s="4">
         <v>46132</v>
       </c>
       <c r="C133" s="43" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D133" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F133" s="6">
         <v>12428.85</v>
       </c>
     </row>
-    <row r="134" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:6" ht="15" customHeight="1">
       <c r="B134" s="4">
         <v>46132</v>
       </c>
       <c r="C134" s="43" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D134" s="43" t="s">
-        <v>178</v>
-      </c>
-      <c r="E134" s="53"/>
+        <v>181</v>
+      </c>
+      <c r="E134" s="51"/>
       <c r="F134" s="6">
         <v>1800</v>
       </c>
     </row>
-    <row r="135" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:6" ht="15" customHeight="1">
       <c r="B135" s="4">
         <v>46132</v>
       </c>
       <c r="C135" s="43" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D135" s="43" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F135" s="6">
         <v>40</v>
       </c>
     </row>
-    <row r="136" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:6" ht="15" customHeight="1">
       <c r="B136" s="4">
         <v>46132</v>
       </c>
       <c r="C136" s="43" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D136" s="43" t="s">
-        <v>182</v>
-      </c>
-      <c r="E136" s="53"/>
+        <v>185</v>
+      </c>
+      <c r="E136" s="51"/>
       <c r="F136" s="6">
         <v>2689.59</v>
       </c>
     </row>
-    <row r="137" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:6" ht="15" customHeight="1">
       <c r="B137" s="4">
         <v>46132</v>
       </c>
       <c r="C137" s="43" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D137" s="43" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F137" s="6">
         <v>588.07000000000005</v>
       </c>
     </row>
-    <row r="138" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:6" ht="15" customHeight="1">
       <c r="B138" s="4">
         <v>46132</v>
       </c>
       <c r="C138" s="43" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D138" s="43" t="s">
-        <v>185</v>
-      </c>
-      <c r="E138" s="53"/>
+        <v>188</v>
+      </c>
+      <c r="E138" s="51"/>
       <c r="F138" s="6">
         <v>915.59</v>
       </c>
     </row>
-    <row r="139" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:6" ht="15" customHeight="1">
       <c r="B139" s="4">
         <v>46132</v>
       </c>
       <c r="C139" s="43" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D139" s="43" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F139" s="6">
         <v>9757.1299999999992</v>
       </c>
     </row>
-    <row r="140" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:6" ht="15" customHeight="1">
       <c r="B140" s="4">
         <v>46132</v>
       </c>
       <c r="C140" s="43" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D140" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="E140" s="53"/>
+        <v>69</v>
+      </c>
+      <c r="E140" s="51"/>
       <c r="F140" s="6">
         <v>2027</v>
       </c>
     </row>
-    <row r="141" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:6" ht="15" customHeight="1">
       <c r="B141" s="4">
         <v>46132</v>
       </c>
       <c r="C141" s="43" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D141" s="43" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F141" s="6">
         <v>97.34</v>
       </c>
     </row>
-    <row r="142" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:6" ht="15" customHeight="1">
       <c r="B142" s="4">
         <v>46132</v>
       </c>
       <c r="C142" s="43" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D142" s="43" t="s">
-        <v>63</v>
-      </c>
-      <c r="E142" s="53"/>
+        <v>66</v>
+      </c>
+      <c r="E142" s="51"/>
       <c r="F142" s="6">
         <v>127</v>
       </c>
     </row>
-    <row r="143" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:6" ht="15" customHeight="1">
       <c r="B143" s="4">
         <v>46132</v>
       </c>
       <c r="C143" s="43" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D143" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F143" s="6">
         <v>1359.21</v>
       </c>
     </row>
-    <row r="144" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:6" ht="15" customHeight="1">
       <c r="B144" s="4">
         <v>46132</v>
       </c>
       <c r="C144" s="43" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D144" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="E144" s="53"/>
+        <v>69</v>
+      </c>
+      <c r="E144" s="51"/>
       <c r="F144" s="6">
         <v>7349.56</v>
       </c>
     </row>
-    <row r="145" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:6" ht="15" customHeight="1">
       <c r="B145" s="4">
         <v>46132</v>
       </c>
       <c r="C145" s="43" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D145" s="43" t="s">
-        <v>189</v>
-      </c>
-      <c r="E145" s="53"/>
+        <v>192</v>
+      </c>
+      <c r="E145" s="51"/>
       <c r="F145" s="6">
         <v>3994</v>
       </c>
     </row>
-    <row r="146" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:6" ht="15" customHeight="1">
       <c r="B146" s="4">
         <v>46132</v>
       </c>
       <c r="C146" s="43" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D146" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F146" s="6">
         <v>6114.45</v>
       </c>
     </row>
-    <row r="147" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:6" ht="15" customHeight="1">
       <c r="B147" s="4">
         <v>46132</v>
       </c>
       <c r="C147" s="43" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D147" s="43" t="s">
-        <v>101</v>
-      </c>
-      <c r="E147" s="53"/>
+        <v>104</v>
+      </c>
+      <c r="E147" s="51"/>
       <c r="F147" s="6">
         <v>534.5</v>
       </c>
     </row>
-    <row r="148" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:6" ht="15" customHeight="1">
       <c r="B148" s="4">
         <v>46132</v>
       </c>
       <c r="C148" s="43" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D148" s="43" t="s">
-        <v>190</v>
-      </c>
-      <c r="E148" s="53"/>
+        <v>193</v>
+      </c>
+      <c r="E148" s="51"/>
       <c r="F148" s="6">
         <v>470.46</v>
       </c>
     </row>
-    <row r="149" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:6" ht="15" customHeight="1">
       <c r="B149" s="4">
         <v>46132</v>
       </c>
       <c r="C149" s="43" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D149" s="43" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F149" s="6">
         <v>1128</v>
       </c>
     </row>
-    <row r="150" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:6" ht="15" customHeight="1">
       <c r="B150" s="4">
         <v>46132</v>
       </c>
       <c r="C150" s="43" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D150" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="E150" s="53"/>
+        <v>69</v>
+      </c>
+      <c r="E150" s="51"/>
       <c r="F150" s="6">
         <v>5906.64</v>
       </c>
     </row>
-    <row r="151" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:6" ht="15" customHeight="1">
       <c r="B151" s="4">
         <v>46132</v>
       </c>
       <c r="C151" s="43" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D151" s="43" t="s">
-        <v>195</v>
-      </c>
-      <c r="E151" s="53"/>
+        <v>198</v>
+      </c>
+      <c r="E151" s="51"/>
       <c r="F151" s="6">
         <v>311.5</v>
       </c>
     </row>
-    <row r="152" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:6" ht="15" customHeight="1">
       <c r="B152" s="4">
         <v>46132</v>
       </c>
       <c r="C152" s="43" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D152" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F152" s="6">
         <v>1998.45</v>
       </c>
     </row>
-    <row r="153" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:6" ht="15" customHeight="1">
       <c r="B153" s="4">
         <v>46132</v>
       </c>
       <c r="C153" s="43" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D153" s="43" t="s">
-        <v>197</v>
-      </c>
-      <c r="E153" s="53"/>
+        <v>200</v>
+      </c>
+      <c r="E153" s="51"/>
       <c r="F153" s="6">
         <v>2067.37</v>
       </c>
     </row>
-    <row r="154" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:6" ht="15" customHeight="1">
       <c r="B154" s="4">
         <v>46134</v>
       </c>
       <c r="C154" s="43" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D154" s="43" t="s">
-        <v>84</v>
-      </c>
-      <c r="E154" s="53"/>
+        <v>87</v>
+      </c>
+      <c r="E154" s="51"/>
       <c r="F154" s="6">
         <v>360</v>
       </c>
     </row>
-    <row r="155" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:6" ht="15" customHeight="1">
       <c r="B155" s="4">
         <v>46134</v>
       </c>
       <c r="C155" s="43" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D155" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F155" s="6">
         <v>5115</v>
       </c>
     </row>
-    <row r="156" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:6" ht="15" customHeight="1">
       <c r="B156" s="4">
         <v>46134</v>
       </c>
       <c r="C156" s="43" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D156" s="43" t="s">
-        <v>143</v>
-      </c>
-      <c r="E156" s="53"/>
+        <v>146</v>
+      </c>
+      <c r="E156" s="51"/>
       <c r="F156" s="6">
         <v>82.4</v>
       </c>
     </row>
-    <row r="157" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:6" ht="15" customHeight="1">
       <c r="B157" s="4">
         <v>46134</v>
       </c>
       <c r="C157" s="43" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D157" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F157" s="6">
         <v>2092</v>
       </c>
     </row>
-    <row r="158" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:6" ht="15" customHeight="1">
       <c r="B158" s="4">
         <v>46134</v>
       </c>
       <c r="C158" s="43" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D158" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="E158" s="53"/>
+        <v>69</v>
+      </c>
+      <c r="E158" s="51"/>
       <c r="F158" s="6">
         <v>2504.25</v>
       </c>
     </row>
-    <row r="159" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:6" ht="15" customHeight="1">
       <c r="B159" s="4">
         <v>46134</v>
       </c>
       <c r="C159" s="43" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D159" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F159" s="6">
         <v>3138.13</v>
       </c>
     </row>
-    <row r="160" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:6" ht="15" customHeight="1">
       <c r="B160" s="4">
         <v>46134</v>
       </c>
       <c r="C160" s="43" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D160" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="E160" s="53"/>
+        <v>69</v>
+      </c>
+      <c r="E160" s="51"/>
       <c r="F160" s="6">
         <v>6844.44</v>
       </c>
     </row>
-    <row r="161" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:6" ht="15" customHeight="1">
       <c r="B161" s="4">
         <v>46134</v>
       </c>
       <c r="C161" s="43" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D161" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F161" s="6">
         <v>11034.3</v>
       </c>
     </row>
-    <row r="162" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:6" ht="15" customHeight="1">
       <c r="B162" s="4">
         <v>46134</v>
       </c>
       <c r="C162" s="43" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D162" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="E162" s="53"/>
+        <v>69</v>
+      </c>
+      <c r="E162" s="51"/>
       <c r="F162" s="6">
         <v>45048</v>
       </c>
     </row>
-    <row r="163" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:6" ht="15" customHeight="1">
       <c r="B163" s="4">
         <v>46134</v>
       </c>
       <c r="C163" s="43" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D163" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F163" s="6">
         <v>30119.64</v>
       </c>
     </row>
-    <row r="164" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:6" ht="15" customHeight="1">
       <c r="B164" s="4">
         <v>46134</v>
       </c>
       <c r="C164" s="43" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D164" s="43" t="s">
-        <v>201</v>
-      </c>
-      <c r="E164" s="53"/>
+        <v>204</v>
+      </c>
+      <c r="E164" s="51"/>
       <c r="F164" s="6">
         <v>2900</v>
       </c>
     </row>
-    <row r="165" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:6" ht="15" customHeight="1">
       <c r="B165" s="4">
         <v>46134</v>
       </c>
       <c r="C165" s="43" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D165" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F165" s="6">
         <v>899.5</v>
       </c>
     </row>
-    <row r="166" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:6" ht="15" customHeight="1">
       <c r="B166" s="4">
         <v>46134</v>
       </c>
       <c r="C166" s="43" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D166" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="E166" s="53"/>
+        <v>69</v>
+      </c>
+      <c r="E166" s="51"/>
       <c r="F166" s="6">
         <v>2278.8000000000002</v>
       </c>
     </row>
-    <row r="167" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:6" ht="15" customHeight="1">
       <c r="B167" s="4">
         <v>46134</v>
       </c>
       <c r="C167" s="43" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D167" s="43" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F167" s="6">
         <v>382.96</v>
       </c>
     </row>
-    <row r="168" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:6" ht="15" customHeight="1">
       <c r="B168" s="4">
         <v>46135</v>
       </c>
       <c r="C168" s="43" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D168" s="43" t="s">
-        <v>131</v>
-      </c>
-      <c r="E168" s="53"/>
+        <v>134</v>
+      </c>
+      <c r="E168" s="51"/>
       <c r="F168" s="6">
         <v>2340</v>
       </c>
     </row>
-    <row r="169" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:6" ht="15" customHeight="1">
       <c r="B169" s="4">
         <v>46135</v>
       </c>
       <c r="C169" s="43" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D169" s="43" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F169" s="6">
         <v>83.72</v>
       </c>
     </row>
-    <row r="170" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:6" ht="15" customHeight="1">
       <c r="B170" s="4">
         <v>46135</v>
       </c>
       <c r="C170" s="43" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D170" s="43" t="s">
-        <v>173</v>
-      </c>
-      <c r="E170" s="53"/>
+        <v>176</v>
+      </c>
+      <c r="E170" s="51"/>
       <c r="F170" s="6">
         <v>308</v>
       </c>
     </row>
-    <row r="171" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:6" ht="15" customHeight="1">
       <c r="B171" s="4">
         <v>46135</v>
       </c>
       <c r="C171" s="43" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D171" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F171" s="6">
         <v>2393.71</v>
       </c>
     </row>
-    <row r="172" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:6" ht="15" customHeight="1">
       <c r="B172" s="4">
         <v>46135</v>
       </c>
       <c r="C172" s="43" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D172" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="E172" s="53"/>
+        <v>69</v>
+      </c>
+      <c r="E172" s="51"/>
       <c r="F172" s="6">
         <v>2959.84</v>
       </c>
     </row>
-    <row r="173" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:6" ht="15" customHeight="1">
       <c r="B173" s="4">
         <v>46135</v>
       </c>
       <c r="C173" s="43" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D173" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F173" s="6">
         <v>8680.48</v>
       </c>
     </row>
-    <row r="174" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:6" ht="15" customHeight="1">
       <c r="B174" s="4">
         <v>46135</v>
       </c>
       <c r="C174" s="43" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D174" s="43" t="s">
-        <v>204</v>
-      </c>
-      <c r="E174" s="53"/>
+        <v>207</v>
+      </c>
+      <c r="E174" s="51"/>
       <c r="F174" s="6">
         <v>15970.84</v>
       </c>
     </row>
-    <row r="175" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:6" ht="15" customHeight="1">
       <c r="B175" s="4">
         <v>46135</v>
       </c>
       <c r="C175" s="43" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D175" s="43" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F175" s="6">
         <v>104.52</v>
       </c>
     </row>
-    <row r="176" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:6" ht="15" customHeight="1">
       <c r="B176" s="4">
         <v>46135</v>
       </c>
       <c r="C176" s="43" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D176" s="43" t="s">
-        <v>171</v>
-      </c>
-      <c r="E176" s="53"/>
+        <v>174</v>
+      </c>
+      <c r="E176" s="51"/>
       <c r="F176" s="6">
         <v>37.25</v>
       </c>
     </row>
-    <row r="177" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:6" ht="15" customHeight="1">
       <c r="B177" s="4">
         <v>46136</v>
       </c>
       <c r="C177" s="43" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D177" s="43" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F177" s="6">
         <v>50</v>
       </c>
     </row>
-    <row r="178" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:6" ht="15" customHeight="1">
       <c r="B178" s="4">
         <v>46136</v>
       </c>
       <c r="C178" s="43" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D178" s="43" t="s">
-        <v>131</v>
-      </c>
-      <c r="E178" s="53"/>
+        <v>134</v>
+      </c>
+      <c r="E178" s="51"/>
       <c r="F178" s="6">
         <v>1914</v>
       </c>
     </row>
-    <row r="179" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:6" ht="15" customHeight="1">
       <c r="B179" s="4">
         <v>46136</v>
       </c>
       <c r="C179" s="43" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D179" s="43" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F179" s="6">
         <v>185</v>
       </c>
     </row>
-    <row r="180" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:6" ht="15" customHeight="1">
       <c r="B180" s="4">
         <v>46136</v>
       </c>
       <c r="C180" s="43" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D180" s="43" t="s">
-        <v>63</v>
-      </c>
-      <c r="E180" s="53"/>
+        <v>66</v>
+      </c>
+      <c r="E180" s="51"/>
       <c r="F180" s="6">
         <v>600</v>
       </c>
     </row>
-    <row r="181" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:6" ht="15" customHeight="1">
       <c r="B181" s="4">
         <v>46136</v>
       </c>
       <c r="C181" s="43" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D181" s="43" t="s">
-        <v>168</v>
-      </c>
-      <c r="E181" s="53"/>
+        <v>171</v>
+      </c>
+      <c r="E181" s="64"/>
       <c r="F181" s="6">
         <v>1019.45</v>
       </c>
     </row>
-    <row r="182" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:6" ht="15" customHeight="1">
       <c r="B182" s="4">
         <v>46136</v>
       </c>
       <c r="C182" s="43" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D182" s="43" t="s">
-        <v>210</v>
-      </c>
-      <c r="E182" s="53"/>
+        <v>213</v>
+      </c>
+      <c r="E182" s="64"/>
       <c r="F182" s="6">
         <v>4000</v>
       </c>
     </row>
-    <row r="183" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:6" ht="15" customHeight="1">
       <c r="B183" s="4">
         <v>46136</v>
       </c>
       <c r="C183" s="43" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D183" s="43" t="s">
-        <v>205</v>
-      </c>
-      <c r="E183" s="53"/>
+        <v>208</v>
+      </c>
+      <c r="E183" s="64"/>
       <c r="F183" s="6">
         <v>126.87</v>
       </c>
     </row>
-    <row r="184" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:6" ht="15" customHeight="1">
       <c r="B184" s="4">
         <v>46136</v>
       </c>
       <c r="C184" s="43" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D184" s="43" t="s">
-        <v>171</v>
-      </c>
-      <c r="E184" s="53"/>
+        <v>174</v>
+      </c>
+      <c r="E184" s="64"/>
       <c r="F184" s="6">
         <v>145.99</v>
       </c>
     </row>
-    <row r="185" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:6" ht="15" customHeight="1">
       <c r="B185" s="4">
         <v>46136</v>
       </c>
       <c r="C185" s="43" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D185" s="43" t="s">
-        <v>84</v>
-      </c>
-      <c r="E185" s="53"/>
+        <v>87</v>
+      </c>
+      <c r="E185" s="64"/>
       <c r="F185" s="6">
         <v>458.33</v>
       </c>
     </row>
-    <row r="186" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:6" ht="15" customHeight="1">
       <c r="B186" s="4">
         <v>46136</v>
       </c>
       <c r="C186" s="43" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D186" s="43" t="s">
-        <v>213</v>
-      </c>
-      <c r="E186" s="53"/>
+        <v>216</v>
+      </c>
+      <c r="E186" s="64"/>
       <c r="F186" s="6">
         <v>8982.7099999999991</v>
       </c>
     </row>
-    <row r="187" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:6" ht="15" customHeight="1">
       <c r="B187" s="4">
         <v>46136</v>
       </c>
       <c r="C187" s="43" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D187" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="E187" s="53"/>
+        <v>69</v>
+      </c>
+      <c r="E187" s="64"/>
       <c r="F187" s="6">
         <v>438.72</v>
       </c>
     </row>
-    <row r="188" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:6" ht="15" customHeight="1">
       <c r="B188" s="4">
         <v>46136</v>
       </c>
       <c r="C188" s="43" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D188" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="E188" s="53"/>
+        <v>69</v>
+      </c>
+      <c r="E188" s="64"/>
       <c r="F188" s="6">
         <v>826.34</v>
       </c>
     </row>
-    <row r="189" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:6" ht="15" customHeight="1">
       <c r="B189" s="4">
         <v>46136</v>
       </c>
       <c r="C189" s="43" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D189" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="E189" s="53"/>
+        <v>69</v>
+      </c>
+      <c r="E189" s="64"/>
       <c r="F189" s="6">
         <v>2278.8000000000002</v>
       </c>
     </row>
-    <row r="190" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:6" ht="15" customHeight="1">
       <c r="B190" s="4">
         <v>46136</v>
       </c>
       <c r="C190" s="43" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D190" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="E190" s="53"/>
+        <v>69</v>
+      </c>
+      <c r="E190" s="64"/>
       <c r="F190" s="6">
         <v>8219</v>
       </c>
     </row>
-    <row r="191" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:6" ht="15" customHeight="1">
       <c r="B191" s="4">
         <v>46136</v>
       </c>
       <c r="C191" s="43" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D191" s="43" t="s">
-        <v>63</v>
-      </c>
-      <c r="E191" s="53"/>
+        <v>66</v>
+      </c>
+      <c r="E191" s="64"/>
       <c r="F191" s="6">
         <v>1700</v>
       </c>
     </row>
-    <row r="192" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:6" ht="15" customHeight="1">
       <c r="B192" s="4">
         <v>46136</v>
       </c>
       <c r="C192" s="43" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D192" s="43" t="s">
-        <v>63</v>
-      </c>
-      <c r="E192" s="53"/>
+        <v>66</v>
+      </c>
+      <c r="E192" s="64"/>
       <c r="F192" s="6">
         <v>115.6</v>
       </c>
     </row>
-    <row r="193" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:6" ht="15" customHeight="1">
       <c r="B193" s="4">
         <v>46136</v>
       </c>
       <c r="C193" s="43" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D193" s="43" t="s">
-        <v>63</v>
-      </c>
-      <c r="E193" s="53"/>
+        <v>66</v>
+      </c>
+      <c r="E193" s="64"/>
       <c r="F193" s="6">
         <v>258.01</v>
       </c>
     </row>
-    <row r="194" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:6" ht="15" customHeight="1">
       <c r="B194" s="4">
         <v>46136</v>
       </c>
       <c r="C194" s="43" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D194" s="43" t="s">
-        <v>215</v>
-      </c>
-      <c r="E194" s="53"/>
+        <v>218</v>
+      </c>
+      <c r="E194" s="64"/>
       <c r="F194" s="6">
         <v>1244.3</v>
       </c>
     </row>
-    <row r="195" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:6" ht="15" customHeight="1">
       <c r="B195" s="4">
         <v>46136</v>
       </c>
       <c r="C195" s="43" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D195" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="E195" s="53"/>
+        <v>69</v>
+      </c>
+      <c r="E195" s="64"/>
       <c r="F195" s="6">
         <v>3941.28</v>
       </c>
     </row>
-    <row r="196" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:6" ht="15" customHeight="1">
       <c r="B196" s="4">
-        <v>46136</v>
-      </c>
-      <c r="D196" s="43"/>
-      <c r="E196" s="53"/>
-    </row>
-    <row r="197" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>46139</v>
+      </c>
+      <c r="C196" s="43" t="s">
+        <v>134</v>
+      </c>
+      <c r="D196" s="43" t="s">
+        <v>219</v>
+      </c>
+      <c r="E196" s="64"/>
+      <c r="F196" s="6">
+        <v>1359.89</v>
+      </c>
+    </row>
+    <row r="197" spans="2:6" ht="15" customHeight="1">
       <c r="B197" s="4">
-        <v>46136</v>
-      </c>
-      <c r="D197" s="43"/>
-      <c r="E197" s="53"/>
-    </row>
-    <row r="198" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>46139</v>
+      </c>
+      <c r="C197" s="43" t="s">
+        <v>220</v>
+      </c>
+      <c r="D197" s="43" t="s">
+        <v>171</v>
+      </c>
+      <c r="E197" s="64"/>
+      <c r="F197" s="6">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="198" spans="2:6" ht="15" customHeight="1">
       <c r="B198" s="4">
-        <v>46136</v>
-      </c>
-      <c r="D198" s="43"/>
-      <c r="E198" s="53"/>
+        <v>46139</v>
+      </c>
+      <c r="C198" s="43" t="s">
+        <v>134</v>
+      </c>
+      <c r="D198" s="43" t="s">
+        <v>134</v>
+      </c>
+      <c r="E198" s="64"/>
+      <c r="F198" s="6">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="199" spans="2:6" ht="15" customHeight="1">
+      <c r="B199" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C199" s="43" t="s">
+        <v>221</v>
+      </c>
+      <c r="D199" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="E199" s="64"/>
+      <c r="F199" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="200" spans="2:6" ht="15" customHeight="1">
+      <c r="B200" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C200" s="43" t="s">
+        <v>222</v>
+      </c>
+      <c r="D200" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="E200" s="64"/>
+      <c r="F200" s="6">
+        <v>142.69999999999999</v>
+      </c>
+    </row>
+    <row r="201" spans="2:6" ht="15" customHeight="1">
+      <c r="B201" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C201" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="D201" s="43" t="s">
+        <v>223</v>
+      </c>
+      <c r="E201" s="64"/>
+      <c r="F201" s="6">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="202" spans="2:6" ht="15" customHeight="1">
+      <c r="B202" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C202" s="43" t="s">
+        <v>224</v>
+      </c>
+      <c r="D202" s="43" t="s">
+        <v>225</v>
+      </c>
+      <c r="E202" s="64"/>
+      <c r="F202" s="6">
+        <v>185.6</v>
+      </c>
+    </row>
+    <row r="203" spans="2:6" ht="15" customHeight="1">
+      <c r="B203" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C203" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="D203" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="E203" s="64"/>
+      <c r="F203" s="6">
+        <v>3480</v>
+      </c>
+    </row>
+    <row r="204" spans="2:6" ht="15" customHeight="1">
+      <c r="B204" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C204" s="43" t="s">
+        <v>227</v>
+      </c>
+      <c r="D204" s="43" t="s">
+        <v>228</v>
+      </c>
+      <c r="E204" s="64"/>
+      <c r="F204" s="6">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="205" spans="2:6" ht="15" customHeight="1">
+      <c r="B205" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C205" s="43" t="s">
+        <v>201</v>
+      </c>
+      <c r="D205" s="43" t="s">
+        <v>229</v>
+      </c>
+      <c r="E205" s="64"/>
+      <c r="F205" s="6">
+        <v>467.59</v>
+      </c>
+    </row>
+    <row r="206" spans="2:6" ht="15" customHeight="1">
+      <c r="B206" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C206" s="43" t="s">
+        <v>230</v>
+      </c>
+      <c r="D206" s="43" t="s">
+        <v>231</v>
+      </c>
+      <c r="E206" s="64"/>
+      <c r="F206" s="6">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="207" spans="2:6" ht="15" customHeight="1">
+      <c r="B207" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C207" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="D207" s="43" t="s">
+        <v>233</v>
+      </c>
+      <c r="E207" s="64"/>
+      <c r="F207" s="6">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="208" spans="2:6" ht="15" customHeight="1">
+      <c r="B208" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C208" s="43" t="s">
+        <v>234</v>
+      </c>
+      <c r="D208" s="43" t="s">
+        <v>235</v>
+      </c>
+      <c r="E208" s="64"/>
+      <c r="F208" s="6">
+        <v>3513.53</v>
+      </c>
+    </row>
+    <row r="209" spans="2:6" ht="15" customHeight="1">
+      <c r="B209" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C209" s="43" t="s">
+        <v>236</v>
+      </c>
+      <c r="D209" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="E209" s="64"/>
+      <c r="F209" s="6">
+        <v>23958.78</v>
+      </c>
+    </row>
+    <row r="210" spans="2:6" ht="15" customHeight="1">
+      <c r="B210" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C210" s="43" t="s">
+        <v>131</v>
+      </c>
+      <c r="D210" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="E210" s="64"/>
+      <c r="F210" s="6">
+        <v>757.43</v>
+      </c>
+    </row>
+    <row r="211" spans="2:6" ht="15" customHeight="1">
+      <c r="B211" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C211" s="43" t="s">
+        <v>143</v>
+      </c>
+      <c r="D211" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="E211" s="64"/>
+      <c r="F211" s="6">
+        <v>833.33</v>
+      </c>
+    </row>
+    <row r="212" spans="2:6" ht="15" customHeight="1">
+      <c r="B212" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C212" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="D212" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="E212" s="64"/>
+      <c r="F212" s="6">
+        <v>859.48</v>
+      </c>
+    </row>
+    <row r="213" spans="2:6" ht="15" customHeight="1">
+      <c r="B213" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C213" s="43" t="s">
+        <v>127</v>
+      </c>
+      <c r="D213" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="E213" s="64"/>
+      <c r="F213" s="6">
+        <v>36035.22</v>
+      </c>
+    </row>
+    <row r="214" spans="2:6" ht="15" customHeight="1">
+      <c r="B214" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C214" s="43" t="s">
+        <v>130</v>
+      </c>
+      <c r="D214" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="E214" s="64"/>
+      <c r="F214" s="6">
+        <v>880.28</v>
+      </c>
+    </row>
+    <row r="215" spans="2:6" ht="15" customHeight="1">
+      <c r="B215" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C215" s="43" t="s">
+        <v>114</v>
+      </c>
+      <c r="D215" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="E215" s="64"/>
+      <c r="F215" s="6">
+        <v>1717.5</v>
+      </c>
+    </row>
+    <row r="216" spans="2:6" ht="15" customHeight="1">
+      <c r="B216" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C216" s="43" t="s">
+        <v>237</v>
+      </c>
+      <c r="D216" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="E216" s="64"/>
+      <c r="F216" s="6">
+        <v>2072.1</v>
+      </c>
+    </row>
+    <row r="217" spans="2:6" ht="15" customHeight="1">
+      <c r="B217" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C217" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="D217" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="E217" s="64"/>
+      <c r="F217" s="6">
+        <v>2504.25</v>
+      </c>
+    </row>
+    <row r="218" spans="2:6" ht="15" customHeight="1">
+      <c r="B218" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C218" s="43" t="s">
+        <v>169</v>
+      </c>
+      <c r="D218" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="E218" s="64"/>
+      <c r="F218" s="6">
+        <v>17790.04</v>
+      </c>
+    </row>
+    <row r="219" spans="2:6" ht="15" customHeight="1">
+      <c r="B219" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C219" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="D219" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="E219" s="64"/>
+      <c r="F219" s="6">
+        <v>2667.6</v>
+      </c>
+    </row>
+    <row r="220" spans="2:6" ht="15" customHeight="1">
+      <c r="B220" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C220" s="43" t="s">
+        <v>70</v>
+      </c>
+      <c r="D220" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="E220" s="64"/>
+      <c r="F220" s="6">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="221" spans="2:6" ht="15" customHeight="1">
+      <c r="B221" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C221" s="43" t="s">
+        <v>238</v>
+      </c>
+      <c r="D221" s="43" t="s">
+        <v>239</v>
+      </c>
+      <c r="E221" s="64"/>
+      <c r="F221" s="6">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="222" spans="2:6" ht="15" customHeight="1">
+      <c r="B222" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C222" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="D222" s="43" t="s">
+        <v>235</v>
+      </c>
+      <c r="E222" s="64"/>
+      <c r="F222" s="6">
+        <v>1775.9</v>
+      </c>
+    </row>
+    <row r="223" spans="2:6" ht="15" customHeight="1">
+      <c r="B223" s="4"/>
+      <c r="D223" s="43"/>
+      <c r="E223" s="64"/>
+    </row>
+    <row r="224" spans="2:6" ht="15" customHeight="1">
+      <c r="B224" s="4"/>
+      <c r="D224" s="43"/>
+      <c r="E224" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7862,44 +8794,44 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{563D29B1-1023-471C-B57D-0AD257F1C41C}">
   <dimension ref="B1:F121"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="73" t="s">
-        <v>216</v>
-      </c>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-    </row>
-    <row r="3" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:6" ht="14.45"/>
+    <row r="2" spans="2:6" ht="15" customHeight="1">
+      <c r="B2" s="99" t="s">
+        <v>240</v>
+      </c>
+      <c r="C2" s="100"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+    </row>
+    <row r="3" spans="2:6" ht="14.45">
       <c r="B3" s="18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>217</v>
+        <v>241</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="14.45">
       <c r="B4" s="19">
         <v>46116</v>
       </c>
@@ -7910,13 +8842,13 @@
         <v>19567.97</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="F4" s="44" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:6" ht="14.45">
       <c r="B5" s="16">
         <v>46121</v>
       </c>
@@ -7927,13 +8859,13 @@
         <v>1000</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="F5" s="45" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6" ht="14.45">
       <c r="B6" s="19">
         <v>46123</v>
       </c>
@@ -7944,13 +8876,13 @@
         <v>1757.28</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="F6" s="44" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6" ht="14.45">
       <c r="B7" s="16">
         <v>46125</v>
       </c>
@@ -7961,13 +8893,13 @@
         <v>2600</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="F7" s="45" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6" ht="14.45">
       <c r="B8" s="29">
         <v>46133</v>
       </c>
@@ -7978,13 +8910,13 @@
         <v>2092</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="F8" s="44" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:6" ht="14.45">
       <c r="B9" s="26">
         <v>46135</v>
       </c>
@@ -7995,13 +8927,13 @@
         <v>19957.34</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="F9" s="45" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:6" ht="14.45">
       <c r="B10" s="31">
         <v>46137</v>
       </c>
@@ -8012,13 +8944,13 @@
         <v>10000</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="F10" s="44" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6" ht="14.45">
       <c r="B11" s="26">
         <v>46140</v>
       </c>
@@ -8029,13 +8961,13 @@
         <v>6666.67</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="F11" s="45" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6" ht="14.45">
       <c r="B12" s="39">
         <v>46140</v>
       </c>
@@ -8046,13 +8978,13 @@
         <v>3333.34</v>
       </c>
       <c r="E12" s="42" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="F12" s="46" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" ht="14.45">
       <c r="B13" s="33">
         <v>46146</v>
       </c>
@@ -8063,13 +8995,13 @@
         <v>19567.98</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="F13" s="45" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:6" ht="14.45">
       <c r="B14" s="36">
         <v>46153</v>
       </c>
@@ -8080,13 +9012,13 @@
         <v>1757.28</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="F14" s="44" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:6" ht="14.45">
       <c r="B15" s="33">
         <v>46163</v>
       </c>
@@ -8097,13 +9029,13 @@
         <v>2092</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="F15" s="45" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:6" ht="14.45">
       <c r="B16" s="36">
         <v>46167</v>
       </c>
@@ -8114,13 +9046,13 @@
         <v>10000</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="F16" s="44" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" ht="14.45">
       <c r="B17" s="33">
         <v>46184</v>
       </c>
@@ -8131,13 +9063,13 @@
         <v>1758.28</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="F17" s="45" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" ht="14.45">
       <c r="B18" s="36">
         <v>46198</v>
       </c>
@@ -8148,115 +9080,115 @@
         <v>10000</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="F18" s="44" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="24" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="25" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="26" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="31" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="2:6" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="33" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="34" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="35" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="36" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="37" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="38" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="39" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="40" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="41" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="42" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="43" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="44" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="45" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="46" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="47" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="48" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="49" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="50" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="51" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="52" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="53" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="54" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="55" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="56" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="57" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="58" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="59" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="60" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="61" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="62" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="63" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="64" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="65" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="66" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="67" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="68" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="69" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="70" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="71" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="72" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="73" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="74" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="75" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="76" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="77" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="78" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="79" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="80" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="81" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="82" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="83" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="84" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="85" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="86" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="87" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="88" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="89" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="90" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="91" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="92" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="93" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="94" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="95" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="96" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="97" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="98" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="99" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="100" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="101" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="102" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="103" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="104" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="105" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="106" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="107" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="108" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="109" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="110" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="111" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="112" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="113" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="114" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="115" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="116" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="117" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="118" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="119" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="120" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="121" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="2:6" ht="14.45"/>
+    <row r="20" spans="2:6" ht="14.45"/>
+    <row r="21" spans="2:6" ht="14.45"/>
+    <row r="22" spans="2:6" ht="14.45"/>
+    <row r="23" spans="2:6" ht="14.45"/>
+    <row r="24" spans="2:6" ht="14.45"/>
+    <row r="25" spans="2:6" ht="14.45"/>
+    <row r="26" spans="2:6" ht="14.45"/>
+    <row r="27" spans="2:6" ht="14.45"/>
+    <row r="28" spans="2:6" ht="14.45"/>
+    <row r="29" spans="2:6" ht="14.45"/>
+    <row r="30" spans="2:6" ht="14.45"/>
+    <row r="31" spans="2:6" ht="14.45"/>
+    <row r="32" spans="2:6" ht="14.45"/>
+    <row r="33" ht="14.45"/>
+    <row r="34" ht="14.45"/>
+    <row r="35" ht="14.45"/>
+    <row r="36" ht="14.45"/>
+    <row r="37" ht="14.45"/>
+    <row r="38" ht="14.45"/>
+    <row r="39" ht="14.45"/>
+    <row r="40" ht="14.45"/>
+    <row r="41" ht="14.45"/>
+    <row r="42" ht="14.45"/>
+    <row r="43" ht="14.45"/>
+    <row r="44" ht="14.45"/>
+    <row r="45" ht="14.45"/>
+    <row r="46" ht="14.45"/>
+    <row r="47" ht="14.45"/>
+    <row r="48" ht="14.45"/>
+    <row r="49" ht="14.45"/>
+    <row r="50" ht="14.45"/>
+    <row r="51" ht="14.45"/>
+    <row r="52" ht="14.45"/>
+    <row r="53" ht="14.45"/>
+    <row r="54" ht="14.45"/>
+    <row r="55" ht="14.45"/>
+    <row r="56" ht="14.45"/>
+    <row r="57" ht="14.45"/>
+    <row r="58" ht="14.45"/>
+    <row r="59" ht="14.45"/>
+    <row r="60" ht="14.45"/>
+    <row r="61" ht="14.45"/>
+    <row r="62" ht="14.45"/>
+    <row r="63" ht="14.45"/>
+    <row r="64" ht="14.45"/>
+    <row r="65" ht="14.45"/>
+    <row r="66" ht="14.45"/>
+    <row r="67" ht="14.45"/>
+    <row r="68" ht="14.45"/>
+    <row r="69" ht="14.45"/>
+    <row r="70" ht="14.45"/>
+    <row r="71" ht="14.45"/>
+    <row r="72" ht="14.45"/>
+    <row r="73" ht="14.45"/>
+    <row r="74" ht="14.45"/>
+    <row r="75" ht="14.45"/>
+    <row r="76" ht="14.45"/>
+    <row r="77" ht="14.45"/>
+    <row r="78" ht="14.45"/>
+    <row r="79" ht="14.45"/>
+    <row r="80" ht="14.45"/>
+    <row r="81" ht="14.45"/>
+    <row r="82" ht="14.45"/>
+    <row r="83" ht="14.45"/>
+    <row r="84" ht="14.45"/>
+    <row r="85" ht="14.45"/>
+    <row r="86" ht="14.45"/>
+    <row r="87" ht="14.45"/>
+    <row r="88" ht="14.45"/>
+    <row r="89" ht="14.45"/>
+    <row r="90" ht="14.45"/>
+    <row r="91" ht="14.45"/>
+    <row r="92" ht="14.45"/>
+    <row r="93" ht="14.45"/>
+    <row r="94" ht="14.45"/>
+    <row r="95" ht="14.45"/>
+    <row r="96" ht="14.45"/>
+    <row r="97" ht="14.45"/>
+    <row r="98" ht="14.45"/>
+    <row r="99" ht="14.45"/>
+    <row r="100" ht="14.45"/>
+    <row r="101" ht="14.45"/>
+    <row r="102" ht="14.45"/>
+    <row r="103" ht="14.45"/>
+    <row r="104" ht="14.45"/>
+    <row r="105" ht="14.45"/>
+    <row r="106" ht="14.45"/>
+    <row r="107" ht="14.45"/>
+    <row r="108" ht="14.45"/>
+    <row r="109" ht="14.45"/>
+    <row r="110" ht="14.45"/>
+    <row r="111" ht="14.45"/>
+    <row r="112" ht="14.45"/>
+    <row r="113" ht="14.45"/>
+    <row r="114" ht="14.45"/>
+    <row r="115" ht="14.45"/>
+    <row r="116" ht="14.45"/>
+    <row r="117" ht="14.45"/>
+    <row r="118" ht="14.45"/>
+    <row r="119" ht="14.45"/>
+    <row r="120" ht="14.45"/>
+    <row r="121" ht="14.45"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:F2"/>
@@ -8268,701 +9200,793 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E746537A-A23A-41AB-9161-94E002D525F0}">
-  <dimension ref="B1:G45"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:G55"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="2.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="2.7109375" customWidth="1"/>
     <col min="7" max="7" width="31" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:7">
       <c r="E1" s="12">
         <f>SUM(Tabela1356[(R$) Valor])</f>
-        <v>670865.03999999992</v>
-      </c>
-    </row>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B2" s="69" t="s">
-        <v>222</v>
-      </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
+        <v>680527.04999999993</v>
+      </c>
+    </row>
+    <row r="2" spans="2:7">
+      <c r="B2" s="95" t="s">
+        <v>246</v>
+      </c>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
       <c r="G2" s="7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7">
       <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7">
       <c r="B4" s="4">
         <v>46113</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="E4" s="6">
         <v>8466.75</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7">
       <c r="B5" s="4">
         <v>46113</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D5" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E5" s="6">
         <v>77304.600000000006</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7">
       <c r="B6" s="4">
         <v>46113</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D6" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E6" s="6">
         <v>108346.92</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7">
       <c r="B7" s="4">
         <v>46113</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E7" s="6">
         <v>17669</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7">
       <c r="B8" s="4">
         <v>46113</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="D8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E8" s="6">
         <v>10540.58</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7">
       <c r="B9" s="4">
         <v>46113</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D9" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E9" s="6">
         <v>13028.88</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B10" s="59">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7">
+      <c r="B10" s="57">
         <v>46113</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D10" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E10" s="6">
         <v>1515.7</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7">
       <c r="B11" s="4">
         <v>46113</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="E11" s="6">
         <v>63.3</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7">
       <c r="B12" s="4">
         <v>46113</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D12" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E12" s="6">
         <v>443.43</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7">
       <c r="B13" s="4">
         <v>46114</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="E13" s="6">
         <v>1485.8</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7">
       <c r="B14" s="4">
         <v>46114</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="E14" s="6">
         <v>707.16</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7">
       <c r="B15" s="4">
         <v>46118</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D15" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E15" s="6">
         <v>582.13</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7">
       <c r="B16" s="4">
         <v>46118</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E16" s="6">
         <v>2770.07</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7">
       <c r="B17" s="4">
         <v>46118</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D17" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E17" s="6">
         <v>2882.43</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7">
       <c r="B18" s="4">
         <v>46118</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D18" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E18" s="6">
         <v>81122.3</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7">
       <c r="B19" s="4">
         <v>46118</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D19" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="E19" s="6">
         <v>8974.76</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7">
       <c r="B20" s="4">
         <v>46119</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D20" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="E20" s="6">
         <v>14500</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7">
       <c r="B21" s="4">
         <v>46121</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D21" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="E21" s="6">
         <v>142.22</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7">
       <c r="B22" s="4">
         <v>46121</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D22" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E22" s="6">
         <v>3504</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7">
       <c r="B23" s="4">
         <v>46121</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D23" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="E23" s="6">
         <v>11823.84</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7">
       <c r="B24" s="4">
         <v>46121</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D24" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="E24" s="6">
         <v>14500</v>
       </c>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:7">
       <c r="B25" s="4">
         <v>46126</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D25" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E25" s="6">
         <v>873</v>
       </c>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:7">
       <c r="B26" s="4">
         <v>46126</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D26" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E26" s="6">
         <v>692.45</v>
       </c>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:7">
       <c r="B27" s="4">
         <v>46126</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D27" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E27" s="6">
         <v>7681.08</v>
       </c>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:7">
       <c r="B28" s="4">
         <v>46126</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D28" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E28" s="6">
         <v>99715.1</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:7">
       <c r="B29" s="4">
         <v>46126</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D29" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="E29" s="6">
         <v>1437</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:7">
       <c r="B30" s="4">
         <v>46126</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D30" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="E30" s="6">
         <v>37</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:7">
       <c r="B31" s="4">
         <v>46126</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="D31" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="E31" s="6">
         <v>13020.4</v>
       </c>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:7">
       <c r="B32" s="4">
         <v>46126</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D32" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="E32" s="6">
         <v>8974.75</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:5">
       <c r="B33" s="4">
         <v>46126</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D33" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="E33" s="6">
         <v>534.5</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:5">
       <c r="B34" s="4">
         <v>46126</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D34" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="E34" s="6">
         <v>1680</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:5">
       <c r="B35" s="4">
         <v>46126</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D35" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="E35" s="6">
         <v>4390</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:5">
       <c r="B36" s="4">
         <v>46127</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D36" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="E36" s="6">
         <v>8024</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:5">
       <c r="B37" s="4">
         <v>46127</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D37" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="E37" s="6">
         <v>20357.04</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:5">
       <c r="B38" s="4">
         <v>46128</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D38" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="E38" s="6">
         <v>3300.7</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:5">
       <c r="B39" s="4">
         <v>46129</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D39" t="s">
-        <v>233</v>
+        <v>256</v>
       </c>
       <c r="E39" s="6">
         <v>4763.3999999999996</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:5">
       <c r="B40" s="4">
         <v>46134</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D40" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="E40" s="6">
         <v>11765</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:5">
       <c r="B41" s="4">
         <v>46134</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D41" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="E41" s="6">
         <v>1958.46</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:5">
       <c r="B42" s="4">
         <v>46134</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D42" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E42" s="6">
         <v>1522.95</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:5">
       <c r="B43" s="4">
         <v>46134</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D43" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E43" s="6">
         <v>41442.46</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:5">
       <c r="B44" s="4">
         <v>46134</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D44" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E44" s="6">
         <v>57885.279999999999</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:5">
       <c r="B45" s="4">
         <v>46134</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D45" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E45" s="6">
         <v>436.6</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5">
+      <c r="B46" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D46" t="s">
+        <v>257</v>
+      </c>
+      <c r="E46" s="6">
+        <v>256.95999999999998</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5">
+      <c r="B47" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D47" t="s">
+        <v>259</v>
+      </c>
+      <c r="E47" s="6">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5">
+      <c r="B48" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D48" t="s">
+        <v>251</v>
+      </c>
+      <c r="E48" s="6">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5">
+      <c r="B49" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D49" t="s">
+        <v>254</v>
+      </c>
+      <c r="E49" s="6">
+        <v>6880</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5">
+      <c r="B50" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D50" t="s">
+        <v>249</v>
+      </c>
+      <c r="E50" s="6">
+        <v>191.55</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5">
+      <c r="B51" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D51" t="s">
+        <v>260</v>
+      </c>
+      <c r="E51" s="6">
+        <v>1453.5</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5">
+      <c r="B52" s="4"/>
+    </row>
+    <row r="55" spans="2:5">
+      <c r="E55" s="6" t="s">
+        <v>261</v>
       </c>
     </row>
   </sheetData>

--- a/Gott Bike/INDICADORES DIÁRIOS.xlsx
+++ b/Gott Bike/INDICADORES DIÁRIOS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8d3dd0af008984df/Consultorias/GOTT BIKE/Compartilhado GOTT Bike/Indicadores e Métricas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8d3dd0af008984df/Consultorias/GitHub/Cotta-Consultoria/Gott Bike/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2546" documentId="8_{49B7964F-2481-4178-A148-E82770C67CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8653D045-8291-406A-A84D-DF033781A297}"/>
+  <xr:revisionPtr revIDLastSave="2547" documentId="8_{49B7964F-2481-4178-A148-E82770C67CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C6CCBD5-DBCB-40E9-9BD4-07F02F87ABCD}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{AF016D11-4BBA-49FD-9799-541824B780DA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AF016D11-4BBA-49FD-9799-541824B780DA}"/>
   </bookViews>
   <sheets>
     <sheet name="Faturamento" sheetId="4" r:id="rId1"/>
@@ -1212,7 +1212,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1360,37 +1360,19 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1399,7 +1381,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="12" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1413,21 +1395,16 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="13" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1446,7 +1423,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -1509,69 +1485,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="ddd\ dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -1611,13 +1524,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color theme="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color theme="1"/>
         </left>
@@ -1650,6 +1556,13 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="1"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1741,13 +1654,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color theme="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color theme="1"/>
         </left>
@@ -1782,6 +1688,13 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1808,6 +1721,69 @@
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="ddd\ dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="ddd\ dd/mm/yyyy"/>
@@ -1862,14 +1838,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4D968E04-06EF-4CC7-9C6F-A57B1CBB5F4B}" name="Tabela1" displayName="Tabela1" ref="B3:E111" totalsRowShown="0" headerRowDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4D968E04-06EF-4CC7-9C6F-A57B1CBB5F4B}" name="Tabela1" displayName="Tabela1" ref="B3:E111" totalsRowShown="0" headerRowDxfId="22">
   <autoFilter ref="B3:E111" xr:uid="{4D968E04-06EF-4CC7-9C6F-A57B1CBB5F4B}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:E89">
     <sortCondition ref="B3:B89"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{BB065966-614D-4168-B93D-A210BB1E0C8D}" name="Data" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{0E418006-DCE5-4F97-93B4-A899D67631E7}" name="Qtde" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{BB065966-614D-4168-B93D-A210BB1E0C8D}" name="Data" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{0E418006-DCE5-4F97-93B4-A899D67631E7}" name="Qtde" dataDxfId="20"/>
     <tableColumn id="3" xr3:uid="{5E9349A6-F048-4999-B707-3D89C965382E}" name="Plataforma"/>
     <tableColumn id="4" xr3:uid="{11AA1DC1-1AE5-4E49-B53D-967E3111E872}" name="(R$) Valor" dataCellStyle="Moeda"/>
   </tableColumns>
@@ -1878,22 +1854,22 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0EF1F2A8-F80A-407B-8B7B-0BFBFEDF6A0D}" name="Tabela8" displayName="Tabela8" ref="G2:G10" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26" headerRowBorderDxfId="24" tableBorderDxfId="25" totalsRowBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0EF1F2A8-F80A-407B-8B7B-0BFBFEDF6A0D}" name="Tabela8" displayName="Tabela8" ref="G2:G10" totalsRowShown="0" headerRowDxfId="19" dataDxfId="17" headerRowBorderDxfId="18" tableBorderDxfId="16" totalsRowBorderDxfId="15">
   <autoFilter ref="G2:G10" xr:uid="{0EF1F2A8-F80A-407B-8B7B-0BFBFEDF6A0D}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{047DC460-557A-40DB-8C81-95DF946F5AD7}" name="PLATAFORMAS" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{047DC460-557A-40DB-8C81-95DF946F5AD7}" name="PLATAFORMAS" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6EB69137-5DEF-4DEE-A295-1FA4C5115578}" name="Tabela135" displayName="Tabela135" ref="B3:F65" totalsRowShown="0" headerRowDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6EB69137-5DEF-4DEE-A295-1FA4C5115578}" name="Tabela135" displayName="Tabela135" ref="B3:F65" totalsRowShown="0" headerRowDxfId="13">
   <autoFilter ref="B3:F65" xr:uid="{6EB69137-5DEF-4DEE-A295-1FA4C5115578}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{F39CB7F4-E762-4BDF-B2C6-8749DB68D027}" name="Data"/>
-    <tableColumn id="2" xr3:uid="{E9E42632-7C2F-4C97-BCA4-C914BCBA10DC}" name="Banco" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{5B08F7C6-B877-42F6-98D4-8D56834BE254}" name="Plataforma" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{E9E42632-7C2F-4C97-BCA4-C914BCBA10DC}" name="Banco" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{5B08F7C6-B877-42F6-98D4-8D56834BE254}" name="Plataforma" dataDxfId="11"/>
     <tableColumn id="6" xr3:uid="{F7822F46-F359-40F0-8736-0420E5F8BEF4}" name="Descrição"/>
     <tableColumn id="4" xr3:uid="{D0BDF5C5-4A71-4AC2-A4FF-BA03AF90DFCB}" name="(R$) Valor" dataCellStyle="Moeda"/>
   </tableColumns>
@@ -1902,17 +1878,17 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{67A3570C-9B27-40AF-9CD6-28857E5EBB30}" name="Tabela810" displayName="Tabela810" ref="P2:P14" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17" headerRowBorderDxfId="15" tableBorderDxfId="16" totalsRowBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{67A3570C-9B27-40AF-9CD6-28857E5EBB30}" name="Tabela810" displayName="Tabela810" ref="P2:P14" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7" totalsRowBorderDxfId="6">
   <autoFilter ref="P2:P14" xr:uid="{67A3570C-9B27-40AF-9CD6-28857E5EBB30}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{9127BBB1-B684-40F8-8735-E6EFF2611541}" name="PLATAFORMAS" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{9127BBB1-B684-40F8-8735-E6EFF2611541}" name="PLATAFORMAS" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C40E1681-2A06-40B2-9F0F-8A80EAD60188}" name="Tabela13" displayName="Tabela13" ref="B3:G224" totalsRowShown="0" headerRowDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C40E1681-2A06-40B2-9F0F-8A80EAD60188}" name="Tabela13" displayName="Tabela13" ref="B3:G224" totalsRowShown="0" headerRowDxfId="30">
   <autoFilter ref="B3:G224" xr:uid="{C40E1681-2A06-40B2-9F0F-8A80EAD60188}">
     <filterColumn colId="0">
       <filters>
@@ -1921,10 +1897,10 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{6CE0E58B-6690-45A4-8D8F-962F67B0773A}" name="Data" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{9BD39337-5CC3-45E0-9CCF-8A1AF726B1E7}" name="Fornecedor" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{83C7ADF5-BFC9-4593-8DC5-4C3E3C16ED71}" name="Classificação" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{75D7101C-1F6F-4866-AE9B-8E1020F00ABA}" name="Transferência" dataDxfId="8" dataCellStyle="Moeda"/>
+    <tableColumn id="1" xr3:uid="{6CE0E58B-6690-45A4-8D8F-962F67B0773A}" name="Data" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{9BD39337-5CC3-45E0-9CCF-8A1AF726B1E7}" name="Fornecedor" dataDxfId="28"/>
+    <tableColumn id="6" xr3:uid="{83C7ADF5-BFC9-4593-8DC5-4C3E3C16ED71}" name="Classificação" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{75D7101C-1F6F-4866-AE9B-8E1020F00ABA}" name="Transferência" dataDxfId="26" dataCellStyle="Moeda"/>
     <tableColumn id="4" xr3:uid="{6D5478EE-2C1F-4D7A-AA31-67FDC70DDD6E}" name="(R$) Valor" dataCellStyle="Moeda"/>
     <tableColumn id="5" xr3:uid="{49C1FEB7-BB7F-4941-A01E-990EEBF05392}" name="Coluna1"/>
   </tableColumns>
@@ -1933,13 +1909,13 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{E28072D7-5426-41A3-ADCC-07A04FBBA8A3}" name="Tabela6" displayName="Tabela6" ref="H2:H88" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{E28072D7-5426-41A3-ADCC-07A04FBBA8A3}" name="Tabela6" displayName="Tabela6" ref="H2:H88" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
   <autoFilter ref="H2:H88" xr:uid="{E28072D7-5426-41A3-ADCC-07A04FBBA8A3}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H3:H88">
     <sortCondition ref="H2:H88"/>
   </sortState>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{B8D45F4A-1FA5-4A2C-99C2-02A8C6CF34F3}" name="CADASTRO FORNECEDORES" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{B8D45F4A-1FA5-4A2C-99C2-02A8C6CF34F3}" name="CADASTRO FORNECEDORES" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2286,20 +2262,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{152610B4-81C2-44F7-A8DF-A454E1B8F2ED}">
   <dimension ref="B1:L110"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="29.5703125" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="2.7109375" customWidth="1"/>
-    <col min="7" max="7" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="2.7109375" customWidth="1"/>
-    <col min="9" max="9" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.85546875" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="29.5546875" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="2.6640625" customWidth="1"/>
+    <col min="7" max="7" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.6640625" customWidth="1"/>
+    <col min="9" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.88671875" customWidth="1"/>
     <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12">
@@ -2313,12 +2289,12 @@
       </c>
     </row>
     <row r="2" spans="2:12">
-      <c r="B2" s="95" t="s">
+      <c r="B2" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
       <c r="G2" s="10" t="s">
         <v>1</v>
       </c>
@@ -2359,11 +2335,12 @@
         <v>1206212.9100000001</v>
       </c>
       <c r="K3" s="59">
-        <v>1704</v>
+        <f>C1</f>
+        <v>1606</v>
       </c>
       <c r="L3" s="53">
         <f>IFERROR(J3/K3,0)</f>
-        <v>707.87142605633812</v>
+        <v>751.06656911581581</v>
       </c>
     </row>
     <row r="4" spans="2:12">
@@ -3908,53 +3885,53 @@
   <dimension ref="B1:P65"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="60.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.140625" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="60.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.109375" customWidth="1"/>
+    <col min="8" max="8" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="3.7109375" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.140625" customWidth="1"/>
-    <col min="16" max="16" width="18.5703125" customWidth="1"/>
+    <col min="11" max="11" width="3.6640625" customWidth="1"/>
+    <col min="12" max="12" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.109375" customWidth="1"/>
+    <col min="16" max="16" width="18.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16">
+    <row r="1" spans="2:16" ht="14.4">
       <c r="F1" s="12">
         <f>SUBTOTAL(9,Tabela135[(R$) Valor])</f>
         <v>852200.21</v>
       </c>
     </row>
-    <row r="2" spans="2:16">
-      <c r="B2" s="95" t="s">
+    <row r="2" spans="2:16" ht="14.4">
+      <c r="B2" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="H2" s="96" t="s">
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="H2" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="97"/>
-      <c r="J2" s="98"/>
-      <c r="L2" s="96" t="s">
+      <c r="I2" s="86"/>
+      <c r="J2" s="87"/>
+      <c r="L2" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="97"/>
-      <c r="N2" s="98"/>
+      <c r="M2" s="86"/>
+      <c r="N2" s="87"/>
       <c r="P2" s="10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:16">
+    <row r="3" spans="2:16" ht="14.4">
       <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
@@ -3992,7 +3969,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="2:16">
+    <row r="4" spans="2:16" ht="14.4">
       <c r="B4" s="4">
         <v>46114</v>
       </c>
@@ -4008,19 +3985,19 @@
       <c r="F4" s="6">
         <v>20435</v>
       </c>
-      <c r="H4" s="65">
+      <c r="H4" s="63">
         <v>46030</v>
       </c>
-      <c r="I4" s="86">
+      <c r="I4" s="76">
         <v>1021.54</v>
       </c>
       <c r="J4" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="L4" s="71">
+      <c r="L4" s="63">
         <v>46118</v>
       </c>
-      <c r="M4" s="86">
+      <c r="M4" s="76">
         <v>655</v>
       </c>
       <c r="N4" s="22" t="s">
@@ -4030,7 +4007,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:16">
+    <row r="5" spans="2:16" ht="14.4">
       <c r="B5" s="4">
         <v>46118</v>
       </c>
@@ -4046,29 +4023,29 @@
       <c r="F5" s="6">
         <v>13502</v>
       </c>
-      <c r="H5" s="66">
+      <c r="H5" s="64">
         <v>46042</v>
       </c>
-      <c r="I5" s="87">
+      <c r="I5" s="77">
         <v>26000</v>
       </c>
       <c r="J5" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="L5" s="74">
+      <c r="L5" s="64">
         <v>46129</v>
       </c>
-      <c r="M5" s="93">
+      <c r="M5" s="77">
         <v>2214.86</v>
       </c>
-      <c r="N5" s="79" t="s">
+      <c r="N5" s="23" t="s">
         <v>30</v>
       </c>
       <c r="P5" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="2:16">
+    <row r="6" spans="2:16" ht="14.4">
       <c r="B6" s="4">
         <v>46118</v>
       </c>
@@ -4084,19 +4061,19 @@
       <c r="F6" s="6">
         <v>82.59</v>
       </c>
-      <c r="H6" s="65">
+      <c r="H6" s="63">
         <v>46051</v>
       </c>
-      <c r="I6" s="86">
+      <c r="I6" s="76">
         <v>6559</v>
       </c>
       <c r="J6" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="L6" s="76">
+      <c r="L6" s="68">
         <v>46129</v>
       </c>
-      <c r="M6" s="86">
+      <c r="M6" s="76">
         <v>490.83</v>
       </c>
       <c r="N6" s="22" t="s">
@@ -4106,7 +4083,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="2:16">
+    <row r="7" spans="2:16" ht="14.4">
       <c r="B7" s="4">
         <v>46118</v>
       </c>
@@ -4122,29 +4099,29 @@
       <c r="F7" s="6">
         <v>266.32</v>
       </c>
-      <c r="H7" s="66">
+      <c r="H7" s="64">
         <v>46087</v>
       </c>
-      <c r="I7" s="87">
+      <c r="I7" s="77">
         <v>14000</v>
       </c>
       <c r="J7" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="L7" s="74">
+      <c r="L7" s="64">
         <v>46129</v>
       </c>
-      <c r="M7" s="93">
+      <c r="M7" s="77">
         <v>1330.36</v>
       </c>
-      <c r="N7" s="79" t="s">
+      <c r="N7" s="23" t="s">
         <v>30</v>
       </c>
       <c r="P7" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="2:16">
+    <row r="8" spans="2:16" ht="14.4">
       <c r="B8" s="4">
         <v>46118</v>
       </c>
@@ -4160,19 +4137,19 @@
       <c r="F8" s="6">
         <v>0</v>
       </c>
-      <c r="H8" s="65">
+      <c r="H8" s="63">
         <v>46090</v>
       </c>
-      <c r="I8" s="86">
+      <c r="I8" s="76">
         <v>24200</v>
       </c>
       <c r="J8" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="L8" s="71">
+      <c r="L8" s="63">
         <v>46140</v>
       </c>
-      <c r="M8" s="86">
+      <c r="M8" s="76">
         <v>655.17999999999995</v>
       </c>
       <c r="N8" s="22" t="s">
@@ -4182,7 +4159,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="2:16">
+    <row r="9" spans="2:16" ht="14.4">
       <c r="B9" s="4">
         <v>46118</v>
       </c>
@@ -4198,29 +4175,29 @@
       <c r="F9" s="6">
         <v>46650</v>
       </c>
-      <c r="H9" s="66">
+      <c r="H9" s="64">
         <v>46119</v>
       </c>
-      <c r="I9" s="87">
+      <c r="I9" s="77">
         <v>3200</v>
       </c>
       <c r="J9" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="L9" s="74">
+      <c r="L9" s="64">
         <v>46140</v>
       </c>
-      <c r="M9" s="93">
+      <c r="M9" s="77">
         <v>1767.85</v>
       </c>
-      <c r="N9" s="79" t="s">
+      <c r="N9" s="23" t="s">
         <v>30</v>
       </c>
       <c r="P9" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="2:16">
+    <row r="10" spans="2:16" ht="14.4">
       <c r="B10" s="4">
         <v>46119</v>
       </c>
@@ -4236,19 +4213,19 @@
       <c r="F10" s="6">
         <v>542.97</v>
       </c>
-      <c r="H10" s="65">
+      <c r="H10" s="63">
         <v>46122</v>
       </c>
-      <c r="I10" s="86">
+      <c r="I10" s="76">
         <v>2000</v>
       </c>
       <c r="J10" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="L10" s="71">
+      <c r="L10" s="63">
         <v>46140</v>
       </c>
-      <c r="M10" s="86">
+      <c r="M10" s="76">
         <v>2854</v>
       </c>
       <c r="N10" s="22" t="s">
@@ -4258,7 +4235,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="2:16">
+    <row r="11" spans="2:16" ht="14.4">
       <c r="B11" s="4">
         <v>46119</v>
       </c>
@@ -4274,23 +4251,23 @@
       <c r="F11" s="6">
         <v>50000</v>
       </c>
-      <c r="H11" s="66">
+      <c r="H11" s="64">
         <v>46129</v>
       </c>
-      <c r="I11" s="87">
+      <c r="I11" s="77">
         <v>4300</v>
       </c>
       <c r="J11" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="L11" s="72"/>
-      <c r="M11" s="93"/>
+      <c r="L11" s="64"/>
+      <c r="M11" s="77"/>
       <c r="N11" s="23"/>
       <c r="P11" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="2:16">
+    <row r="12" spans="2:16" ht="14.4">
       <c r="B12" s="4">
         <v>46119</v>
       </c>
@@ -4303,23 +4280,23 @@
       <c r="F12" s="6">
         <v>3200</v>
       </c>
-      <c r="H12" s="65">
+      <c r="H12" s="63">
         <v>46132</v>
       </c>
-      <c r="I12" s="88">
+      <c r="I12" s="78">
         <v>4825</v>
       </c>
-      <c r="J12" s="67" t="s">
+      <c r="J12" s="65" t="s">
         <v>30</v>
       </c>
-      <c r="L12" s="71"/>
-      <c r="M12" s="86"/>
-      <c r="N12" s="67"/>
+      <c r="L12" s="63"/>
+      <c r="M12" s="76"/>
+      <c r="N12" s="65"/>
       <c r="P12" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="2:16">
+    <row r="13" spans="2:16" ht="14.4">
       <c r="B13" s="4">
         <v>46120</v>
       </c>
@@ -4335,23 +4312,23 @@
       <c r="F13" s="6">
         <v>350</v>
       </c>
-      <c r="H13" s="66">
+      <c r="H13" s="64">
         <v>46134</v>
       </c>
-      <c r="I13" s="89">
+      <c r="I13" s="79">
         <v>10000</v>
       </c>
-      <c r="J13" s="62" t="s">
+      <c r="J13" s="61" t="s">
         <v>29</v>
       </c>
-      <c r="L13" s="72"/>
-      <c r="M13" s="94"/>
-      <c r="N13" s="62"/>
+      <c r="L13" s="64"/>
+      <c r="M13" s="82"/>
+      <c r="N13" s="61"/>
       <c r="P13" s="8" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="2:16">
+    <row r="14" spans="2:16" ht="14.4">
       <c r="B14" s="4">
         <v>46120</v>
       </c>
@@ -4367,23 +4344,23 @@
       <c r="F14" s="6">
         <v>24769</v>
       </c>
-      <c r="H14" s="65">
+      <c r="H14" s="63">
         <v>46134</v>
       </c>
-      <c r="I14" s="88">
+      <c r="I14" s="78">
         <v>22000</v>
       </c>
       <c r="J14" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="L14" s="71"/>
-      <c r="M14" s="86"/>
+      <c r="L14" s="63"/>
+      <c r="M14" s="76"/>
       <c r="N14" s="22"/>
       <c r="P14" s="11" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="2:16">
+    <row r="15" spans="2:16" ht="14.4">
       <c r="B15" s="4">
         <v>46121</v>
       </c>
@@ -4399,20 +4376,20 @@
       <c r="F15" s="6">
         <v>469.86</v>
       </c>
-      <c r="H15" s="66">
+      <c r="H15" s="64">
         <v>46137</v>
       </c>
-      <c r="I15" s="89">
+      <c r="I15" s="79">
         <v>10000</v>
       </c>
-      <c r="J15" s="62" t="s">
+      <c r="J15" s="61" t="s">
         <v>30</v>
       </c>
-      <c r="L15" s="72"/>
-      <c r="M15" s="93"/>
-      <c r="N15" s="62"/>
-    </row>
-    <row r="16" spans="2:16">
+      <c r="L15" s="64"/>
+      <c r="M15" s="77"/>
+      <c r="N15" s="61"/>
+    </row>
+    <row r="16" spans="2:16" ht="14.4">
       <c r="B16" s="4">
         <v>46121</v>
       </c>
@@ -4428,20 +4405,20 @@
       <c r="F16" s="6">
         <v>50000</v>
       </c>
-      <c r="H16" s="70">
+      <c r="H16" s="67">
         <v>46137</v>
       </c>
-      <c r="I16" s="88">
+      <c r="I16" s="78">
         <v>7770</v>
       </c>
-      <c r="J16" s="67" t="s">
+      <c r="J16" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="L16" s="73"/>
-      <c r="M16" s="86"/>
-      <c r="N16" s="67"/>
-    </row>
-    <row r="17" spans="2:14">
+      <c r="L16" s="67"/>
+      <c r="M16" s="76"/>
+      <c r="N16" s="65"/>
+    </row>
+    <row r="17" spans="2:14" ht="14.4">
       <c r="B17" s="4">
         <v>46122</v>
       </c>
@@ -4457,20 +4434,20 @@
       <c r="F17" s="6">
         <v>2290.2800000000002</v>
       </c>
-      <c r="H17" s="70">
+      <c r="H17" s="67">
         <v>46139</v>
       </c>
-      <c r="I17" s="90">
+      <c r="I17" s="79">
         <v>5200</v>
       </c>
       <c r="J17" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="L17" s="77"/>
-      <c r="M17" s="93"/>
-      <c r="N17" s="79"/>
-    </row>
-    <row r="18" spans="2:14">
+      <c r="L17" s="69"/>
+      <c r="M17" s="77"/>
+      <c r="N17" s="23"/>
+    </row>
+    <row r="18" spans="2:14" ht="14.4">
       <c r="B18" s="4">
         <v>46122</v>
       </c>
@@ -4490,10 +4467,10 @@
       <c r="I18" s="22"/>
       <c r="J18" s="22"/>
       <c r="L18" s="21"/>
-      <c r="M18" s="86"/>
+      <c r="M18" s="76"/>
       <c r="N18" s="22"/>
     </row>
-    <row r="19" spans="2:14">
+    <row r="19" spans="2:14" ht="14.4">
       <c r="B19" s="4">
         <v>46122</v>
       </c>
@@ -4510,13 +4487,13 @@
         <v>2690.03</v>
       </c>
       <c r="H19" s="15"/>
-      <c r="I19" s="91"/>
+      <c r="I19" s="80"/>
       <c r="J19" s="23"/>
       <c r="L19" s="15"/>
-      <c r="M19" s="93"/>
+      <c r="M19" s="77"/>
       <c r="N19" s="23"/>
     </row>
-    <row r="20" spans="2:14">
+    <row r="20" spans="2:14" ht="14.4">
       <c r="B20" s="4">
         <v>46122</v>
       </c>
@@ -4533,13 +4510,13 @@
         <v>2476.36</v>
       </c>
       <c r="H20" s="21"/>
-      <c r="I20" s="92"/>
+      <c r="I20" s="81"/>
       <c r="J20" s="22"/>
       <c r="L20" s="21"/>
-      <c r="M20" s="86"/>
+      <c r="M20" s="76"/>
       <c r="N20" s="22"/>
     </row>
-    <row r="21" spans="2:14">
+    <row r="21" spans="2:14" ht="14.4">
       <c r="B21" s="4">
         <v>46122</v>
       </c>
@@ -4553,13 +4530,13 @@
         <v>140</v>
       </c>
       <c r="H21" s="15"/>
-      <c r="I21" s="91"/>
+      <c r="I21" s="80"/>
       <c r="J21" s="23"/>
       <c r="L21" s="15"/>
-      <c r="M21" s="93"/>
+      <c r="M21" s="77"/>
       <c r="N21" s="23"/>
     </row>
-    <row r="22" spans="2:14">
+    <row r="22" spans="2:14" ht="14.4">
       <c r="B22" s="4">
         <v>46125</v>
       </c>
@@ -4579,10 +4556,10 @@
       <c r="I22" s="22"/>
       <c r="J22" s="22"/>
       <c r="L22" s="21"/>
-      <c r="M22" s="86"/>
+      <c r="M22" s="76"/>
       <c r="N22" s="22"/>
     </row>
-    <row r="23" spans="2:14">
+    <row r="23" spans="2:14" ht="14.4">
       <c r="B23" s="4">
         <v>46125</v>
       </c>
@@ -4599,7 +4576,7 @@
         <v>256.14</v>
       </c>
     </row>
-    <row r="24" spans="2:14">
+    <row r="24" spans="2:14" ht="14.4">
       <c r="B24" s="4">
         <v>46125</v>
       </c>
@@ -4616,7 +4593,7 @@
         <v>27884</v>
       </c>
     </row>
-    <row r="25" spans="2:14">
+    <row r="25" spans="2:14" ht="14.4">
       <c r="B25" s="4">
         <v>46126</v>
       </c>
@@ -4640,7 +4617,7 @@
         <v>797907.13</v>
       </c>
     </row>
-    <row r="26" spans="2:14">
+    <row r="26" spans="2:14" ht="14.4">
       <c r="B26" s="4">
         <v>46127</v>
       </c>
@@ -4664,7 +4641,7 @@
         <v>54293.08</v>
       </c>
     </row>
-    <row r="27" spans="2:14">
+    <row r="27" spans="2:14" ht="14.4">
       <c r="B27" s="4">
         <v>46128</v>
       </c>
@@ -4685,7 +4662,7 @@
         <v>852200.21</v>
       </c>
     </row>
-    <row r="28" spans="2:14">
+    <row r="28" spans="2:14" ht="14.4">
       <c r="B28" s="4">
         <v>46128</v>
       </c>
@@ -4702,7 +4679,7 @@
         <v>30409</v>
       </c>
     </row>
-    <row r="29" spans="2:14">
+    <row r="29" spans="2:14" ht="14.4">
       <c r="B29" s="4">
         <v>46128</v>
       </c>
@@ -5077,7 +5054,7 @@
       <c r="C51" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D51" s="61" t="s">
+      <c r="D51" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F51" s="6">
@@ -5103,16 +5080,16 @@
       <c r="B53" s="4">
         <v>46139</v>
       </c>
-      <c r="C53" s="62" t="s">
+      <c r="C53" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="D53" s="61" t="s">
+      <c r="D53" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E53" t="s">
         <v>28</v>
       </c>
-      <c r="F53" s="63">
+      <c r="F53" s="62">
         <v>7770</v>
       </c>
     </row>
@@ -5120,7 +5097,7 @@
       <c r="B54" s="4">
         <v>46139</v>
       </c>
-      <c r="C54" s="67" t="s">
+      <c r="C54" s="65" t="s">
         <v>27</v>
       </c>
       <c r="D54" s="60" t="s">
@@ -5129,7 +5106,7 @@
       <c r="E54" t="s">
         <v>44</v>
       </c>
-      <c r="F54" s="68">
+      <c r="F54" s="66">
         <v>1456.54</v>
       </c>
     </row>
@@ -5137,16 +5114,16 @@
       <c r="B55" s="4">
         <v>46139</v>
       </c>
-      <c r="C55" s="62" t="s">
+      <c r="C55" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="D55" s="61" t="s">
+      <c r="D55" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E55" t="s">
         <v>28</v>
       </c>
-      <c r="F55" s="63">
+      <c r="F55" s="62">
         <v>5200</v>
       </c>
     </row>
@@ -5154,7 +5131,7 @@
       <c r="B56" s="4">
         <v>46140</v>
       </c>
-      <c r="C56" s="67" t="s">
+      <c r="C56" s="65" t="s">
         <v>27</v>
       </c>
       <c r="D56" s="60" t="s">
@@ -5163,89 +5140,85 @@
       <c r="E56" t="s">
         <v>53</v>
       </c>
-      <c r="F56" s="68">
+      <c r="F56" s="66">
         <v>21423</v>
       </c>
     </row>
     <row r="57" spans="2:6" ht="15" customHeight="1">
-      <c r="B57" s="74">
+      <c r="B57" s="64">
         <v>46118</v>
       </c>
-      <c r="C57" s="69" t="s">
+      <c r="C57" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="D57" s="61" t="s">
+      <c r="D57" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E57" s="78"/>
-      <c r="F57" s="75">
+      <c r="F57" s="17">
         <v>655</v>
       </c>
     </row>
     <row r="58" spans="2:6" ht="15" customHeight="1">
-      <c r="B58" s="74">
+      <c r="B58" s="64">
         <v>46129</v>
       </c>
-      <c r="C58" s="69" t="s">
+      <c r="C58" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="D58" s="61" t="s">
+      <c r="D58" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E58" s="78"/>
-      <c r="F58" s="75">
+      <c r="F58" s="17">
         <v>2214.86</v>
       </c>
     </row>
     <row r="59" spans="2:6" ht="15" customHeight="1">
-      <c r="B59" s="74">
+      <c r="B59" s="64">
         <v>46129</v>
       </c>
-      <c r="C59" s="69" t="s">
+      <c r="C59" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="D59" s="61" t="s">
+      <c r="D59" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E59" s="78"/>
-      <c r="F59" s="75">
+      <c r="F59" s="17">
         <v>490.83</v>
       </c>
     </row>
     <row r="60" spans="2:6" ht="15" customHeight="1">
-      <c r="B60" s="72">
+      <c r="B60" s="64">
         <v>46129</v>
       </c>
-      <c r="C60" s="62" t="s">
+      <c r="C60" s="61" t="s">
         <v>37</v>
       </c>
       <c r="D60" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="F60" s="75">
+      <c r="F60" s="17">
         <v>1330.36</v>
       </c>
     </row>
     <row r="61" spans="2:6" ht="15" customHeight="1">
-      <c r="B61" s="74">
+      <c r="B61" s="64">
         <v>46140</v>
       </c>
-      <c r="C61" s="69" t="s">
+      <c r="C61" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="D61" s="61" t="s">
+      <c r="D61" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E61" s="78"/>
-      <c r="F61" s="75">
+      <c r="F61" s="17">
         <v>655.17999999999995</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="15" customHeight="1">
-      <c r="B62" s="72">
+      <c r="B62" s="64">
         <v>46140</v>
       </c>
-      <c r="C62" s="62" t="s">
+      <c r="C62" s="61" t="s">
         <v>37</v>
       </c>
       <c r="D62" s="60" t="s">
@@ -5256,33 +5229,32 @@
       </c>
     </row>
     <row r="63" spans="2:6" ht="15" customHeight="1">
-      <c r="B63" s="74">
+      <c r="B63" s="64">
         <v>46140</v>
       </c>
-      <c r="C63" s="69" t="s">
+      <c r="C63" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="D63" s="61" t="s">
+      <c r="D63" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E63" s="78"/>
-      <c r="F63" s="75">
+      <c r="F63" s="17">
         <v>2854</v>
       </c>
     </row>
     <row r="64" spans="2:6" ht="15" customHeight="1">
-      <c r="B64" s="80"/>
-      <c r="C64" s="81"/>
-      <c r="D64" s="82"/>
-      <c r="E64" s="80"/>
-      <c r="F64" s="83"/>
+      <c r="B64" s="70"/>
+      <c r="C64" s="71"/>
+      <c r="D64" s="72"/>
+      <c r="E64" s="70"/>
+      <c r="F64" s="73"/>
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1">
-      <c r="B65" s="84"/>
-      <c r="C65" s="69"/>
-      <c r="D65" s="69"/>
-      <c r="E65" s="84"/>
-      <c r="F65" s="85"/>
+      <c r="B65" s="74"/>
+      <c r="C65" s="61"/>
+      <c r="D65" s="61"/>
+      <c r="E65" s="74"/>
+      <c r="F65" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5308,18 +5280,18 @@
   <dimension ref="B1:H224"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.5703125" style="43" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="2.7109375" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.5546875" style="43" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" customWidth="1"/>
     <col min="8" max="8" width="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="2.7109375" customWidth="1"/>
+    <col min="9" max="9" width="2.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8">
+    <row r="1" spans="2:8" ht="14.4">
       <c r="D1" s="55">
         <f>SUM(E1:F1)</f>
         <v>774125.41999999969</v>
@@ -5332,19 +5304,19 @@
         <f>SUBTOTAL(9,Tabela13[(R$) Valor])</f>
         <v>733025.41999999969</v>
       </c>
-      <c r="H1" s="101">
+      <c r="H1" s="83">
         <f>993810.43-F1</f>
         <v>260785.01000000036</v>
       </c>
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1">
-      <c r="B2" s="95" t="s">
+      <c r="B2" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
       <c r="G2" t="s">
         <v>55</v>
       </c>
@@ -5352,7 +5324,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="2:8">
+    <row r="3" spans="2:8" ht="14.4">
       <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
@@ -5375,7 +5347,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="14.45">
+    <row r="4" spans="2:8" ht="14.4">
       <c r="B4" s="4">
         <v>46113</v>
       </c>
@@ -5392,7 +5364,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="14.45">
+    <row r="5" spans="2:8" ht="14.4">
       <c r="B5" s="4">
         <v>46113</v>
       </c>
@@ -5409,7 +5381,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="14.45">
+    <row r="6" spans="2:8" ht="14.4">
       <c r="B6" s="4">
         <v>46113</v>
       </c>
@@ -5426,7 +5398,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="14.45">
+    <row r="7" spans="2:8" ht="14.4">
       <c r="B7" s="4">
         <v>46113</v>
       </c>
@@ -5443,7 +5415,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="14.45">
+    <row r="8" spans="2:8" ht="14.4">
       <c r="B8" s="4">
         <v>46113</v>
       </c>
@@ -5460,7 +5432,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="14.45">
+    <row r="9" spans="2:8" ht="14.4">
       <c r="B9" s="4">
         <v>46113</v>
       </c>
@@ -5477,7 +5449,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="14.45">
+    <row r="10" spans="2:8" ht="14.4">
       <c r="B10" s="4">
         <v>46113</v>
       </c>
@@ -5497,7 +5469,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="14.45">
+    <row r="11" spans="2:8" ht="14.4">
       <c r="B11" s="4">
         <v>46113</v>
       </c>
@@ -5514,7 +5486,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="12" spans="2:8" ht="14.45">
+    <row r="12" spans="2:8" ht="14.4">
       <c r="B12" s="4">
         <v>46114</v>
       </c>
@@ -5531,7 +5503,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="14.45">
+    <row r="13" spans="2:8" ht="14.4">
       <c r="B13" s="4">
         <v>46114</v>
       </c>
@@ -5548,7 +5520,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="2:8" ht="14.45">
+    <row r="14" spans="2:8" ht="14.4">
       <c r="B14" s="4">
         <v>46114</v>
       </c>
@@ -5565,7 +5537,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="14.45">
+    <row r="15" spans="2:8" ht="14.4">
       <c r="B15" s="4">
         <v>46114</v>
       </c>
@@ -5582,7 +5554,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="14.45">
+    <row r="16" spans="2:8" ht="14.4">
       <c r="B16" s="4">
         <v>46114</v>
       </c>
@@ -5599,7 +5571,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="14.45">
+    <row r="17" spans="2:8" ht="14.4">
       <c r="B17" s="4">
         <v>46114</v>
       </c>
@@ -5616,7 +5588,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="14.45">
+    <row r="18" spans="2:8" ht="14.4">
       <c r="B18" s="4">
         <v>46114</v>
       </c>
@@ -5633,7 +5605,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="14.45">
+    <row r="19" spans="2:8" ht="14.4">
       <c r="B19" s="4">
         <v>46118</v>
       </c>
@@ -5650,7 +5622,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="14.45">
+    <row r="20" spans="2:8" ht="14.4">
       <c r="B20" s="4">
         <v>46118</v>
       </c>
@@ -5667,7 +5639,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="14.45">
+    <row r="21" spans="2:8" ht="14.4">
       <c r="B21" s="4">
         <v>46118</v>
       </c>
@@ -5684,7 +5656,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="14.45">
+    <row r="22" spans="2:8" ht="14.4">
       <c r="B22" s="4">
         <v>46118</v>
       </c>
@@ -5701,7 +5673,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="23" spans="2:8" ht="14.45">
+    <row r="23" spans="2:8" ht="14.4">
       <c r="B23" s="4">
         <v>46118</v>
       </c>
@@ -5718,7 +5690,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="14.45">
+    <row r="24" spans="2:8" ht="14.4">
       <c r="B24" s="4">
         <v>46118</v>
       </c>
@@ -5735,7 +5707,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="2:8" ht="14.45">
+    <row r="25" spans="2:8" ht="14.4">
       <c r="B25" s="4">
         <v>46118</v>
       </c>
@@ -5752,7 +5724,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="14.45">
+    <row r="26" spans="2:8" ht="14.4">
       <c r="B26" s="4">
         <v>46118</v>
       </c>
@@ -5769,7 +5741,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="14.45">
+    <row r="27" spans="2:8" ht="14.4">
       <c r="B27" s="4">
         <v>46118</v>
       </c>
@@ -5786,7 +5758,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="14.45">
+    <row r="28" spans="2:8" ht="14.4">
       <c r="B28" s="4">
         <v>46118</v>
       </c>
@@ -5803,7 +5775,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="29" spans="2:8" ht="14.45">
+    <row r="29" spans="2:8" ht="14.4">
       <c r="B29" s="4">
         <v>46118</v>
       </c>
@@ -5820,7 +5792,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="14.45">
+    <row r="30" spans="2:8" ht="14.4">
       <c r="B30" s="4">
         <v>46118</v>
       </c>
@@ -5837,7 +5809,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="31" spans="2:8" ht="14.45">
+    <row r="31" spans="2:8" ht="14.4">
       <c r="B31" s="4">
         <v>46118</v>
       </c>
@@ -5854,7 +5826,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="14.45">
+    <row r="32" spans="2:8" ht="14.4">
       <c r="B32" s="4">
         <v>46118</v>
       </c>
@@ -5871,7 +5843,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="14.45">
+    <row r="33" spans="2:8" ht="14.4">
       <c r="B33" s="4">
         <v>46118</v>
       </c>
@@ -5888,7 +5860,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="34" spans="2:8" ht="14.45">
+    <row r="34" spans="2:8" ht="14.4">
       <c r="B34" s="4">
         <v>46118</v>
       </c>
@@ -5905,7 +5877,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="14.45">
+    <row r="35" spans="2:8" ht="14.4">
       <c r="B35" s="4">
         <v>46118</v>
       </c>
@@ -5922,7 +5894,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="14.45">
+    <row r="36" spans="2:8" ht="14.4">
       <c r="B36" s="4">
         <v>46119</v>
       </c>
@@ -5939,7 +5911,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="37" spans="2:8" ht="14.45">
+    <row r="37" spans="2:8" ht="14.4">
       <c r="B37" s="4">
         <v>46119</v>
       </c>
@@ -5956,7 +5928,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="38" spans="2:8" ht="14.45">
+    <row r="38" spans="2:8" ht="14.4">
       <c r="B38" s="4">
         <v>46119</v>
       </c>
@@ -5973,7 +5945,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="39" spans="2:8" ht="14.45">
+    <row r="39" spans="2:8" ht="14.4">
       <c r="B39" s="4">
         <v>46119</v>
       </c>
@@ -5990,7 +5962,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="14.45">
+    <row r="40" spans="2:8" ht="14.4">
       <c r="B40" s="4">
         <v>46119</v>
       </c>
@@ -6007,7 +5979,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="14.45">
+    <row r="41" spans="2:8" ht="14.4">
       <c r="B41" s="4">
         <v>46119</v>
       </c>
@@ -6024,7 +5996,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="14.45">
+    <row r="42" spans="2:8" ht="14.4">
       <c r="B42" s="4">
         <v>46119</v>
       </c>
@@ -6041,7 +6013,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="43" spans="2:8" ht="14.45">
+    <row r="43" spans="2:8" ht="14.4">
       <c r="B43" s="4">
         <v>46119</v>
       </c>
@@ -6061,7 +6033,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="14.45">
+    <row r="44" spans="2:8" ht="14.4">
       <c r="B44" s="4">
         <v>46119</v>
       </c>
@@ -6078,7 +6050,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="45" spans="2:8" ht="14.45">
+    <row r="45" spans="2:8" ht="14.4">
       <c r="B45" s="4">
         <v>46119</v>
       </c>
@@ -6095,7 +6067,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="14.45">
+    <row r="46" spans="2:8" ht="14.4">
       <c r="B46" s="4">
         <v>46120</v>
       </c>
@@ -6112,7 +6084,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="47" spans="2:8" ht="14.45">
+    <row r="47" spans="2:8" ht="14.4">
       <c r="B47" s="4">
         <v>46120</v>
       </c>
@@ -6129,7 +6101,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="48" spans="2:8" ht="14.45">
+    <row r="48" spans="2:8" ht="14.4">
       <c r="B48" s="4">
         <v>46120</v>
       </c>
@@ -6146,7 +6118,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="49" spans="2:8" ht="14.45">
+    <row r="49" spans="2:8" ht="14.4">
       <c r="B49" s="4">
         <v>46120</v>
       </c>
@@ -6163,7 +6135,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="50" spans="2:8" ht="14.45">
+    <row r="50" spans="2:8" ht="14.4">
       <c r="B50" s="4">
         <v>46120</v>
       </c>
@@ -6180,7 +6152,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="51" spans="2:8" ht="14.45">
+    <row r="51" spans="2:8" ht="14.4">
       <c r="B51" s="4">
         <v>46120</v>
       </c>
@@ -6197,7 +6169,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="52" spans="2:8" ht="14.45">
+    <row r="52" spans="2:8" ht="14.4">
       <c r="B52" s="4">
         <v>46120</v>
       </c>
@@ -6214,7 +6186,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="53" spans="2:8" ht="14.45">
+    <row r="53" spans="2:8" ht="14.4">
       <c r="B53" s="4">
         <v>46120</v>
       </c>
@@ -6231,7 +6203,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="54" spans="2:8" ht="14.45">
+    <row r="54" spans="2:8" ht="14.4">
       <c r="B54" s="4">
         <v>46120</v>
       </c>
@@ -6248,7 +6220,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="55" spans="2:8" ht="14.45">
+    <row r="55" spans="2:8" ht="14.4">
       <c r="B55" s="4">
         <v>46120</v>
       </c>
@@ -6265,7 +6237,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="56" spans="2:8" ht="14.45">
+    <row r="56" spans="2:8" ht="14.4">
       <c r="B56" s="4">
         <v>46120</v>
       </c>
@@ -6282,7 +6254,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="57" spans="2:8" ht="14.45">
+    <row r="57" spans="2:8" ht="14.4">
       <c r="B57" s="4">
         <v>46120</v>
       </c>
@@ -6299,7 +6271,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="58" spans="2:8" ht="14.45">
+    <row r="58" spans="2:8" ht="14.4">
       <c r="B58" s="14">
         <v>46121</v>
       </c>
@@ -6316,7 +6288,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="59" spans="2:8" ht="14.45">
+    <row r="59" spans="2:8" ht="14.4">
       <c r="B59" s="14">
         <v>46121</v>
       </c>
@@ -6333,7 +6305,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="60" spans="2:8" ht="14.45">
+    <row r="60" spans="2:8" ht="14.4">
       <c r="B60" s="14">
         <v>46121</v>
       </c>
@@ -6350,7 +6322,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="61" spans="2:8" ht="14.45">
+    <row r="61" spans="2:8" ht="14.4">
       <c r="B61" s="14">
         <v>46121</v>
       </c>
@@ -6367,7 +6339,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="62" spans="2:8" ht="14.45">
+    <row r="62" spans="2:8" ht="14.4">
       <c r="B62" s="14">
         <v>46121</v>
       </c>
@@ -6384,7 +6356,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="63" spans="2:8" ht="14.45">
+    <row r="63" spans="2:8" ht="14.4">
       <c r="B63" s="14">
         <v>46121</v>
       </c>
@@ -6401,7 +6373,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="14.45">
+    <row r="64" spans="2:8" ht="14.4">
       <c r="B64" s="4">
         <v>46122</v>
       </c>
@@ -6418,7 +6390,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="65" spans="2:8" ht="14.45">
+    <row r="65" spans="2:8" ht="14.4">
       <c r="B65" s="4">
         <v>46122</v>
       </c>
@@ -6435,7 +6407,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="66" spans="2:8" ht="14.45">
+    <row r="66" spans="2:8" ht="14.4">
       <c r="B66" s="4">
         <v>46122</v>
       </c>
@@ -6452,7 +6424,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="67" spans="2:8" ht="14.45">
+    <row r="67" spans="2:8" ht="14.4">
       <c r="B67" s="4">
         <v>46122</v>
       </c>
@@ -6469,7 +6441,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="68" spans="2:8" ht="14.45">
+    <row r="68" spans="2:8" ht="14.4">
       <c r="B68" s="4">
         <v>46122</v>
       </c>
@@ -6486,7 +6458,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="69" spans="2:8" ht="14.45">
+    <row r="69" spans="2:8" ht="14.4">
       <c r="B69" s="4">
         <v>46122</v>
       </c>
@@ -6503,7 +6475,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="70" spans="2:8" ht="14.45">
+    <row r="70" spans="2:8" ht="14.4">
       <c r="B70" s="4">
         <v>46122</v>
       </c>
@@ -6520,7 +6492,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="71" spans="2:8" ht="14.45">
+    <row r="71" spans="2:8" ht="14.4">
       <c r="B71" s="4">
         <v>46122</v>
       </c>
@@ -6537,7 +6509,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="72" spans="2:8" ht="14.45">
+    <row r="72" spans="2:8" ht="14.4">
       <c r="B72" s="4">
         <v>46122</v>
       </c>
@@ -6554,7 +6526,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="73" spans="2:8" ht="14.45">
+    <row r="73" spans="2:8" ht="14.4">
       <c r="B73" s="4">
         <v>46122</v>
       </c>
@@ -6571,7 +6543,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="74" spans="2:8" ht="14.45">
+    <row r="74" spans="2:8" ht="14.4">
       <c r="B74" s="4">
         <v>46122</v>
       </c>
@@ -6588,7 +6560,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="75" spans="2:8" ht="14.45">
+    <row r="75" spans="2:8" ht="14.4">
       <c r="B75" s="4">
         <v>46122</v>
       </c>
@@ -6605,7 +6577,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="76" spans="2:8" ht="14.45">
+    <row r="76" spans="2:8" ht="14.4">
       <c r="B76" s="4">
         <v>46122</v>
       </c>
@@ -6622,7 +6594,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="77" spans="2:8" ht="14.45">
+    <row r="77" spans="2:8" ht="14.4">
       <c r="B77" s="4">
         <v>46122</v>
       </c>
@@ -6639,7 +6611,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="78" spans="2:8" ht="14.45">
+    <row r="78" spans="2:8" ht="14.4">
       <c r="B78" s="4">
         <v>46125</v>
       </c>
@@ -6656,7 +6628,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="79" spans="2:8" ht="14.45">
+    <row r="79" spans="2:8" ht="14.4">
       <c r="B79" s="4">
         <v>46125</v>
       </c>
@@ -6673,7 +6645,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="80" spans="2:8" ht="14.45">
+    <row r="80" spans="2:8" ht="14.4">
       <c r="B80" s="4">
         <v>46126</v>
       </c>
@@ -6690,7 +6662,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="81" spans="2:8" ht="14.45">
+    <row r="81" spans="2:8" ht="14.4">
       <c r="B81" s="4">
         <v>46126</v>
       </c>
@@ -6707,7 +6679,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="82" spans="2:8" ht="14.45">
+    <row r="82" spans="2:8" ht="14.4">
       <c r="B82" s="4">
         <v>46126</v>
       </c>
@@ -6722,7 +6694,7 @@
       </c>
       <c r="H82" s="1"/>
     </row>
-    <row r="83" spans="2:8" ht="14.45">
+    <row r="83" spans="2:8" ht="14.4">
       <c r="B83" s="4">
         <v>46126</v>
       </c>
@@ -6737,7 +6709,7 @@
       </c>
       <c r="H83" s="1"/>
     </row>
-    <row r="84" spans="2:8" ht="14.45">
+    <row r="84" spans="2:8" ht="14.4">
       <c r="B84" s="4">
         <v>46126</v>
       </c>
@@ -6752,7 +6724,7 @@
       </c>
       <c r="H84" s="1"/>
     </row>
-    <row r="85" spans="2:8" ht="14.45">
+    <row r="85" spans="2:8" ht="14.4">
       <c r="B85" s="4">
         <v>46126</v>
       </c>
@@ -6767,7 +6739,7 @@
       </c>
       <c r="H85" s="1"/>
     </row>
-    <row r="86" spans="2:8" ht="14.45">
+    <row r="86" spans="2:8" ht="14.4">
       <c r="B86" s="4">
         <v>46126</v>
       </c>
@@ -6782,7 +6754,7 @@
       </c>
       <c r="H86" s="1"/>
     </row>
-    <row r="87" spans="2:8" ht="14.45">
+    <row r="87" spans="2:8" ht="14.4">
       <c r="B87" s="4">
         <v>46126</v>
       </c>
@@ -6797,7 +6769,7 @@
       </c>
       <c r="H87" s="1"/>
     </row>
-    <row r="88" spans="2:8" ht="14.45">
+    <row r="88" spans="2:8" ht="14.4">
       <c r="B88" s="4">
         <v>46126</v>
       </c>
@@ -6812,7 +6784,7 @@
       </c>
       <c r="H88" s="1"/>
     </row>
-    <row r="89" spans="2:8" ht="14.45">
+    <row r="89" spans="2:8" ht="14.4">
       <c r="B89" s="4">
         <v>46126</v>
       </c>
@@ -6826,7 +6798,7 @@
         <v>3030.85</v>
       </c>
     </row>
-    <row r="90" spans="2:8" ht="14.45">
+    <row r="90" spans="2:8" ht="14.4">
       <c r="B90" s="4">
         <v>46126</v>
       </c>
@@ -6840,7 +6812,7 @@
         <v>2445.6999999999998</v>
       </c>
     </row>
-    <row r="91" spans="2:8" ht="14.45">
+    <row r="91" spans="2:8" ht="14.4">
       <c r="B91" s="4">
         <v>46126</v>
       </c>
@@ -6854,7 +6826,7 @@
         <v>1260.79</v>
       </c>
     </row>
-    <row r="92" spans="2:8" ht="14.45">
+    <row r="92" spans="2:8" ht="14.4">
       <c r="B92" s="4">
         <v>46126</v>
       </c>
@@ -6868,7 +6840,7 @@
         <v>2504.25</v>
       </c>
     </row>
-    <row r="93" spans="2:8" ht="14.45">
+    <row r="93" spans="2:8" ht="14.4">
       <c r="B93" s="4">
         <v>46126</v>
       </c>
@@ -6882,7 +6854,7 @@
         <v>4470</v>
       </c>
     </row>
-    <row r="94" spans="2:8" ht="14.45">
+    <row r="94" spans="2:8" ht="14.4">
       <c r="B94" s="4">
         <v>46126</v>
       </c>
@@ -6896,7 +6868,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="95" spans="2:8" ht="14.45">
+    <row r="95" spans="2:8" ht="14.4">
       <c r="B95" s="4">
         <v>46126</v>
       </c>
@@ -6910,7 +6882,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="96" spans="2:8" ht="14.45">
+    <row r="96" spans="2:8" ht="14.4">
       <c r="B96" s="4">
         <v>46126</v>
       </c>
@@ -6924,7 +6896,7 @@
         <v>145.99</v>
       </c>
     </row>
-    <row r="97" spans="2:6" ht="14.45">
+    <row r="97" spans="2:6" ht="14.4">
       <c r="B97" s="4">
         <v>46126</v>
       </c>
@@ -6938,7 +6910,7 @@
         <v>621.67999999999995</v>
       </c>
     </row>
-    <row r="98" spans="2:6" ht="14.45">
+    <row r="98" spans="2:6" ht="14.4">
       <c r="B98" s="4">
         <v>46127</v>
       </c>
@@ -6952,7 +6924,7 @@
         <v>222.23</v>
       </c>
     </row>
-    <row r="99" spans="2:6" ht="14.45">
+    <row r="99" spans="2:6" ht="14.4">
       <c r="B99" s="4">
         <v>46127</v>
       </c>
@@ -6966,7 +6938,7 @@
         <v>1320.66</v>
       </c>
     </row>
-    <row r="100" spans="2:6" ht="14.45">
+    <row r="100" spans="2:6" ht="14.4">
       <c r="B100" s="4">
         <v>46127</v>
       </c>
@@ -6980,7 +6952,7 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="14.45">
+    <row r="101" spans="2:6" ht="14.4">
       <c r="B101" s="4">
         <v>46127</v>
       </c>
@@ -6994,7 +6966,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="102" spans="2:6" ht="14.45">
+    <row r="102" spans="2:6" ht="14.4">
       <c r="B102" s="4">
         <v>46128</v>
       </c>
@@ -7008,7 +6980,7 @@
         <v>3806.08</v>
       </c>
     </row>
-    <row r="103" spans="2:6" ht="14.45">
+    <row r="103" spans="2:6" ht="14.4">
       <c r="B103" s="4">
         <v>46128</v>
       </c>
@@ -7022,7 +6994,7 @@
         <v>2454.98</v>
       </c>
     </row>
-    <row r="104" spans="2:6" ht="14.45">
+    <row r="104" spans="2:6" ht="14.4">
       <c r="B104" s="4">
         <v>46128</v>
       </c>
@@ -7036,7 +7008,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="105" spans="2:6" ht="14.45">
+    <row r="105" spans="2:6" ht="14.4">
       <c r="B105" s="4">
         <v>46128</v>
       </c>
@@ -7050,7 +7022,7 @@
         <v>2809.99</v>
       </c>
     </row>
-    <row r="106" spans="2:6" ht="14.45">
+    <row r="106" spans="2:6" ht="14.4">
       <c r="B106" s="4">
         <v>46128</v>
       </c>
@@ -7064,7 +7036,7 @@
         <v>152.93</v>
       </c>
     </row>
-    <row r="107" spans="2:6" ht="14.45">
+    <row r="107" spans="2:6" ht="14.4">
       <c r="B107" s="4">
         <v>46128</v>
       </c>
@@ -7078,7 +7050,7 @@
         <v>3664.04</v>
       </c>
     </row>
-    <row r="108" spans="2:6" ht="14.45">
+    <row r="108" spans="2:6" ht="14.4">
       <c r="B108" s="4">
         <v>46128</v>
       </c>
@@ -7092,7 +7064,7 @@
         <v>896.61</v>
       </c>
     </row>
-    <row r="109" spans="2:6" ht="14.45">
+    <row r="109" spans="2:6" ht="14.4">
       <c r="B109" s="4">
         <v>46128</v>
       </c>
@@ -7106,7 +7078,7 @@
         <v>536.58000000000004</v>
       </c>
     </row>
-    <row r="110" spans="2:6" ht="14.45">
+    <row r="110" spans="2:6" ht="14.4">
       <c r="B110" s="4">
         <v>46128</v>
       </c>
@@ -7120,7 +7092,7 @@
         <v>4498.9399999999996</v>
       </c>
     </row>
-    <row r="111" spans="2:6" ht="14.45">
+    <row r="111" spans="2:6" ht="14.4">
       <c r="B111" s="4">
         <v>46128</v>
       </c>
@@ -7134,7 +7106,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="112" spans="2:6" ht="14.45">
+    <row r="112" spans="2:6" ht="14.4">
       <c r="B112" s="4">
         <v>46128</v>
       </c>
@@ -7148,7 +7120,7 @@
         <v>91.17</v>
       </c>
     </row>
-    <row r="113" spans="2:6" ht="14.45">
+    <row r="113" spans="2:6" ht="14.4">
       <c r="B113" s="4">
         <v>46128</v>
       </c>
@@ -7162,7 +7134,7 @@
         <v>13953.27</v>
       </c>
     </row>
-    <row r="114" spans="2:6" ht="14.45">
+    <row r="114" spans="2:6" ht="14.4">
       <c r="B114" s="4">
         <v>46128</v>
       </c>
@@ -7176,7 +7148,7 @@
         <v>130.5</v>
       </c>
     </row>
-    <row r="115" spans="2:6" ht="14.45">
+    <row r="115" spans="2:6" ht="14.4">
       <c r="B115" s="4">
         <v>46128</v>
       </c>
@@ -7190,7 +7162,7 @@
         <v>5916.4</v>
       </c>
     </row>
-    <row r="116" spans="2:6" ht="14.45">
+    <row r="116" spans="2:6" ht="14.4">
       <c r="B116" s="4">
         <v>46128</v>
       </c>
@@ -7204,7 +7176,7 @@
         <v>13391.92</v>
       </c>
     </row>
-    <row r="117" spans="2:6" ht="14.45">
+    <row r="117" spans="2:6" ht="14.4">
       <c r="B117" s="4">
         <v>46128</v>
       </c>
@@ -7218,7 +7190,7 @@
         <v>826.63</v>
       </c>
     </row>
-    <row r="118" spans="2:6" ht="14.45">
+    <row r="118" spans="2:6" ht="14.4">
       <c r="B118" s="4">
         <v>46128</v>
       </c>
@@ -7232,7 +7204,7 @@
         <v>91.8</v>
       </c>
     </row>
-    <row r="119" spans="2:6" ht="14.45">
+    <row r="119" spans="2:6" ht="14.4">
       <c r="B119" s="4">
         <v>46128</v>
       </c>
@@ -7246,7 +7218,7 @@
         <v>359.29</v>
       </c>
     </row>
-    <row r="120" spans="2:6" ht="14.45">
+    <row r="120" spans="2:6" ht="14.4">
       <c r="B120" s="4">
         <v>46128</v>
       </c>
@@ -7260,7 +7232,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="121" spans="2:6" ht="14.45">
+    <row r="121" spans="2:6" ht="14.4">
       <c r="B121" s="4">
         <v>46129</v>
       </c>
@@ -8143,7 +8115,7 @@
       <c r="D181" s="43" t="s">
         <v>171</v>
       </c>
-      <c r="E181" s="64"/>
+      <c r="E181" s="51"/>
       <c r="F181" s="6">
         <v>1019.45</v>
       </c>
@@ -8158,7 +8130,7 @@
       <c r="D182" s="43" t="s">
         <v>213</v>
       </c>
-      <c r="E182" s="64"/>
+      <c r="E182" s="51"/>
       <c r="F182" s="6">
         <v>4000</v>
       </c>
@@ -8173,7 +8145,7 @@
       <c r="D183" s="43" t="s">
         <v>208</v>
       </c>
-      <c r="E183" s="64"/>
+      <c r="E183" s="51"/>
       <c r="F183" s="6">
         <v>126.87</v>
       </c>
@@ -8188,7 +8160,7 @@
       <c r="D184" s="43" t="s">
         <v>174</v>
       </c>
-      <c r="E184" s="64"/>
+      <c r="E184" s="51"/>
       <c r="F184" s="6">
         <v>145.99</v>
       </c>
@@ -8203,7 +8175,7 @@
       <c r="D185" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="E185" s="64"/>
+      <c r="E185" s="51"/>
       <c r="F185" s="6">
         <v>458.33</v>
       </c>
@@ -8218,7 +8190,7 @@
       <c r="D186" s="43" t="s">
         <v>216</v>
       </c>
-      <c r="E186" s="64"/>
+      <c r="E186" s="51"/>
       <c r="F186" s="6">
         <v>8982.7099999999991</v>
       </c>
@@ -8233,7 +8205,7 @@
       <c r="D187" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="E187" s="64"/>
+      <c r="E187" s="51"/>
       <c r="F187" s="6">
         <v>438.72</v>
       </c>
@@ -8248,7 +8220,7 @@
       <c r="D188" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="E188" s="64"/>
+      <c r="E188" s="51"/>
       <c r="F188" s="6">
         <v>826.34</v>
       </c>
@@ -8263,7 +8235,7 @@
       <c r="D189" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="E189" s="64"/>
+      <c r="E189" s="51"/>
       <c r="F189" s="6">
         <v>2278.8000000000002</v>
       </c>
@@ -8278,7 +8250,7 @@
       <c r="D190" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="E190" s="64"/>
+      <c r="E190" s="51"/>
       <c r="F190" s="6">
         <v>8219</v>
       </c>
@@ -8293,7 +8265,7 @@
       <c r="D191" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="E191" s="64"/>
+      <c r="E191" s="51"/>
       <c r="F191" s="6">
         <v>1700</v>
       </c>
@@ -8308,7 +8280,7 @@
       <c r="D192" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="E192" s="64"/>
+      <c r="E192" s="51"/>
       <c r="F192" s="6">
         <v>115.6</v>
       </c>
@@ -8323,7 +8295,7 @@
       <c r="D193" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="E193" s="64"/>
+      <c r="E193" s="51"/>
       <c r="F193" s="6">
         <v>258.01</v>
       </c>
@@ -8338,7 +8310,7 @@
       <c r="D194" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E194" s="64"/>
+      <c r="E194" s="51"/>
       <c r="F194" s="6">
         <v>1244.3</v>
       </c>
@@ -8353,7 +8325,7 @@
       <c r="D195" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="E195" s="64"/>
+      <c r="E195" s="51"/>
       <c r="F195" s="6">
         <v>3941.28</v>
       </c>
@@ -8368,7 +8340,7 @@
       <c r="D196" s="43" t="s">
         <v>219</v>
       </c>
-      <c r="E196" s="64"/>
+      <c r="E196" s="51"/>
       <c r="F196" s="6">
         <v>1359.89</v>
       </c>
@@ -8383,7 +8355,7 @@
       <c r="D197" s="43" t="s">
         <v>171</v>
       </c>
-      <c r="E197" s="64"/>
+      <c r="E197" s="51"/>
       <c r="F197" s="6">
         <v>183</v>
       </c>
@@ -8398,7 +8370,7 @@
       <c r="D198" s="43" t="s">
         <v>134</v>
       </c>
-      <c r="E198" s="64"/>
+      <c r="E198" s="51"/>
       <c r="F198" s="6">
         <v>2400</v>
       </c>
@@ -8413,7 +8385,7 @@
       <c r="D199" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="E199" s="64"/>
+      <c r="E199" s="51"/>
       <c r="F199" s="6">
         <v>100</v>
       </c>
@@ -8428,7 +8400,7 @@
       <c r="D200" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="E200" s="64"/>
+      <c r="E200" s="51"/>
       <c r="F200" s="6">
         <v>142.69999999999999</v>
       </c>
@@ -8443,7 +8415,7 @@
       <c r="D201" s="43" t="s">
         <v>223</v>
       </c>
-      <c r="E201" s="64"/>
+      <c r="E201" s="51"/>
       <c r="F201" s="6">
         <v>600</v>
       </c>
@@ -8458,7 +8430,7 @@
       <c r="D202" s="43" t="s">
         <v>225</v>
       </c>
-      <c r="E202" s="64"/>
+      <c r="E202" s="51"/>
       <c r="F202" s="6">
         <v>185.6</v>
       </c>
@@ -8473,7 +8445,7 @@
       <c r="D203" s="43" t="s">
         <v>226</v>
       </c>
-      <c r="E203" s="64"/>
+      <c r="E203" s="51"/>
       <c r="F203" s="6">
         <v>3480</v>
       </c>
@@ -8488,7 +8460,7 @@
       <c r="D204" s="43" t="s">
         <v>228</v>
       </c>
-      <c r="E204" s="64"/>
+      <c r="E204" s="51"/>
       <c r="F204" s="6">
         <v>975</v>
       </c>
@@ -8503,7 +8475,7 @@
       <c r="D205" s="43" t="s">
         <v>229</v>
       </c>
-      <c r="E205" s="64"/>
+      <c r="E205" s="51"/>
       <c r="F205" s="6">
         <v>467.59</v>
       </c>
@@ -8518,7 +8490,7 @@
       <c r="D206" s="43" t="s">
         <v>231</v>
       </c>
-      <c r="E206" s="64"/>
+      <c r="E206" s="51"/>
       <c r="F206" s="6">
         <v>2900</v>
       </c>
@@ -8533,7 +8505,7 @@
       <c r="D207" s="43" t="s">
         <v>233</v>
       </c>
-      <c r="E207" s="64"/>
+      <c r="E207" s="51"/>
       <c r="F207" s="6">
         <v>280</v>
       </c>
@@ -8548,7 +8520,7 @@
       <c r="D208" s="43" t="s">
         <v>235</v>
       </c>
-      <c r="E208" s="64"/>
+      <c r="E208" s="51"/>
       <c r="F208" s="6">
         <v>3513.53</v>
       </c>
@@ -8563,7 +8535,7 @@
       <c r="D209" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="E209" s="64"/>
+      <c r="E209" s="51"/>
       <c r="F209" s="6">
         <v>23958.78</v>
       </c>
@@ -8578,7 +8550,7 @@
       <c r="D210" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="E210" s="64"/>
+      <c r="E210" s="51"/>
       <c r="F210" s="6">
         <v>757.43</v>
       </c>
@@ -8593,7 +8565,7 @@
       <c r="D211" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="E211" s="64"/>
+      <c r="E211" s="51"/>
       <c r="F211" s="6">
         <v>833.33</v>
       </c>
@@ -8608,7 +8580,7 @@
       <c r="D212" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="E212" s="64"/>
+      <c r="E212" s="51"/>
       <c r="F212" s="6">
         <v>859.48</v>
       </c>
@@ -8623,7 +8595,7 @@
       <c r="D213" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="E213" s="64"/>
+      <c r="E213" s="51"/>
       <c r="F213" s="6">
         <v>36035.22</v>
       </c>
@@ -8638,7 +8610,7 @@
       <c r="D214" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="E214" s="64"/>
+      <c r="E214" s="51"/>
       <c r="F214" s="6">
         <v>880.28</v>
       </c>
@@ -8653,7 +8625,7 @@
       <c r="D215" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="E215" s="64"/>
+      <c r="E215" s="51"/>
       <c r="F215" s="6">
         <v>1717.5</v>
       </c>
@@ -8668,7 +8640,7 @@
       <c r="D216" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="E216" s="64"/>
+      <c r="E216" s="51"/>
       <c r="F216" s="6">
         <v>2072.1</v>
       </c>
@@ -8683,7 +8655,7 @@
       <c r="D217" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="E217" s="64"/>
+      <c r="E217" s="51"/>
       <c r="F217" s="6">
         <v>2504.25</v>
       </c>
@@ -8698,7 +8670,7 @@
       <c r="D218" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="E218" s="64"/>
+      <c r="E218" s="51"/>
       <c r="F218" s="6">
         <v>17790.04</v>
       </c>
@@ -8713,7 +8685,7 @@
       <c r="D219" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="E219" s="64"/>
+      <c r="E219" s="51"/>
       <c r="F219" s="6">
         <v>2667.6</v>
       </c>
@@ -8728,7 +8700,7 @@
       <c r="D220" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="E220" s="64"/>
+      <c r="E220" s="51"/>
       <c r="F220" s="6">
         <v>130</v>
       </c>
@@ -8743,7 +8715,7 @@
       <c r="D221" s="43" t="s">
         <v>239</v>
       </c>
-      <c r="E221" s="64"/>
+      <c r="E221" s="51"/>
       <c r="F221" s="6">
         <v>1150</v>
       </c>
@@ -8758,7 +8730,7 @@
       <c r="D222" s="43" t="s">
         <v>235</v>
       </c>
-      <c r="E222" s="64"/>
+      <c r="E222" s="51"/>
       <c r="F222" s="6">
         <v>1775.9</v>
       </c>
@@ -8766,12 +8738,12 @@
     <row r="223" spans="2:6" ht="15" customHeight="1">
       <c r="B223" s="4"/>
       <c r="D223" s="43"/>
-      <c r="E223" s="64"/>
+      <c r="E223" s="51"/>
     </row>
     <row r="224" spans="2:6" ht="15" customHeight="1">
       <c r="B224" s="4"/>
       <c r="D224" s="43"/>
-      <c r="E224" s="64"/>
+      <c r="E224" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -8796,25 +8768,25 @@
   <dimension ref="B1:F121"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="14.45"/>
+    <row r="1" spans="2:6" ht="14.4"/>
     <row r="2" spans="2:6" ht="15" customHeight="1">
-      <c r="B2" s="99" t="s">
+      <c r="B2" s="88" t="s">
         <v>240</v>
       </c>
-      <c r="C2" s="100"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="100"/>
-    </row>
-    <row r="3" spans="2:6" ht="14.45">
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+    </row>
+    <row r="3" spans="2:6" ht="14.4">
       <c r="B3" s="18" t="s">
         <v>24</v>
       </c>
@@ -8831,7 +8803,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="4" spans="2:6" ht="14.45">
+    <row r="4" spans="2:6" ht="14.4">
       <c r="B4" s="19">
         <v>46116</v>
       </c>
@@ -8848,7 +8820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="14.45">
+    <row r="5" spans="2:6" ht="14.4">
       <c r="B5" s="16">
         <v>46121</v>
       </c>
@@ -8865,7 +8837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="14.45">
+    <row r="6" spans="2:6" ht="14.4">
       <c r="B6" s="19">
         <v>46123</v>
       </c>
@@ -8882,7 +8854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="14.45">
+    <row r="7" spans="2:6" ht="14.4">
       <c r="B7" s="16">
         <v>46125</v>
       </c>
@@ -8899,7 +8871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="14.45">
+    <row r="8" spans="2:6" ht="14.4">
       <c r="B8" s="29">
         <v>46133</v>
       </c>
@@ -8916,7 +8888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="14.45">
+    <row r="9" spans="2:6" ht="14.4">
       <c r="B9" s="26">
         <v>46135</v>
       </c>
@@ -8933,7 +8905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="14.45">
+    <row r="10" spans="2:6" ht="14.4">
       <c r="B10" s="31">
         <v>46137</v>
       </c>
@@ -8950,7 +8922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="14.45">
+    <row r="11" spans="2:6" ht="14.4">
       <c r="B11" s="26">
         <v>46140</v>
       </c>
@@ -8967,7 +8939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="14.45">
+    <row r="12" spans="2:6" ht="14.4">
       <c r="B12" s="39">
         <v>46140</v>
       </c>
@@ -8984,7 +8956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="14.45">
+    <row r="13" spans="2:6" ht="14.4">
       <c r="B13" s="33">
         <v>46146</v>
       </c>
@@ -9001,7 +8973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="14.45">
+    <row r="14" spans="2:6" ht="14.4">
       <c r="B14" s="36">
         <v>46153</v>
       </c>
@@ -9018,7 +8990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="14.45">
+    <row r="15" spans="2:6" ht="14.4">
       <c r="B15" s="33">
         <v>46163</v>
       </c>
@@ -9035,7 +9007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:6" ht="14.45">
+    <row r="16" spans="2:6" ht="14.4">
       <c r="B16" s="36">
         <v>46167</v>
       </c>
@@ -9052,7 +9024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:6" ht="14.45">
+    <row r="17" spans="2:6" ht="14.4">
       <c r="B17" s="33">
         <v>46184</v>
       </c>
@@ -9069,7 +9041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:6" ht="14.45">
+    <row r="18" spans="2:6" ht="14.4">
       <c r="B18" s="36">
         <v>46198</v>
       </c>
@@ -9086,109 +9058,109 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:6" ht="14.45"/>
-    <row r="20" spans="2:6" ht="14.45"/>
-    <row r="21" spans="2:6" ht="14.45"/>
-    <row r="22" spans="2:6" ht="14.45"/>
-    <row r="23" spans="2:6" ht="14.45"/>
-    <row r="24" spans="2:6" ht="14.45"/>
-    <row r="25" spans="2:6" ht="14.45"/>
-    <row r="26" spans="2:6" ht="14.45"/>
-    <row r="27" spans="2:6" ht="14.45"/>
-    <row r="28" spans="2:6" ht="14.45"/>
-    <row r="29" spans="2:6" ht="14.45"/>
-    <row r="30" spans="2:6" ht="14.45"/>
-    <row r="31" spans="2:6" ht="14.45"/>
-    <row r="32" spans="2:6" ht="14.45"/>
-    <row r="33" ht="14.45"/>
-    <row r="34" ht="14.45"/>
-    <row r="35" ht="14.45"/>
-    <row r="36" ht="14.45"/>
-    <row r="37" ht="14.45"/>
-    <row r="38" ht="14.45"/>
-    <row r="39" ht="14.45"/>
-    <row r="40" ht="14.45"/>
-    <row r="41" ht="14.45"/>
-    <row r="42" ht="14.45"/>
-    <row r="43" ht="14.45"/>
-    <row r="44" ht="14.45"/>
-    <row r="45" ht="14.45"/>
-    <row r="46" ht="14.45"/>
-    <row r="47" ht="14.45"/>
-    <row r="48" ht="14.45"/>
-    <row r="49" ht="14.45"/>
-    <row r="50" ht="14.45"/>
-    <row r="51" ht="14.45"/>
-    <row r="52" ht="14.45"/>
-    <row r="53" ht="14.45"/>
-    <row r="54" ht="14.45"/>
-    <row r="55" ht="14.45"/>
-    <row r="56" ht="14.45"/>
-    <row r="57" ht="14.45"/>
-    <row r="58" ht="14.45"/>
-    <row r="59" ht="14.45"/>
-    <row r="60" ht="14.45"/>
-    <row r="61" ht="14.45"/>
-    <row r="62" ht="14.45"/>
-    <row r="63" ht="14.45"/>
-    <row r="64" ht="14.45"/>
-    <row r="65" ht="14.45"/>
-    <row r="66" ht="14.45"/>
-    <row r="67" ht="14.45"/>
-    <row r="68" ht="14.45"/>
-    <row r="69" ht="14.45"/>
-    <row r="70" ht="14.45"/>
-    <row r="71" ht="14.45"/>
-    <row r="72" ht="14.45"/>
-    <row r="73" ht="14.45"/>
-    <row r="74" ht="14.45"/>
-    <row r="75" ht="14.45"/>
-    <row r="76" ht="14.45"/>
-    <row r="77" ht="14.45"/>
-    <row r="78" ht="14.45"/>
-    <row r="79" ht="14.45"/>
-    <row r="80" ht="14.45"/>
-    <row r="81" ht="14.45"/>
-    <row r="82" ht="14.45"/>
-    <row r="83" ht="14.45"/>
-    <row r="84" ht="14.45"/>
-    <row r="85" ht="14.45"/>
-    <row r="86" ht="14.45"/>
-    <row r="87" ht="14.45"/>
-    <row r="88" ht="14.45"/>
-    <row r="89" ht="14.45"/>
-    <row r="90" ht="14.45"/>
-    <row r="91" ht="14.45"/>
-    <row r="92" ht="14.45"/>
-    <row r="93" ht="14.45"/>
-    <row r="94" ht="14.45"/>
-    <row r="95" ht="14.45"/>
-    <row r="96" ht="14.45"/>
-    <row r="97" ht="14.45"/>
-    <row r="98" ht="14.45"/>
-    <row r="99" ht="14.45"/>
-    <row r="100" ht="14.45"/>
-    <row r="101" ht="14.45"/>
-    <row r="102" ht="14.45"/>
-    <row r="103" ht="14.45"/>
-    <row r="104" ht="14.45"/>
-    <row r="105" ht="14.45"/>
-    <row r="106" ht="14.45"/>
-    <row r="107" ht="14.45"/>
-    <row r="108" ht="14.45"/>
-    <row r="109" ht="14.45"/>
-    <row r="110" ht="14.45"/>
-    <row r="111" ht="14.45"/>
-    <row r="112" ht="14.45"/>
-    <row r="113" ht="14.45"/>
-    <row r="114" ht="14.45"/>
-    <row r="115" ht="14.45"/>
-    <row r="116" ht="14.45"/>
-    <row r="117" ht="14.45"/>
-    <row r="118" ht="14.45"/>
-    <row r="119" ht="14.45"/>
-    <row r="120" ht="14.45"/>
-    <row r="121" ht="14.45"/>
+    <row r="19" spans="2:6" ht="14.4"/>
+    <row r="20" spans="2:6" ht="14.4"/>
+    <row r="21" spans="2:6" ht="14.4"/>
+    <row r="22" spans="2:6" ht="14.4"/>
+    <row r="23" spans="2:6" ht="14.4"/>
+    <row r="24" spans="2:6" ht="14.4"/>
+    <row r="25" spans="2:6" ht="14.4"/>
+    <row r="26" spans="2:6" ht="14.4"/>
+    <row r="27" spans="2:6" ht="14.4"/>
+    <row r="28" spans="2:6" ht="14.4"/>
+    <row r="29" spans="2:6" ht="14.4"/>
+    <row r="30" spans="2:6" ht="14.4"/>
+    <row r="31" spans="2:6" ht="14.4"/>
+    <row r="32" spans="2:6" ht="14.4"/>
+    <row r="33" ht="14.4"/>
+    <row r="34" ht="14.4"/>
+    <row r="35" ht="14.4"/>
+    <row r="36" ht="14.4"/>
+    <row r="37" ht="14.4"/>
+    <row r="38" ht="14.4"/>
+    <row r="39" ht="14.4"/>
+    <row r="40" ht="14.4"/>
+    <row r="41" ht="14.4"/>
+    <row r="42" ht="14.4"/>
+    <row r="43" ht="14.4"/>
+    <row r="44" ht="14.4"/>
+    <row r="45" ht="14.4"/>
+    <row r="46" ht="14.4"/>
+    <row r="47" ht="14.4"/>
+    <row r="48" ht="14.4"/>
+    <row r="49" ht="14.4"/>
+    <row r="50" ht="14.4"/>
+    <row r="51" ht="14.4"/>
+    <row r="52" ht="14.4"/>
+    <row r="53" ht="14.4"/>
+    <row r="54" ht="14.4"/>
+    <row r="55" ht="14.4"/>
+    <row r="56" ht="14.4"/>
+    <row r="57" ht="14.4"/>
+    <row r="58" ht="14.4"/>
+    <row r="59" ht="14.4"/>
+    <row r="60" ht="14.4"/>
+    <row r="61" ht="14.4"/>
+    <row r="62" ht="14.4"/>
+    <row r="63" ht="14.4"/>
+    <row r="64" ht="14.4"/>
+    <row r="65" ht="14.4"/>
+    <row r="66" ht="14.4"/>
+    <row r="67" ht="14.4"/>
+    <row r="68" ht="14.4"/>
+    <row r="69" ht="14.4"/>
+    <row r="70" ht="14.4"/>
+    <row r="71" ht="14.4"/>
+    <row r="72" ht="14.4"/>
+    <row r="73" ht="14.4"/>
+    <row r="74" ht="14.4"/>
+    <row r="75" ht="14.4"/>
+    <row r="76" ht="14.4"/>
+    <row r="77" ht="14.4"/>
+    <row r="78" ht="14.4"/>
+    <row r="79" ht="14.4"/>
+    <row r="80" ht="14.4"/>
+    <row r="81" ht="14.4"/>
+    <row r="82" ht="14.4"/>
+    <row r="83" ht="14.4"/>
+    <row r="84" ht="14.4"/>
+    <row r="85" ht="14.4"/>
+    <row r="86" ht="14.4"/>
+    <row r="87" ht="14.4"/>
+    <row r="88" ht="14.4"/>
+    <row r="89" ht="14.4"/>
+    <row r="90" ht="14.4"/>
+    <row r="91" ht="14.4"/>
+    <row r="92" ht="14.4"/>
+    <row r="93" ht="14.4"/>
+    <row r="94" ht="14.4"/>
+    <row r="95" ht="14.4"/>
+    <row r="96" ht="14.4"/>
+    <row r="97" ht="14.4"/>
+    <row r="98" ht="14.4"/>
+    <row r="99" ht="14.4"/>
+    <row r="100" ht="14.4"/>
+    <row r="101" ht="14.4"/>
+    <row r="102" ht="14.4"/>
+    <row r="103" ht="14.4"/>
+    <row r="104" ht="14.4"/>
+    <row r="105" ht="14.4"/>
+    <row r="106" ht="14.4"/>
+    <row r="107" ht="14.4"/>
+    <row r="108" ht="14.4"/>
+    <row r="109" ht="14.4"/>
+    <row r="110" ht="14.4"/>
+    <row r="111" ht="14.4"/>
+    <row r="112" ht="14.4"/>
+    <row r="113" ht="14.4"/>
+    <row r="114" ht="14.4"/>
+    <row r="115" ht="14.4"/>
+    <row r="116" ht="14.4"/>
+    <row r="117" ht="14.4"/>
+    <row r="118" ht="14.4"/>
+    <row r="119" ht="14.4"/>
+    <row r="120" ht="14.4"/>
+    <row r="121" ht="14.4"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:F2"/>
@@ -9201,13 +9173,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E746537A-A23A-41AB-9161-94E002D525F0}">
   <dimension ref="B1:G55"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="2.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="2.6640625" customWidth="1"/>
     <col min="7" max="7" width="31" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9218,12 +9190,12 @@
       </c>
     </row>
     <row r="2" spans="2:7">
-      <c r="B2" s="95" t="s">
+      <c r="B2" s="84" t="s">
         <v>246</v>
       </c>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
       <c r="G2" s="7" t="s">
         <v>56</v>
       </c>
